--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -3433,10 +3433,10 @@
         <v>39</v>
       </c>
       <c r="N75" t="n">
-        <v>15403.521040462</v>
+        <v>15403.521104651</v>
       </c>
       <c r="O75" t="n">
-        <v>600737.320578018</v>
+        <v>600737.323081389</v>
       </c>
       <c r="P75" t="n">
         <v>33500</v>
@@ -3472,10 +3472,10 @@
         <v>74</v>
       </c>
       <c r="N76" t="n">
-        <v>14857.623272727</v>
+        <v>14857.623287671</v>
       </c>
       <c r="O76" t="n">
-        <v>1099464.122181798</v>
+        <v>1099464.123287654</v>
       </c>
       <c r="P76" t="n">
         <v>34900</v>
@@ -11711,10 +11711,10 @@
         <v>1378</v>
       </c>
       <c r="N269" t="n">
-        <v>5216.8959816133</v>
+        <v>5216.8959810174</v>
       </c>
       <c r="O269" t="n">
-        <v>7188882.662663127</v>
+        <v>7188882.661841977</v>
       </c>
       <c r="P269" t="n">
         <v>8500</v>
@@ -13203,22 +13203,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N303" t="n">
         <v>7939.23</v>
       </c>
       <c r="O303" t="n">
-        <v>1198823.73</v>
+        <v>1190884.5</v>
       </c>
       <c r="P303" t="n">
         <v>14900</v>
       </c>
       <c r="Q303" t="n">
-        <v>2249900</v>
+        <v>2235000</v>
       </c>
     </row>
     <row r="304">
@@ -13559,22 +13559,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M311" t="n">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="N311" t="n">
         <v>1203.38</v>
       </c>
       <c r="O311" t="n">
-        <v>471724.96</v>
+        <v>464504.6800000001</v>
       </c>
       <c r="P311" t="n">
         <v>1900</v>
       </c>
       <c r="Q311" t="n">
-        <v>744800</v>
+        <v>733400</v>
       </c>
     </row>
     <row r="312">
@@ -13912,22 +13912,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M319" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N319" t="n">
         <v>7041</v>
       </c>
       <c r="O319" t="n">
-        <v>288681</v>
+        <v>281640</v>
       </c>
       <c r="P319" t="n">
         <v>11500</v>
       </c>
       <c r="Q319" t="n">
-        <v>471500</v>
+        <v>460000</v>
       </c>
     </row>
     <row r="320">
@@ -13958,22 +13958,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M320" t="n">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="N320" t="n">
         <v>5667.94</v>
       </c>
       <c r="O320" t="n">
-        <v>4222615.3</v>
+        <v>4216947.359999999</v>
       </c>
       <c r="P320" t="n">
         <v>9500</v>
       </c>
       <c r="Q320" t="n">
-        <v>7077500</v>
+        <v>7068000</v>
       </c>
     </row>
     <row r="321">
@@ -14269,10 +14269,10 @@
         <v>358</v>
       </c>
       <c r="N327" t="n">
-        <v>3594.2533147632</v>
+        <v>3596.7580209059</v>
       </c>
       <c r="O327" t="n">
-        <v>1286742.686685225</v>
+        <v>1287639.371484312</v>
       </c>
       <c r="P327" t="n">
         <v>6500</v>
@@ -14312,22 +14312,22 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M328" t="n">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="N328" t="n">
         <v>489.88</v>
       </c>
       <c r="O328" t="n">
-        <v>191053.2</v>
+        <v>183215.12</v>
       </c>
       <c r="P328" t="n">
         <v>700</v>
       </c>
       <c r="Q328" t="n">
-        <v>273000</v>
+        <v>261800</v>
       </c>
     </row>
     <row r="329">
@@ -15706,10 +15706,10 @@
         <v>8119</v>
       </c>
       <c r="N360" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O360" t="n">
-        <v>35489539.46998077</v>
+        <v>35494373.89846043</v>
       </c>
       <c r="P360" t="n">
         <v>8900</v>
@@ -16644,22 +16644,22 @@
         <v>0</v>
       </c>
       <c r="L382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M382" t="n">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="N382" t="n">
         <v>17472.91</v>
       </c>
       <c r="O382" t="n">
-        <v>33338312.28</v>
+        <v>33303366.46</v>
       </c>
       <c r="P382" t="n">
         <v>2900</v>
       </c>
       <c r="Q382" t="n">
-        <v>5533200</v>
+        <v>5527400</v>
       </c>
     </row>
     <row r="383">
@@ -16688,22 +16688,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M383" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N383" t="n">
         <v>1343.77</v>
       </c>
       <c r="O383" t="n">
-        <v>217690.74</v>
+        <v>208284.35</v>
       </c>
       <c r="P383" t="n">
         <v>2500</v>
       </c>
       <c r="Q383" t="n">
-        <v>405000</v>
+        <v>387500</v>
       </c>
     </row>
     <row r="384">
@@ -16820,22 +16820,22 @@
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M386" t="n">
-        <v>2180</v>
+        <v>2164</v>
       </c>
       <c r="N386" t="n">
         <v>1387.55</v>
       </c>
       <c r="O386" t="n">
-        <v>3024859</v>
+        <v>3002658.2</v>
       </c>
       <c r="P386" t="n">
         <v>2300</v>
       </c>
       <c r="Q386" t="n">
-        <v>5014000</v>
+        <v>4977200</v>
       </c>
     </row>
     <row r="387">
@@ -17964,22 +17964,22 @@
         <v>0</v>
       </c>
       <c r="L412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M412" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N412" t="n">
         <v>3751</v>
       </c>
       <c r="O412" t="n">
-        <v>138787</v>
+        <v>135036</v>
       </c>
       <c r="P412" t="n">
         <v>6400</v>
       </c>
       <c r="Q412" t="n">
-        <v>236800</v>
+        <v>230400</v>
       </c>
     </row>
     <row r="413">
@@ -18288,10 +18288,10 @@
         <v>348</v>
       </c>
       <c r="N419" t="n">
-        <v>1550.1943880809</v>
+        <v>1550.1943922358</v>
       </c>
       <c r="O419" t="n">
-        <v>539467.6470521531</v>
+        <v>539467.6484980584</v>
       </c>
       <c r="P419" t="n">
         <v>2500</v>
@@ -18380,10 +18380,10 @@
         <v>438</v>
       </c>
       <c r="N421" t="n">
-        <v>2403.5165803524</v>
+        <v>2403.5166025127</v>
       </c>
       <c r="O421" t="n">
-        <v>1052740.262194351</v>
+        <v>1052740.271900563</v>
       </c>
       <c r="P421" t="n">
         <v>3500</v>
@@ -18464,22 +18464,22 @@
         <v>0</v>
       </c>
       <c r="L423" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M423" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N423" t="n">
-        <v>2521.42109375</v>
+        <v>2521.3983636364</v>
       </c>
       <c r="O423" t="n">
-        <v>148763.84453125</v>
+        <v>126069.91818182</v>
       </c>
       <c r="P423" t="n">
         <v>3900</v>
       </c>
       <c r="Q423" t="n">
-        <v>230100</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="424">
@@ -18970,22 +18970,22 @@
         <v>0</v>
       </c>
       <c r="L435" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M435" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="N435" t="n">
         <v>2638</v>
       </c>
       <c r="O435" t="n">
-        <v>625206</v>
+        <v>609378</v>
       </c>
       <c r="P435" t="n">
         <v>4500</v>
       </c>
       <c r="Q435" t="n">
-        <v>1066500</v>
+        <v>1039500</v>
       </c>
     </row>
     <row r="436">
@@ -27976,22 +27976,22 @@
         <v>0</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M647" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N647" t="n">
         <v>16974.69</v>
       </c>
       <c r="O647" t="n">
-        <v>1205202.99</v>
+        <v>1171253.61</v>
       </c>
       <c r="P647" t="n">
         <v>26900</v>
       </c>
       <c r="Q647" t="n">
-        <v>1909900</v>
+        <v>1856100</v>
       </c>
     </row>
     <row r="648">
@@ -28366,10 +28366,10 @@
         <v>163</v>
       </c>
       <c r="N656" t="n">
-        <v>1561.0035960591</v>
+        <v>1561.003634439</v>
       </c>
       <c r="O656" t="n">
-        <v>254443.5861576333</v>
+        <v>254443.592413557</v>
       </c>
       <c r="P656" t="n">
         <v>2900</v>
@@ -28744,22 +28744,22 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M665" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N665" t="n">
         <v>7409</v>
       </c>
       <c r="O665" t="n">
-        <v>852035</v>
+        <v>844626</v>
       </c>
       <c r="P665" t="n">
         <v>12600</v>
       </c>
       <c r="Q665" t="n">
-        <v>1449000</v>
+        <v>1436400</v>
       </c>
     </row>
     <row r="666">
@@ -38758,22 +38758,22 @@
         <v>0</v>
       </c>
       <c r="L886" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M886" t="n">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="N886" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O886" t="n">
-        <v>1928401.296111705</v>
+        <v>1923853.179367609</v>
       </c>
       <c r="P886" t="n">
         <v>2300</v>
       </c>
       <c r="Q886" t="n">
-        <v>2925600</v>
+        <v>2918700</v>
       </c>
     </row>
     <row r="887">
@@ -38992,10 +38992,10 @@
         <v>194</v>
       </c>
       <c r="N891" t="n">
-        <v>2079.3834819145</v>
+        <v>2079.3834145441</v>
       </c>
       <c r="O891" t="n">
-        <v>403400.395491413</v>
+        <v>403400.3824215554</v>
       </c>
       <c r="P891" t="n">
         <v>2900</v>
@@ -39536,22 +39536,22 @@
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M903" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N903" t="n">
         <v>12351</v>
       </c>
       <c r="O903" t="n">
-        <v>123510</v>
+        <v>111159</v>
       </c>
       <c r="P903" t="n">
         <v>10900</v>
       </c>
       <c r="Q903" t="n">
-        <v>109000</v>
+        <v>98100</v>
       </c>
     </row>
     <row r="904">
@@ -39672,22 +39672,22 @@
         <v>0</v>
       </c>
       <c r="L906" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M906" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N906" t="n">
-        <v>1906.1790510949</v>
+        <v>1906.1788059701</v>
       </c>
       <c r="O906" t="n">
-        <v>217304.4118248186</v>
+        <v>211585.8474626811</v>
       </c>
       <c r="P906" t="n">
         <v>2900</v>
       </c>
       <c r="Q906" t="n">
-        <v>330600</v>
+        <v>321900</v>
       </c>
     </row>
     <row r="907">
@@ -39718,22 +39718,22 @@
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M907" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N907" t="n">
-        <v>3033.6928395062</v>
+        <v>3033.6906410256</v>
       </c>
       <c r="O907" t="n">
-        <v>448986.5402469176</v>
+        <v>430784.0710256352</v>
       </c>
       <c r="P907" t="n">
         <v>4500</v>
       </c>
       <c r="Q907" t="n">
-        <v>666000</v>
+        <v>639000</v>
       </c>
     </row>
     <row r="908">
@@ -42416,22 +42416,22 @@
         <v>0</v>
       </c>
       <c r="L966" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M966" t="n">
-        <v>841</v>
+        <v>826</v>
       </c>
       <c r="N966" t="n">
-        <v>517.2940518305199</v>
+        <v>517.72052761748</v>
       </c>
       <c r="O966" t="n">
-        <v>435044.2975894673</v>
+        <v>427637.1558120385</v>
       </c>
       <c r="P966" t="n">
         <v>900</v>
       </c>
       <c r="Q966" t="n">
-        <v>756900</v>
+        <v>743400</v>
       </c>
     </row>
     <row r="967">
@@ -42739,10 +42739,10 @@
         <v>13203</v>
       </c>
       <c r="N973" t="n">
-        <v>703.79483731577</v>
+        <v>703.86725350482</v>
       </c>
       <c r="O973" t="n">
-        <v>9292203.237080112</v>
+        <v>9293159.348024139</v>
       </c>
       <c r="P973" t="n">
         <v>900</v>
@@ -44467,22 +44467,22 @@
         <v>0</v>
       </c>
       <c r="L1011" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1011" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N1011" t="n">
         <v>2672.89</v>
       </c>
       <c r="O1011" t="n">
-        <v>157700.51</v>
+        <v>155027.62</v>
       </c>
       <c r="P1011" t="n">
         <v>10200</v>
       </c>
       <c r="Q1011" t="n">
-        <v>601800</v>
+        <v>591600</v>
       </c>
     </row>
     <row r="1012">
@@ -44516,22 +44516,22 @@
         <v>0</v>
       </c>
       <c r="L1012" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1012" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N1012" t="n">
         <v>5430.86</v>
       </c>
       <c r="O1012" t="n">
-        <v>244388.7</v>
+        <v>238957.84</v>
       </c>
       <c r="P1012" t="n">
         <v>13900</v>
       </c>
       <c r="Q1012" t="n">
-        <v>625500</v>
+        <v>611600</v>
       </c>
     </row>
     <row r="1013">
@@ -45310,10 +45310,10 @@
         <v>1068</v>
       </c>
       <c r="N1029" t="n">
-        <v>1783.7988761992</v>
+        <v>1783.7988756856</v>
       </c>
       <c r="O1029" t="n">
-        <v>1905097.199780746</v>
+        <v>1905097.199232221</v>
       </c>
       <c r="P1029" t="n">
         <v>1500</v>
@@ -47004,22 +47004,22 @@
         <v>0</v>
       </c>
       <c r="L1065" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1065" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N1065" t="n">
         <v>10301.17</v>
       </c>
       <c r="O1065" t="n">
-        <v>185421.06</v>
+        <v>175119.89</v>
       </c>
       <c r="P1065" t="n">
         <v>14300</v>
       </c>
       <c r="Q1065" t="n">
-        <v>257400</v>
+        <v>243100</v>
       </c>
     </row>
     <row r="1066">
@@ -47633,10 +47633,10 @@
         <v>13</v>
       </c>
       <c r="N1078" t="n">
-        <v>315.02726865672</v>
+        <v>315.02740121581</v>
       </c>
       <c r="O1078" t="n">
-        <v>4095.35449253736</v>
+        <v>4095.35621580553</v>
       </c>
       <c r="P1078" t="n">
         <v>2200</v>
@@ -51314,22 +51314,22 @@
         <v>0</v>
       </c>
       <c r="L1162" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1162" t="n">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="N1162" t="n">
         <v>6160</v>
       </c>
       <c r="O1162" t="n">
-        <v>1484560</v>
+        <v>1373680</v>
       </c>
       <c r="P1162" t="n">
         <v>7500</v>
       </c>
       <c r="Q1162" t="n">
-        <v>1807500</v>
+        <v>1672500</v>
       </c>
     </row>
     <row r="1163">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -969,22 +969,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N14" t="n">
-        <v>1990.0434548944</v>
+        <v>1990.0434042553</v>
       </c>
       <c r="O14" t="n">
-        <v>290546.3444145824</v>
+        <v>282586.1634042526</v>
       </c>
       <c r="P14" t="n">
         <v>4400</v>
       </c>
       <c r="Q14" t="n">
-        <v>642400</v>
+        <v>624800</v>
       </c>
     </row>
     <row r="15">
@@ -5578,10 +5578,10 @@
         <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>22267.552777778</v>
+        <v>26721.063333333</v>
       </c>
       <c r="O125" t="n">
-        <v>44535.105555556</v>
+        <v>53442.126666666</v>
       </c>
       <c r="P125" t="n">
         <v>46300</v>
@@ -6052,10 +6052,10 @@
         <v>15</v>
       </c>
       <c r="N136" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O136" t="n">
-        <v>2121253.2693069</v>
+        <v>2128277.28675495</v>
       </c>
       <c r="P136" t="n">
         <v>251900</v>
@@ -6094,10 +6094,10 @@
         <v>2</v>
       </c>
       <c r="N137" t="n">
-        <v>200072.20216981</v>
+        <v>201977.65171429</v>
       </c>
       <c r="O137" t="n">
-        <v>400144.40433962</v>
+        <v>403955.30342858</v>
       </c>
       <c r="P137" t="n">
         <v>312000</v>
@@ -6659,10 +6659,10 @@
         <v>79</v>
       </c>
       <c r="N151" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O151" t="n">
-        <v>4871683.059530409</v>
+        <v>4953790.077387644</v>
       </c>
       <c r="P151" t="n">
         <v>98900</v>
@@ -11617,22 +11617,22 @@
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M267" t="n">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="N267" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O267" t="n">
-        <v>1642314.266953093</v>
+        <v>1629402.987518962</v>
       </c>
       <c r="P267" t="n">
         <v>4500</v>
       </c>
       <c r="Q267" t="n">
-        <v>2862000</v>
+        <v>2839500</v>
       </c>
     </row>
     <row r="268">
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="N283" t="n">
-        <v>8214</v>
+        <v>8701.9603960396</v>
       </c>
       <c r="O283" t="n">
-        <v>16428</v>
+        <v>17403.9207920792</v>
       </c>
       <c r="P283" t="n">
         <v>7900</v>
@@ -13517,22 +13517,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M310" t="n">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="N310" t="n">
         <v>1203.38</v>
       </c>
       <c r="O310" t="n">
-        <v>464504.6800000001</v>
+        <v>456081.02</v>
       </c>
       <c r="P310" t="n">
         <v>1900</v>
       </c>
       <c r="Q310" t="n">
-        <v>733400</v>
+        <v>720100</v>
       </c>
     </row>
     <row r="311">
@@ -13916,22 +13916,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M319" t="n">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="N319" t="n">
         <v>5667.94</v>
       </c>
       <c r="O319" t="n">
-        <v>4216947.359999999</v>
+        <v>4199943.54</v>
       </c>
       <c r="P319" t="n">
         <v>9500</v>
       </c>
       <c r="Q319" t="n">
-        <v>7068000</v>
+        <v>7039500</v>
       </c>
     </row>
     <row r="320">
@@ -14008,22 +14008,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M321" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N321" t="n">
         <v>8662</v>
       </c>
       <c r="O321" t="n">
-        <v>173240</v>
+        <v>155916</v>
       </c>
       <c r="P321" t="n">
         <v>14200</v>
       </c>
       <c r="Q321" t="n">
-        <v>284000</v>
+        <v>255600</v>
       </c>
     </row>
     <row r="322">
@@ -16435,22 +16435,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M377" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N377" t="n">
         <v>4648.6</v>
       </c>
       <c r="O377" t="n">
-        <v>1022692</v>
+        <v>1004097.6</v>
       </c>
       <c r="P377" t="n">
         <v>8900</v>
       </c>
       <c r="Q377" t="n">
-        <v>1958000</v>
+        <v>1922400</v>
       </c>
     </row>
     <row r="378">
@@ -18148,22 +18148,22 @@
         <v>0</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M416" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="N416" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O416" t="n">
-        <v>303351.907632159</v>
+        <v>293566.36348593</v>
       </c>
       <c r="P416" t="n">
         <v>2500</v>
       </c>
       <c r="Q416" t="n">
-        <v>465000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="417">
@@ -18332,22 +18332,22 @@
         <v>0</v>
       </c>
       <c r="L420" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M420" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N420" t="n">
-        <v>2403.516914488</v>
+        <v>2403.5169237057</v>
       </c>
       <c r="O420" t="n">
-        <v>903722.359847488</v>
+        <v>898915.3294659317</v>
       </c>
       <c r="P420" t="n">
         <v>3500</v>
       </c>
       <c r="Q420" t="n">
-        <v>1316000</v>
+        <v>1309000</v>
       </c>
     </row>
     <row r="421">
@@ -18422,22 +18422,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M422" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N422" t="n">
-        <v>2521.3785714286</v>
+        <v>2521.3667391304</v>
       </c>
       <c r="O422" t="n">
-        <v>110940.6571428584</v>
+        <v>103376.0363043464</v>
       </c>
       <c r="P422" t="n">
         <v>3900</v>
       </c>
       <c r="Q422" t="n">
-        <v>171600</v>
+        <v>159900</v>
       </c>
     </row>
     <row r="423">
@@ -25560,22 +25560,22 @@
         <v>0</v>
       </c>
       <c r="L590" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M590" t="n">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="N590" t="n">
-        <v>4814.2679274047</v>
+        <v>4814.2679269747</v>
       </c>
       <c r="O590" t="n">
-        <v>4390612.349793086</v>
+        <v>4371355.277693028</v>
       </c>
       <c r="P590" t="n">
         <v>9900</v>
       </c>
       <c r="Q590" t="n">
-        <v>9028800</v>
+        <v>8989200</v>
       </c>
     </row>
     <row r="591">
@@ -26528,22 +26528,22 @@
         <v>0</v>
       </c>
       <c r="L613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M613" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N613" t="n">
         <v>1647</v>
       </c>
       <c r="O613" t="n">
-        <v>459513</v>
+        <v>457866</v>
       </c>
       <c r="P613" t="n">
         <v>2900</v>
       </c>
       <c r="Q613" t="n">
-        <v>809100</v>
+        <v>806200</v>
       </c>
     </row>
     <row r="614">
@@ -27940,10 +27940,10 @@
         <v>69</v>
       </c>
       <c r="N646" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O646" t="n">
-        <v>1171253.61</v>
+        <v>1178439.214969326</v>
       </c>
       <c r="P646" t="n">
         <v>26900</v>
@@ -29251,10 +29251,10 @@
         <v>39</v>
       </c>
       <c r="N677" t="n">
-        <v>9627.34</v>
+        <v>11147.446315789</v>
       </c>
       <c r="O677" t="n">
-        <v>375466.26</v>
+        <v>434750.406315771</v>
       </c>
       <c r="P677" t="n">
         <v>15900</v>
@@ -30480,10 +30480,10 @@
         <v>1</v>
       </c>
       <c r="N706" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="O706" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="P706" t="n">
         <v>13900</v>
@@ -38624,22 +38624,22 @@
         <v>0</v>
       </c>
       <c r="L883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M883" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N883" t="n">
         <v>64612</v>
       </c>
       <c r="O883" t="n">
-        <v>1679912</v>
+        <v>1615300</v>
       </c>
       <c r="P883" t="n">
         <v>103900</v>
       </c>
       <c r="Q883" t="n">
-        <v>2701400</v>
+        <v>2597500</v>
       </c>
     </row>
     <row r="884">
@@ -38676,10 +38676,10 @@
         <v>1267</v>
       </c>
       <c r="N884" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O884" t="n">
-        <v>1920821.098337889</v>
+        <v>1920821.098017085</v>
       </c>
       <c r="P884" t="n">
         <v>2300</v>
@@ -39630,22 +39630,22 @@
         <v>0</v>
       </c>
       <c r="L905" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M905" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N905" t="n">
-        <v>3033.6882666667</v>
+        <v>3033.6856944444</v>
       </c>
       <c r="O905" t="n">
-        <v>412581.6042666712</v>
+        <v>394379.140277772</v>
       </c>
       <c r="P905" t="n">
         <v>4500</v>
       </c>
       <c r="Q905" t="n">
-        <v>612000</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="906">
@@ -39676,22 +39676,22 @@
         <v>0</v>
       </c>
       <c r="L906" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M906" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="N906" t="n">
-        <v>1668.6387301587</v>
+        <v>1668.64</v>
       </c>
       <c r="O906" t="n">
-        <v>328721.8298412639</v>
+        <v>315372.96</v>
       </c>
       <c r="P906" t="n">
         <v>2500</v>
       </c>
       <c r="Q906" t="n">
-        <v>492500</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="907">
@@ -40225,22 +40225,22 @@
         <v>0</v>
       </c>
       <c r="L918" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M918" t="n">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N918" t="n">
         <v>11690</v>
       </c>
       <c r="O918" t="n">
-        <v>8416800</v>
+        <v>8405110</v>
       </c>
       <c r="P918" t="n">
         <v>18900</v>
       </c>
       <c r="Q918" t="n">
-        <v>13608000</v>
+        <v>13589100</v>
       </c>
     </row>
     <row r="919">
@@ -42334,10 +42334,10 @@
         <v>816</v>
       </c>
       <c r="N964" t="n">
-        <v>517.29416017244</v>
+        <v>517.81142476254</v>
       </c>
       <c r="O964" t="n">
-        <v>422112.034700711</v>
+        <v>422534.1226062326</v>
       </c>
       <c r="P964" t="n">
         <v>900</v>
@@ -42645,22 +42645,22 @@
         <v>0</v>
       </c>
       <c r="L971" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M971" t="n">
-        <v>13197</v>
+        <v>13185</v>
       </c>
       <c r="N971" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O971" t="n">
-        <v>9287980.354837965</v>
+        <v>9279534.806351718</v>
       </c>
       <c r="P971" t="n">
         <v>900</v>
       </c>
       <c r="Q971" t="n">
-        <v>11877300</v>
+        <v>11866500</v>
       </c>
     </row>
     <row r="972">
@@ -48773,22 +48773,22 @@
         <v>0</v>
       </c>
       <c r="L1105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1105" t="n">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="N1105" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1105" t="n">
-        <v>1644844.86</v>
+        <v>1642491.72</v>
       </c>
       <c r="P1105" t="n">
         <v>1900</v>
       </c>
       <c r="Q1105" t="n">
-        <v>2656200</v>
+        <v>2652400</v>
       </c>
     </row>
     <row r="1106">
@@ -48867,10 +48867,10 @@
         <v>40</v>
       </c>
       <c r="N1107" t="n">
-        <v>3181.9</v>
+        <v>3248.0517671518</v>
       </c>
       <c r="O1107" t="n">
-        <v>127276</v>
+        <v>129922.070686072</v>
       </c>
       <c r="P1107" t="n">
         <v>5100</v>
@@ -53223,10 +53223,10 @@
         <v>595</v>
       </c>
       <c r="N1203" t="n">
-        <v>4171.6685988024</v>
+        <v>4171.6685954382</v>
       </c>
       <c r="O1203" t="n">
-        <v>2482142.816287428</v>
+        <v>2482142.814285729</v>
       </c>
       <c r="P1203" t="n">
         <v>5000</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -895,10 +895,10 @@
         <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="O12" t="n">
-        <v>76074.9692307696</v>
+        <v>76074.9703406826</v>
       </c>
       <c r="P12" t="n">
         <v>2600</v>
@@ -1917,10 +1917,10 @@
         <v>49</v>
       </c>
       <c r="N37" t="n">
-        <v>15970.739066667</v>
+        <v>15970.739014085</v>
       </c>
       <c r="O37" t="n">
-        <v>782566.214266683</v>
+        <v>782566.211690165</v>
       </c>
       <c r="P37" t="n">
         <v>26900</v>
@@ -4854,10 +4854,10 @@
         <v>5</v>
       </c>
       <c r="N107" t="n">
-        <v>16486.407586207</v>
+        <v>16486.407256637</v>
       </c>
       <c r="O107" t="n">
-        <v>82432.037931035</v>
+        <v>82432.03628318501</v>
       </c>
       <c r="P107" t="n">
         <v>30500</v>
@@ -9835,10 +9835,10 @@
         <v>850</v>
       </c>
       <c r="N225" t="n">
-        <v>1098.0633365079</v>
+        <v>1098.0633810433</v>
       </c>
       <c r="O225" t="n">
-        <v>933353.836031715</v>
+        <v>933353.873886805</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
@@ -12094,10 +12094,10 @@
         <v>2802</v>
       </c>
       <c r="N278" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O278" t="n">
-        <v>8851128.063218173</v>
+        <v>8851128.065078141</v>
       </c>
       <c r="P278" t="n">
         <v>5600</v>
@@ -12715,22 +12715,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M292" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N292" t="n">
         <v>7507.39</v>
       </c>
       <c r="O292" t="n">
-        <v>2117083.98</v>
+        <v>2109576.59</v>
       </c>
       <c r="P292" t="n">
         <v>13500</v>
       </c>
       <c r="Q292" t="n">
-        <v>3807000</v>
+        <v>3793500</v>
       </c>
     </row>
     <row r="293">
@@ -13039,10 +13039,10 @@
         <v>468</v>
       </c>
       <c r="N299" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O299" t="n">
-        <v>1776392.28356368</v>
+        <v>1776392.283564335</v>
       </c>
       <c r="P299" t="n">
         <v>6200</v>
@@ -13517,22 +13517,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M310" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N310" t="n">
         <v>1203.38</v>
       </c>
       <c r="O310" t="n">
-        <v>454877.64</v>
+        <v>450064.1200000001</v>
       </c>
       <c r="P310" t="n">
         <v>1900</v>
       </c>
       <c r="Q310" t="n">
-        <v>718200</v>
+        <v>710600</v>
       </c>
     </row>
     <row r="311">
@@ -13563,22 +13563,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M311" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N311" t="n">
         <v>3472</v>
       </c>
       <c r="O311" t="n">
-        <v>1159648</v>
+        <v>1156176</v>
       </c>
       <c r="P311" t="n">
         <v>4800</v>
       </c>
       <c r="Q311" t="n">
-        <v>1603200</v>
+        <v>1598400</v>
       </c>
     </row>
     <row r="312">
@@ -13824,22 +13824,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M317" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N317" t="n">
         <v>1267</v>
       </c>
       <c r="O317" t="n">
-        <v>57015</v>
+        <v>55748</v>
       </c>
       <c r="P317" t="n">
         <v>1900</v>
       </c>
       <c r="Q317" t="n">
-        <v>85500</v>
+        <v>83600</v>
       </c>
     </row>
     <row r="318">
@@ -15786,22 +15786,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N362" t="n">
-        <v>1592.5654585153</v>
+        <v>1592.5654545455</v>
       </c>
       <c r="O362" t="n">
-        <v>506435.8158078654</v>
+        <v>504843.2490909235</v>
       </c>
       <c r="P362" t="n">
         <v>3900</v>
       </c>
       <c r="Q362" t="n">
-        <v>1240200</v>
+        <v>1236300</v>
       </c>
     </row>
     <row r="363">
@@ -16476,22 +16476,22 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M378" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="N378" t="n">
         <v>1312.43</v>
       </c>
       <c r="O378" t="n">
-        <v>1342615.89</v>
+        <v>1341303.46</v>
       </c>
       <c r="P378" t="n">
         <v>2300</v>
       </c>
       <c r="Q378" t="n">
-        <v>2352900</v>
+        <v>2350600</v>
       </c>
     </row>
     <row r="379">
@@ -18202,10 +18202,10 @@
         <v>319</v>
       </c>
       <c r="N417" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O417" t="n">
-        <v>494512.0272261488</v>
+        <v>494512.0323344872</v>
       </c>
       <c r="P417" t="n">
         <v>2500</v>
@@ -18242,22 +18242,22 @@
         <v>0</v>
       </c>
       <c r="L418" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M418" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="N418" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="O418" t="n">
-        <v>78969.28199999999</v>
+        <v>55278.46531915051</v>
       </c>
       <c r="P418" t="n">
         <v>2900</v>
       </c>
       <c r="Q418" t="n">
-        <v>145000</v>
+        <v>101500</v>
       </c>
     </row>
     <row r="419">
@@ -18288,22 +18288,22 @@
         <v>0</v>
       </c>
       <c r="L419" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M419" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="N419" t="n">
-        <v>2403.5172431982</v>
+        <v>2403.5172815804</v>
       </c>
       <c r="O419" t="n">
-        <v>877283.793767343</v>
+        <v>870073.2559321048</v>
       </c>
       <c r="P419" t="n">
         <v>3500</v>
       </c>
       <c r="Q419" t="n">
-        <v>1277500</v>
+        <v>1267000</v>
       </c>
     </row>
     <row r="420">
@@ -18378,22 +18378,22 @@
         <v>0</v>
       </c>
       <c r="L421" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M421" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N421" t="n">
-        <v>2521.33775</v>
+        <v>2521.3197297297</v>
       </c>
       <c r="O421" t="n">
-        <v>88246.82125000001</v>
+        <v>80682.23135135041</v>
       </c>
       <c r="P421" t="n">
         <v>3900</v>
       </c>
       <c r="Q421" t="n">
-        <v>136500</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="422">
@@ -18419,22 +18419,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M422" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N422" t="n">
-        <v>1232.8060309278</v>
+        <v>1232.8059585492</v>
       </c>
       <c r="O422" t="n">
-        <v>61640.30154639</v>
+        <v>60407.49196891081</v>
       </c>
       <c r="P422" t="n">
         <v>2400</v>
       </c>
       <c r="Q422" t="n">
-        <v>120000</v>
+        <v>117600</v>
       </c>
     </row>
     <row r="423">
@@ -22788,10 +22788,10 @@
         <v>197</v>
       </c>
       <c r="N524" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O524" t="n">
-        <v>399885.1947385581</v>
+        <v>399885.196055641</v>
       </c>
       <c r="P524" t="n">
         <v>3600</v>
@@ -24584,10 +24584,10 @@
         <v>179</v>
       </c>
       <c r="N567" t="n">
-        <v>3731.024440678</v>
+        <v>3731.0244863014</v>
       </c>
       <c r="O567" t="n">
-        <v>667853.374881362</v>
+        <v>667853.3830479506</v>
       </c>
       <c r="P567" t="n">
         <v>5200</v>
@@ -25788,10 +25788,10 @@
         <v>75</v>
       </c>
       <c r="N595" t="n">
-        <v>12005.15982684</v>
+        <v>12005.159823789</v>
       </c>
       <c r="O595" t="n">
-        <v>900386.9870129999</v>
+        <v>900386.9867841749</v>
       </c>
       <c r="P595" t="n">
         <v>19500</v>
@@ -35462,10 +35462,10 @@
         <v>15</v>
       </c>
       <c r="N814" t="n">
-        <v>4907.8225450902</v>
+        <v>4907.8225656566</v>
       </c>
       <c r="O814" t="n">
-        <v>73617.33817635301</v>
+        <v>73617.33848484899</v>
       </c>
       <c r="P814" t="n">
         <v>8200</v>
@@ -36003,22 +36003,22 @@
         <v>0</v>
       </c>
       <c r="L826" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M826" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N826" t="n">
         <v>16469</v>
       </c>
       <c r="O826" t="n">
-        <v>2272722</v>
+        <v>2256253</v>
       </c>
       <c r="P826" t="n">
         <v>26900</v>
       </c>
       <c r="Q826" t="n">
-        <v>3712200</v>
+        <v>3685300</v>
       </c>
     </row>
     <row r="827">
@@ -38580,22 +38580,22 @@
         <v>0</v>
       </c>
       <c r="L882" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M882" t="n">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="N882" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O882" t="n">
-        <v>1920821.098017085</v>
+        <v>1914756.942371418</v>
       </c>
       <c r="P882" t="n">
         <v>2300</v>
       </c>
       <c r="Q882" t="n">
-        <v>2914100</v>
+        <v>2904900</v>
       </c>
     </row>
     <row r="883">
@@ -38854,22 +38854,22 @@
         <v>0</v>
       </c>
       <c r="L888" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M888" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N888" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O888" t="n">
-        <v>501238.5840198956</v>
+        <v>497632.555164996</v>
       </c>
       <c r="P888" t="n">
         <v>2500</v>
       </c>
       <c r="Q888" t="n">
-        <v>695000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="889">
@@ -38992,22 +38992,22 @@
         <v>0</v>
       </c>
       <c r="L891" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M891" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N891" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O891" t="n">
-        <v>464674.6027039192</v>
+        <v>456450.2645076762</v>
       </c>
       <c r="P891" t="n">
         <v>2900</v>
       </c>
       <c r="Q891" t="n">
-        <v>655400</v>
+        <v>643800</v>
       </c>
     </row>
     <row r="892">
@@ -39448,22 +39448,22 @@
         <v>0</v>
       </c>
       <c r="L901" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M901" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N901" t="n">
-        <v>2311.894010989</v>
+        <v>2311.8935</v>
       </c>
       <c r="O901" t="n">
-        <v>420764.709999998</v>
+        <v>416140.83</v>
       </c>
       <c r="P901" t="n">
         <v>3500</v>
       </c>
       <c r="Q901" t="n">
-        <v>637000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="902">
@@ -39638,10 +39638,10 @@
         <v>123</v>
       </c>
       <c r="N905" t="n">
-        <v>2546.982132964</v>
+        <v>2546.9817919075</v>
       </c>
       <c r="O905" t="n">
-        <v>313278.802354572</v>
+        <v>313278.7604046225</v>
       </c>
       <c r="P905" t="n">
         <v>3900</v>
@@ -42244,10 +42244,10 @@
         <v>800</v>
       </c>
       <c r="N962" t="n">
-        <v>517.29429288703</v>
+        <v>517.29430006698</v>
       </c>
       <c r="O962" t="n">
-        <v>413835.434309624</v>
+        <v>413835.440053584</v>
       </c>
       <c r="P962" t="n">
         <v>900</v>
@@ -45126,22 +45126,22 @@
         <v>0</v>
       </c>
       <c r="L1025" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1025" t="n">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="N1025" t="n">
-        <v>1783.7988736264</v>
+        <v>1783.7988731104</v>
       </c>
       <c r="O1025" t="n">
-        <v>1905097.197032995</v>
+        <v>1903313.397608797</v>
       </c>
       <c r="P1025" t="n">
         <v>1500</v>
       </c>
       <c r="Q1025" t="n">
-        <v>1602000</v>
+        <v>1600500</v>
       </c>
     </row>
     <row r="1026">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1340,10 +1340,10 @@
         <v>473</v>
       </c>
       <c r="N23" t="n">
-        <v>4072</v>
+        <v>4088.8962655602</v>
       </c>
       <c r="O23" t="n">
-        <v>1926056</v>
+        <v>1934047.933609975</v>
       </c>
       <c r="P23" t="n">
         <v>7500</v>
@@ -4854,10 +4854,10 @@
         <v>5</v>
       </c>
       <c r="N107" t="n">
-        <v>16486.407256637</v>
+        <v>16486.407142857</v>
       </c>
       <c r="O107" t="n">
-        <v>82432.03628318501</v>
+        <v>82432.035714285</v>
       </c>
       <c r="P107" t="n">
         <v>30500</v>
@@ -9365,22 +9365,22 @@
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N214" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O214" t="n">
-        <v>1007211.273744354</v>
+        <v>1002273.963604214</v>
       </c>
       <c r="P214" t="n">
         <v>7500</v>
       </c>
       <c r="Q214" t="n">
-        <v>1530000</v>
+        <v>1522500</v>
       </c>
     </row>
     <row r="215">
@@ -11057,10 +11057,10 @@
         <v>297</v>
       </c>
       <c r="N254" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="O254" t="n">
-        <v>4037224.95</v>
+        <v>4047024.039684417</v>
       </c>
       <c r="P254" t="n">
         <v>25500</v>
@@ -11617,22 +11617,22 @@
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M267" t="n">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="N267" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O267" t="n">
-        <v>1577757.836119269</v>
+        <v>1572593.321517809</v>
       </c>
       <c r="P267" t="n">
         <v>4500</v>
       </c>
       <c r="Q267" t="n">
-        <v>2749500</v>
+        <v>2740500</v>
       </c>
     </row>
     <row r="268">
@@ -11669,10 +11669,10 @@
         <v>1377</v>
       </c>
       <c r="N268" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O268" t="n">
-        <v>7183665.74278478</v>
+        <v>7187947.46875285</v>
       </c>
       <c r="P268" t="n">
         <v>8500</v>
@@ -12715,22 +12715,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M292" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N292" t="n">
         <v>7507.39</v>
       </c>
       <c r="O292" t="n">
-        <v>2109576.59</v>
+        <v>2094561.81</v>
       </c>
       <c r="P292" t="n">
         <v>13500</v>
       </c>
       <c r="Q292" t="n">
-        <v>3793500</v>
+        <v>3766500</v>
       </c>
     </row>
     <row r="293">
@@ -12764,22 +12764,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M293" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N293" t="n">
         <v>9664</v>
       </c>
       <c r="O293" t="n">
-        <v>280256</v>
+        <v>260928</v>
       </c>
       <c r="P293" t="n">
         <v>15900</v>
       </c>
       <c r="Q293" t="n">
-        <v>461100</v>
+        <v>429300</v>
       </c>
     </row>
     <row r="294">
@@ -12813,22 +12813,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N294" t="n">
         <v>8796</v>
       </c>
       <c r="O294" t="n">
-        <v>2858700</v>
+        <v>2849904</v>
       </c>
       <c r="P294" t="n">
         <v>14900</v>
       </c>
       <c r="Q294" t="n">
-        <v>4842500</v>
+        <v>4827600</v>
       </c>
     </row>
     <row r="295">
@@ -12911,10 +12911,10 @@
         <v>654</v>
       </c>
       <c r="N296" t="n">
-        <v>6507</v>
+        <v>6513.4596293845</v>
       </c>
       <c r="O296" t="n">
-        <v>4255578</v>
+        <v>4259802.597617463</v>
       </c>
       <c r="P296" t="n">
         <v>9900</v>
@@ -13161,22 +13161,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M302" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N302" t="n">
         <v>7939.23</v>
       </c>
       <c r="O302" t="n">
-        <v>1182945.27</v>
+        <v>1167066.81</v>
       </c>
       <c r="P302" t="n">
         <v>14900</v>
       </c>
       <c r="Q302" t="n">
-        <v>2220100</v>
+        <v>2190300</v>
       </c>
     </row>
     <row r="303">
@@ -13517,22 +13517,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M310" t="n">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="N310" t="n">
         <v>1203.38</v>
       </c>
       <c r="O310" t="n">
-        <v>398318.78</v>
+        <v>389895.1200000001</v>
       </c>
       <c r="P310" t="n">
         <v>1900</v>
       </c>
       <c r="Q310" t="n">
-        <v>628900</v>
+        <v>615600</v>
       </c>
     </row>
     <row r="311">
@@ -13742,22 +13742,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M315" t="n">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N315" t="n">
         <v>2331</v>
       </c>
       <c r="O315" t="n">
-        <v>969696</v>
+        <v>967365</v>
       </c>
       <c r="P315" t="n">
         <v>3500</v>
       </c>
       <c r="Q315" t="n">
-        <v>1456000</v>
+        <v>1452500</v>
       </c>
     </row>
     <row r="316">
@@ -13876,10 +13876,10 @@
         <v>40</v>
       </c>
       <c r="N318" t="n">
-        <v>7041</v>
+        <v>7062.9802289282</v>
       </c>
       <c r="O318" t="n">
-        <v>281640</v>
+        <v>282519.209157128</v>
       </c>
       <c r="P318" t="n">
         <v>11500</v>
@@ -13968,10 +13968,10 @@
         <v>1</v>
       </c>
       <c r="N320" t="n">
-        <v>8012</v>
+        <v>8051.1465798046</v>
       </c>
       <c r="O320" t="n">
-        <v>8012</v>
+        <v>8051.1465798046</v>
       </c>
       <c r="P320" t="n">
         <v>13200</v>
@@ -14014,10 +14014,10 @@
         <v>18</v>
       </c>
       <c r="N321" t="n">
-        <v>8662</v>
+        <v>8680.102403343801</v>
       </c>
       <c r="O321" t="n">
-        <v>155916</v>
+        <v>156241.8432601884</v>
       </c>
       <c r="P321" t="n">
         <v>14200</v>
@@ -14227,10 +14227,10 @@
         <v>353</v>
       </c>
       <c r="N326" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O326" t="n">
-        <v>1268771.362881602</v>
+        <v>1268771.361156315</v>
       </c>
       <c r="P326" t="n">
         <v>6500</v>
@@ -14537,10 +14537,10 @@
         <v>283</v>
       </c>
       <c r="N333" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O333" t="n">
-        <v>4194733.208278437</v>
+        <v>4199861.243985465</v>
       </c>
       <c r="P333" t="n">
         <v>24900</v>
@@ -15219,10 +15219,10 @@
         <v>2520</v>
       </c>
       <c r="N349" t="n">
-        <v>3472.2761671707</v>
+        <v>3490.9933434692</v>
       </c>
       <c r="O349" t="n">
-        <v>8750135.941270163</v>
+        <v>8797303.225542385</v>
       </c>
       <c r="P349" t="n">
         <v>5900</v>
@@ -15786,22 +15786,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N362" t="n">
-        <v>1592.5653777778</v>
+        <v>1592.5653736655</v>
       </c>
       <c r="O362" t="n">
-        <v>496880.3978666736</v>
+        <v>495287.8312099705</v>
       </c>
       <c r="P362" t="n">
         <v>3900</v>
       </c>
       <c r="Q362" t="n">
-        <v>1216800</v>
+        <v>1212900</v>
       </c>
     </row>
     <row r="363">
@@ -16348,10 +16348,10 @@
         <v>358</v>
       </c>
       <c r="N375" t="n">
-        <v>6242.93</v>
+        <v>6260.7161253561</v>
       </c>
       <c r="O375" t="n">
-        <v>2234968.94</v>
+        <v>2241336.372877484</v>
       </c>
       <c r="P375" t="n">
         <v>10400</v>
@@ -17933,10 +17933,10 @@
         <v>1</v>
       </c>
       <c r="N411" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O411" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="P411" t="n">
         <v>15900</v>
@@ -18110,10 +18110,10 @@
         <v>137</v>
       </c>
       <c r="N415" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O415" t="n">
-        <v>223436.6318707839</v>
+        <v>223436.6330368731</v>
       </c>
       <c r="P415" t="n">
         <v>2500</v>
@@ -18196,22 +18196,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M417" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N417" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O417" t="n">
-        <v>412351.7398614418</v>
+        <v>409251.3533057136</v>
       </c>
       <c r="P417" t="n">
         <v>2500</v>
       </c>
       <c r="Q417" t="n">
-        <v>665000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="418">
@@ -18288,22 +18288,22 @@
         <v>0</v>
       </c>
       <c r="L419" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M419" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="N419" t="n">
-        <v>2403.5178067661</v>
+        <v>2403.5178733813</v>
       </c>
       <c r="O419" t="n">
-        <v>764318.6625516198</v>
+        <v>754704.6122417282</v>
       </c>
       <c r="P419" t="n">
         <v>3500</v>
       </c>
       <c r="Q419" t="n">
-        <v>1113000</v>
+        <v>1099000</v>
       </c>
     </row>
     <row r="420">
@@ -18501,22 +18501,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N424" t="n">
         <v>11507.72</v>
       </c>
       <c r="O424" t="n">
-        <v>184123.52</v>
+        <v>172615.8</v>
       </c>
       <c r="P424" t="n">
         <v>25800</v>
       </c>
       <c r="Q424" t="n">
-        <v>412800</v>
+        <v>387000</v>
       </c>
     </row>
     <row r="425">
@@ -22788,10 +22788,10 @@
         <v>197</v>
       </c>
       <c r="N524" t="n">
-        <v>2029.8740983607</v>
+        <v>2029.8741050903</v>
       </c>
       <c r="O524" t="n">
-        <v>399885.1973770579</v>
+        <v>399885.1987027891</v>
       </c>
       <c r="P524" t="n">
         <v>3600</v>
@@ -23948,22 +23948,22 @@
         <v>0</v>
       </c>
       <c r="L552" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N552" t="n">
         <v>14060.64</v>
       </c>
       <c r="O552" t="n">
-        <v>28121.28</v>
+        <v>14060.64</v>
       </c>
       <c r="P552" t="n">
         <v>22900</v>
       </c>
       <c r="Q552" t="n">
-        <v>45800</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="553">
@@ -25522,10 +25522,10 @@
         <v>908</v>
       </c>
       <c r="N589" t="n">
-        <v>4814.2679269747</v>
+        <v>4817.516083662</v>
       </c>
       <c r="O589" t="n">
-        <v>4371355.277693028</v>
+        <v>4374304.603965096</v>
       </c>
       <c r="P589" t="n">
         <v>9900</v>
@@ -25696,10 +25696,10 @@
         <v>86</v>
       </c>
       <c r="N593" t="n">
-        <v>11562.038418079</v>
+        <v>11660.859259259</v>
       </c>
       <c r="O593" t="n">
-        <v>994335.3039547941</v>
+        <v>1002833.896296274</v>
       </c>
       <c r="P593" t="n">
         <v>18500</v>
@@ -25742,10 +25742,10 @@
         <v>2</v>
       </c>
       <c r="N594" t="n">
-        <v>13513.643445378</v>
+        <v>13744.645897436</v>
       </c>
       <c r="O594" t="n">
-        <v>27027.286890756</v>
+        <v>27489.291794872</v>
       </c>
       <c r="P594" t="n">
         <v>21900</v>
@@ -25951,22 +25951,22 @@
         <v>0</v>
       </c>
       <c r="L599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M599" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N599" t="n">
         <v>2856</v>
       </c>
       <c r="O599" t="n">
-        <v>297024</v>
+        <v>294168</v>
       </c>
       <c r="P599" t="n">
         <v>2400</v>
       </c>
       <c r="Q599" t="n">
-        <v>249600</v>
+        <v>247200</v>
       </c>
     </row>
     <row r="600">
@@ -27890,22 +27890,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M645" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N645" t="n">
         <v>16974.69</v>
       </c>
       <c r="O645" t="n">
-        <v>1154278.92</v>
+        <v>1137304.23</v>
       </c>
       <c r="P645" t="n">
         <v>26900</v>
       </c>
       <c r="Q645" t="n">
-        <v>1829200</v>
+        <v>1802300</v>
       </c>
     </row>
     <row r="646">
@@ -28280,10 +28280,10 @@
         <v>152</v>
       </c>
       <c r="N654" t="n">
-        <v>1561.0038892883</v>
+        <v>1561.0040101523</v>
       </c>
       <c r="O654" t="n">
-        <v>237272.5911718216</v>
+        <v>237272.6095431496</v>
       </c>
       <c r="P654" t="n">
         <v>2900</v>
@@ -28997,10 +28997,10 @@
         <v>165</v>
       </c>
       <c r="N671" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O671" t="n">
-        <v>1315041.777944565</v>
+        <v>1318085.856134256</v>
       </c>
       <c r="P671" t="n">
         <v>12900</v>
@@ -29207,10 +29207,10 @@
         <v>39</v>
       </c>
       <c r="N676" t="n">
-        <v>9627.34</v>
+        <v>9794.2880924855</v>
       </c>
       <c r="O676" t="n">
-        <v>375466.26</v>
+        <v>381977.2356069345</v>
       </c>
       <c r="P676" t="n">
         <v>15900</v>
@@ -32185,10 +32185,10 @@
         <v>43</v>
       </c>
       <c r="N743" t="n">
-        <v>25749.15</v>
+        <v>24523</v>
       </c>
       <c r="O743" t="n">
-        <v>1107213.45</v>
+        <v>1054489</v>
       </c>
       <c r="P743" t="n">
         <v>41900</v>
@@ -32277,10 +32277,10 @@
         <v>41</v>
       </c>
       <c r="N745" t="n">
-        <v>22739</v>
+        <v>22855.411262799</v>
       </c>
       <c r="O745" t="n">
-        <v>932299</v>
+        <v>937071.861774759</v>
       </c>
       <c r="P745" t="n">
         <v>36900</v>
@@ -33895,10 +33895,10 @@
         <v>62</v>
       </c>
       <c r="N780" t="n">
-        <v>13687</v>
+        <v>13795.340369393</v>
       </c>
       <c r="O780" t="n">
-        <v>848594</v>
+        <v>855311.102902366</v>
       </c>
       <c r="P780" t="n">
         <v>21900</v>
@@ -34309,10 +34309,10 @@
         <v>45</v>
       </c>
       <c r="N789" t="n">
-        <v>8858.16</v>
+        <v>8872.673642818099</v>
       </c>
       <c r="O789" t="n">
-        <v>398617.2</v>
+        <v>399270.3139268145</v>
       </c>
       <c r="P789" t="n">
         <v>15500</v>
@@ -35738,10 +35738,10 @@
         <v>6</v>
       </c>
       <c r="N820" t="n">
-        <v>3903.7390742358</v>
+        <v>3903.7391243433</v>
       </c>
       <c r="O820" t="n">
-        <v>23422.4344454148</v>
+        <v>23422.4347460598</v>
       </c>
       <c r="P820" t="n">
         <v>7500</v>
@@ -35871,10 +35871,10 @@
         <v>34</v>
       </c>
       <c r="N823" t="n">
-        <v>33000</v>
+        <v>33980.198019802</v>
       </c>
       <c r="O823" t="n">
-        <v>1122000</v>
+        <v>1155326.732673268</v>
       </c>
       <c r="P823" t="n">
         <v>52900</v>
@@ -36239,10 +36239,10 @@
         <v>10</v>
       </c>
       <c r="N831" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O831" t="n">
-        <v>68492</v>
+        <v>68557.04463437799</v>
       </c>
       <c r="P831" t="n">
         <v>11500</v>
@@ -38586,10 +38586,10 @@
         <v>1242</v>
       </c>
       <c r="N882" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O882" t="n">
-        <v>1882920.123073264</v>
+        <v>1882920.121962667</v>
       </c>
       <c r="P882" t="n">
         <v>2300</v>
@@ -38676,10 +38676,10 @@
         <v>246</v>
       </c>
       <c r="N884" t="n">
-        <v>2458.5126157653</v>
+        <v>2500.9617517986</v>
       </c>
       <c r="O884" t="n">
-        <v>604794.1034782637</v>
+        <v>615236.5909424556</v>
       </c>
       <c r="P884" t="n">
         <v>3500</v>
@@ -38768,10 +38768,10 @@
         <v>78</v>
       </c>
       <c r="N886" t="n">
-        <v>1771.089398827</v>
+        <v>1835.6884042553</v>
       </c>
       <c r="O886" t="n">
-        <v>138144.973108506</v>
+        <v>143183.6955319134</v>
       </c>
       <c r="P886" t="n">
         <v>2500</v>
@@ -38814,10 +38814,10 @@
         <v>167</v>
       </c>
       <c r="N887" t="n">
-        <v>2079.3833258511</v>
+        <v>2079.3833208536</v>
       </c>
       <c r="O887" t="n">
-        <v>347257.0154171337</v>
+        <v>347257.0145825511</v>
       </c>
       <c r="P887" t="n">
         <v>2900</v>
@@ -38860,10 +38860,10 @@
         <v>247</v>
       </c>
       <c r="N888" t="n">
-        <v>1803.0166107644</v>
+        <v>1837.4143839428</v>
       </c>
       <c r="O888" t="n">
-        <v>445345.1028588068</v>
+        <v>453841.3528338716</v>
       </c>
       <c r="P888" t="n">
         <v>2500</v>
@@ -38906,10 +38906,10 @@
         <v>85</v>
       </c>
       <c r="N889" t="n">
-        <v>3306.5944272446</v>
+        <v>3645.1535836177</v>
       </c>
       <c r="O889" t="n">
-        <v>281060.526315791</v>
+        <v>309838.0546075045</v>
       </c>
       <c r="P889" t="n">
         <v>4900</v>
@@ -38998,10 +38998,10 @@
         <v>218</v>
       </c>
       <c r="N891" t="n">
-        <v>2056.0822493428</v>
+        <v>2093.8229560229</v>
       </c>
       <c r="O891" t="n">
-        <v>448225.9303567304</v>
+        <v>456453.4044129922</v>
       </c>
       <c r="P891" t="n">
         <v>2900</v>
@@ -39090,10 +39090,10 @@
         <v>176</v>
       </c>
       <c r="N893" t="n">
-        <v>1655.9295385779</v>
+        <v>1751.31108</v>
       </c>
       <c r="O893" t="n">
-        <v>291443.5987897104</v>
+        <v>308230.75008</v>
       </c>
       <c r="P893" t="n">
         <v>2500</v>
@@ -39323,10 +39323,10 @@
         <v>386</v>
       </c>
       <c r="N898" t="n">
-        <v>1592.2824611033</v>
+        <v>1592.2825142045</v>
       </c>
       <c r="O898" t="n">
-        <v>614621.0299858738</v>
+        <v>614621.050482937</v>
       </c>
       <c r="P898" t="n">
         <v>2500</v>
@@ -39494,22 +39494,22 @@
         <v>0</v>
       </c>
       <c r="L902" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M902" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N902" t="n">
-        <v>1906.1764864865</v>
+        <v>1906.1759813084</v>
       </c>
       <c r="O902" t="n">
-        <v>167743.530810812</v>
+        <v>160118.7824299056</v>
       </c>
       <c r="P902" t="n">
         <v>2900</v>
       </c>
       <c r="Q902" t="n">
-        <v>255200</v>
+        <v>243600</v>
       </c>
     </row>
     <row r="903">
@@ -39586,22 +39586,22 @@
         <v>0</v>
       </c>
       <c r="L904" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M904" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="N904" t="n">
-        <v>1668.6443636364</v>
+        <v>1668.6458215962</v>
       </c>
       <c r="O904" t="n">
-        <v>285338.1861818244</v>
+        <v>273657.9147417768</v>
       </c>
       <c r="P904" t="n">
         <v>2500</v>
       </c>
       <c r="Q904" t="n">
-        <v>427500</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="905">
@@ -40135,22 +40135,22 @@
         <v>0</v>
       </c>
       <c r="L916" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M916" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="N916" t="n">
         <v>11690</v>
       </c>
       <c r="O916" t="n">
-        <v>8405110</v>
+        <v>8393420</v>
       </c>
       <c r="P916" t="n">
         <v>18900</v>
       </c>
       <c r="Q916" t="n">
-        <v>13589100</v>
+        <v>13570200</v>
       </c>
     </row>
     <row r="917">
@@ -40190,10 +40190,10 @@
         <v>598</v>
       </c>
       <c r="N917" t="n">
-        <v>13518</v>
+        <v>13559.454697519</v>
       </c>
       <c r="O917" t="n">
-        <v>8083764</v>
+        <v>8108553.909116362</v>
       </c>
       <c r="P917" t="n">
         <v>21900</v>
@@ -40239,10 +40239,10 @@
         <v>720</v>
       </c>
       <c r="N918" t="n">
-        <v>9736</v>
+        <v>9760.865567680499</v>
       </c>
       <c r="O918" t="n">
-        <v>7009920</v>
+        <v>7027823.208729959</v>
       </c>
       <c r="P918" t="n">
         <v>15900</v>
@@ -40288,10 +40288,10 @@
         <v>48</v>
       </c>
       <c r="N919" t="n">
-        <v>44470</v>
+        <v>45032.911392405</v>
       </c>
       <c r="O919" t="n">
-        <v>2134560</v>
+        <v>2161579.74683544</v>
       </c>
       <c r="P919" t="n">
         <v>71900</v>
@@ -40337,10 +40337,10 @@
         <v>1196</v>
       </c>
       <c r="N920" t="n">
-        <v>5215</v>
+        <v>5227.7693437806</v>
       </c>
       <c r="O920" t="n">
-        <v>6237140</v>
+        <v>6252412.135161598</v>
       </c>
       <c r="P920" t="n">
         <v>8900</v>
@@ -40664,10 +40664,10 @@
         <v>1</v>
       </c>
       <c r="N927" t="n">
-        <v>15423.36</v>
+        <v>15646.886956522</v>
       </c>
       <c r="O927" t="n">
-        <v>15423.36</v>
+        <v>15646.886956522</v>
       </c>
       <c r="P927" t="n">
         <v>24900</v>
@@ -41724,10 +41724,10 @@
         <v>351</v>
       </c>
       <c r="N950" t="n">
-        <v>2286.1645279383</v>
+        <v>2286.164496124</v>
       </c>
       <c r="O950" t="n">
-        <v>802443.7493063434</v>
+        <v>802443.738139524</v>
       </c>
       <c r="P950" t="n">
         <v>3000</v>
@@ -42238,22 +42238,22 @@
         <v>0</v>
       </c>
       <c r="L962" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M962" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="N962" t="n">
-        <v>517.2943625967</v>
+        <v>517.29445253004</v>
       </c>
       <c r="O962" t="n">
-        <v>413835.49007736</v>
+        <v>387970.83939753</v>
       </c>
       <c r="P962" t="n">
         <v>900</v>
       </c>
       <c r="Q962" t="n">
-        <v>720000</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="963">
@@ -42429,10 +42429,10 @@
         <v>932</v>
       </c>
       <c r="N966" t="n">
-        <v>3110.8379310345</v>
+        <v>3110.8378564067</v>
       </c>
       <c r="O966" t="n">
-        <v>2899300.951724154</v>
+        <v>2899300.882171045</v>
       </c>
       <c r="P966" t="n">
         <v>4500</v>
@@ -42561,10 +42561,10 @@
         <v>13134</v>
       </c>
       <c r="N969" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O969" t="n">
-        <v>9243641.044454988</v>
+        <v>9243640.789773725</v>
       </c>
       <c r="P969" t="n">
         <v>900</v>
@@ -49960,10 +49960,10 @@
         <v>1</v>
       </c>
       <c r="N1132" t="n">
-        <v>1757.3206205251</v>
+        <v>1757.3206220096</v>
       </c>
       <c r="O1132" t="n">
-        <v>1757.3206205251</v>
+        <v>1757.3206220096</v>
       </c>
       <c r="P1132" t="n">
         <v>2000</v>
@@ -51289,10 +51289,10 @@
         <v>72</v>
       </c>
       <c r="N1161" t="n">
-        <v>7920</v>
+        <v>7945.2229299363</v>
       </c>
       <c r="O1161" t="n">
-        <v>570240</v>
+        <v>572056.0509554136</v>
       </c>
       <c r="P1161" t="n">
         <v>10500</v>
@@ -51338,10 +51338,10 @@
         <v>72</v>
       </c>
       <c r="N1162" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="O1162" t="n">
-        <v>570240</v>
+        <v>571680</v>
       </c>
       <c r="P1162" t="n">
         <v>10500</v>
@@ -51387,10 +51387,10 @@
         <v>72</v>
       </c>
       <c r="N1163" t="n">
-        <v>7920</v>
+        <v>8024.2105263158</v>
       </c>
       <c r="O1163" t="n">
-        <v>570240</v>
+        <v>577743.1578947376</v>
       </c>
       <c r="P1163" t="n">
         <v>10500</v>
@@ -51436,10 +51436,10 @@
         <v>72</v>
       </c>
       <c r="N1164" t="n">
-        <v>7920</v>
+        <v>7961.0362694301</v>
       </c>
       <c r="O1164" t="n">
-        <v>570240</v>
+        <v>573194.6113989672</v>
       </c>
       <c r="P1164" t="n">
         <v>10500</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1340,10 +1340,10 @@
         <v>473</v>
       </c>
       <c r="N23" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="O23" t="n">
-        <v>1934047.933609975</v>
+        <v>1926056</v>
       </c>
       <c r="P23" t="n">
         <v>7500</v>
@@ -4935,10 +4935,10 @@
         <v>13</v>
       </c>
       <c r="N109" t="n">
-        <v>15899.011607143</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O109" t="n">
-        <v>206687.150892859</v>
+        <v>204255.536488094</v>
       </c>
       <c r="P109" t="n">
         <v>28500</v>
@@ -7536,10 +7536,10 @@
         <v>158</v>
       </c>
       <c r="N171" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O171" t="n">
-        <v>417771.1873381262</v>
+        <v>406085.28</v>
       </c>
       <c r="P171" t="n">
         <v>4700</v>
@@ -8290,10 +8290,10 @@
         <v>7</v>
       </c>
       <c r="N189" t="n">
-        <v>4368.6523333333</v>
+        <v>4273.6816666667</v>
       </c>
       <c r="O189" t="n">
-        <v>30580.5663333331</v>
+        <v>29915.7716666669</v>
       </c>
       <c r="P189" t="n">
         <v>6500</v>
@@ -8546,10 +8546,10 @@
         <v>94</v>
       </c>
       <c r="N195" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O195" t="n">
-        <v>249961.584672895</v>
+        <v>240953.96</v>
       </c>
       <c r="P195" t="n">
         <v>4700</v>
@@ -9074,10 +9074,10 @@
         <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>27515</v>
+        <v>16509</v>
       </c>
       <c r="O207" t="n">
-        <v>27515</v>
+        <v>16509</v>
       </c>
       <c r="P207" t="n">
         <v>11500</v>
@@ -9278,22 +9278,22 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M212" t="n">
-        <v>9105</v>
+        <v>9078</v>
       </c>
       <c r="N212" t="n">
         <v>1726.32</v>
       </c>
       <c r="O212" t="n">
-        <v>15718143.6</v>
+        <v>15671532.96</v>
       </c>
       <c r="P212" t="n">
         <v>1500</v>
       </c>
       <c r="Q212" t="n">
-        <v>13657500</v>
+        <v>13617000</v>
       </c>
     </row>
     <row r="213">
@@ -10842,10 +10842,10 @@
         <v>4</v>
       </c>
       <c r="N249" t="n">
-        <v>12796.783333333</v>
+        <v>12587</v>
       </c>
       <c r="O249" t="n">
-        <v>51187.133333332</v>
+        <v>50348</v>
       </c>
       <c r="P249" t="n">
         <v>18900</v>
@@ -11098,10 +11098,10 @@
         <v>280</v>
       </c>
       <c r="N255" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O255" t="n">
-        <v>4833642.085298879</v>
+        <v>4818074.8</v>
       </c>
       <c r="P255" t="n">
         <v>20000</v>
@@ -13517,22 +13517,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M310" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="N310" t="n">
         <v>1203.38</v>
       </c>
       <c r="O310" t="n">
-        <v>388691.74</v>
+        <v>380268.08</v>
       </c>
       <c r="P310" t="n">
         <v>1900</v>
       </c>
       <c r="Q310" t="n">
-        <v>613700</v>
+        <v>600400</v>
       </c>
     </row>
     <row r="311">
@@ -14227,10 +14227,10 @@
         <v>353</v>
       </c>
       <c r="N326" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O326" t="n">
-        <v>1268771.350752699</v>
+        <v>1268771.34551725</v>
       </c>
       <c r="P326" t="n">
         <v>6500</v>
@@ -15129,10 +15129,10 @@
         <v>260</v>
       </c>
       <c r="N347" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O347" t="n">
-        <v>706898.87172996</v>
+        <v>700983.4</v>
       </c>
       <c r="P347" t="n">
         <v>8200</v>
@@ -16348,10 +16348,10 @@
         <v>358</v>
       </c>
       <c r="N375" t="n">
-        <v>6260.7161253561</v>
+        <v>6242.93</v>
       </c>
       <c r="O375" t="n">
-        <v>2241336.372877484</v>
+        <v>2234968.94</v>
       </c>
       <c r="P375" t="n">
         <v>10400</v>
@@ -16734,22 +16734,22 @@
         <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M384" t="n">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="N384" t="n">
         <v>1387.55</v>
       </c>
       <c r="O384" t="n">
-        <v>2929118.05</v>
+        <v>2927730.5</v>
       </c>
       <c r="P384" t="n">
         <v>2300</v>
       </c>
       <c r="Q384" t="n">
-        <v>4855300</v>
+        <v>4853000</v>
       </c>
     </row>
     <row r="385">
@@ -18507,10 +18507,10 @@
         <v>15</v>
       </c>
       <c r="N424" t="n">
-        <v>11749.140699301</v>
+        <v>11507.72</v>
       </c>
       <c r="O424" t="n">
-        <v>176237.110489515</v>
+        <v>172615.8</v>
       </c>
       <c r="P424" t="n">
         <v>25800</v>
@@ -21998,10 +21998,10 @@
         <v>11</v>
       </c>
       <c r="N505" t="n">
-        <v>2701.9479396985</v>
+        <v>2661.82</v>
       </c>
       <c r="O505" t="n">
-        <v>29721.4273366835</v>
+        <v>29280.02</v>
       </c>
       <c r="P505" t="n">
         <v>3200</v>
@@ -23780,10 +23780,10 @@
         <v>32</v>
       </c>
       <c r="N548" t="n">
-        <v>4355.2256097561</v>
+        <v>4355.2256790123</v>
       </c>
       <c r="O548" t="n">
-        <v>139367.2195121952</v>
+        <v>139367.2217283936</v>
       </c>
       <c r="P548" t="n">
         <v>7900</v>
@@ -25793,10 +25793,10 @@
         <v>1</v>
       </c>
       <c r="N595" t="n">
-        <v>61248.535714286</v>
+        <v>60174</v>
       </c>
       <c r="O595" t="n">
-        <v>61248.535714286</v>
+        <v>60174</v>
       </c>
       <c r="P595" t="n">
         <v>96900</v>
@@ -27389,10 +27389,10 @@
         <v>2</v>
       </c>
       <c r="N633" t="n">
-        <v>27637.186666667</v>
+        <v>20727.89</v>
       </c>
       <c r="O633" t="n">
-        <v>55274.373333334</v>
+        <v>41455.78</v>
       </c>
       <c r="P633" t="n">
         <v>33500</v>
@@ -27435,10 +27435,10 @@
         <v>1</v>
       </c>
       <c r="N634" t="n">
-        <v>15768.141666667</v>
+        <v>13515.55</v>
       </c>
       <c r="O634" t="n">
-        <v>15768.141666667</v>
+        <v>13515.55</v>
       </c>
       <c r="P634" t="n">
         <v>30900</v>
@@ -27563,10 +27563,10 @@
         <v>135</v>
       </c>
       <c r="N637" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O637" t="n">
-        <v>3676503.03545457</v>
+        <v>3661708.251818205</v>
       </c>
       <c r="P637" t="n">
         <v>44500</v>
@@ -28233,22 +28233,22 @@
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M653" t="n">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="N653" t="n">
-        <v>1561.0041954445</v>
+        <v>1561.004375</v>
       </c>
       <c r="O653" t="n">
-        <v>235711.6335121195</v>
+        <v>209174.58625</v>
       </c>
       <c r="P653" t="n">
         <v>2900</v>
       </c>
       <c r="Q653" t="n">
-        <v>437900</v>
+        <v>388600</v>
       </c>
     </row>
     <row r="654">
@@ -28956,10 +28956,10 @@
         <v>165</v>
       </c>
       <c r="N670" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O670" t="n">
-        <v>1318085.856134256</v>
+        <v>1315041.778009261</v>
       </c>
       <c r="P670" t="n">
         <v>12900</v>
@@ -29166,10 +29166,10 @@
         <v>39</v>
       </c>
       <c r="N675" t="n">
-        <v>9794.2880924855</v>
+        <v>9627.34</v>
       </c>
       <c r="O675" t="n">
-        <v>381977.2356069345</v>
+        <v>375466.26</v>
       </c>
       <c r="P675" t="n">
         <v>15900</v>
@@ -30441,10 +30441,10 @@
         <v>48</v>
       </c>
       <c r="N705" t="n">
-        <v>2647.8160651629</v>
+        <v>2634.61</v>
       </c>
       <c r="O705" t="n">
-        <v>127095.1711278192</v>
+        <v>126461.28</v>
       </c>
       <c r="P705" t="n">
         <v>4200</v>
@@ -30487,10 +30487,10 @@
         <v>4</v>
       </c>
       <c r="N706" t="n">
-        <v>3131.5075106082</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O706" t="n">
-        <v>12526.0300424328</v>
+        <v>12455.560113154</v>
       </c>
       <c r="P706" t="n">
         <v>5000</v>
@@ -30717,10 +30717,10 @@
         <v>78</v>
       </c>
       <c r="N711" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O711" t="n">
-        <v>195849.4414336902</v>
+        <v>194686.44</v>
       </c>
       <c r="P711" t="n">
         <v>4100</v>
@@ -30996,10 +30996,10 @@
         <v>7</v>
       </c>
       <c r="N717" t="n">
-        <v>5859.18</v>
+        <v>5791.05</v>
       </c>
       <c r="O717" t="n">
-        <v>41014.26</v>
+        <v>40537.35</v>
       </c>
       <c r="P717" t="n">
         <v>9300</v>
@@ -31494,22 +31494,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M728" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N728" t="n">
         <v>18536</v>
       </c>
       <c r="O728" t="n">
-        <v>92680</v>
+        <v>74144</v>
       </c>
       <c r="P728" t="n">
         <v>30900</v>
       </c>
       <c r="Q728" t="n">
-        <v>154500</v>
+        <v>123600</v>
       </c>
     </row>
     <row r="729">
@@ -32328,10 +32328,10 @@
         <v>175</v>
       </c>
       <c r="N746" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O746" t="n">
-        <v>2816272.331154625</v>
+        <v>2810150</v>
       </c>
       <c r="P746" t="n">
         <v>25900</v>
@@ -32374,10 +32374,10 @@
         <v>194</v>
       </c>
       <c r="N747" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O747" t="n">
-        <v>4961916.709966446</v>
+        <v>4953596</v>
       </c>
       <c r="P747" t="n">
         <v>40900</v>
@@ -32745,10 +32745,10 @@
         <v>20</v>
       </c>
       <c r="N755" t="n">
-        <v>9927.272727272701</v>
+        <v>9750</v>
       </c>
       <c r="O755" t="n">
-        <v>198545.454545454</v>
+        <v>195000</v>
       </c>
       <c r="P755" t="n">
         <v>15600</v>
@@ -32837,10 +32837,10 @@
         <v>44</v>
       </c>
       <c r="N757" t="n">
-        <v>7278.6868686869</v>
+        <v>7230</v>
       </c>
       <c r="O757" t="n">
-        <v>320262.2222222236</v>
+        <v>318120</v>
       </c>
       <c r="P757" t="n">
         <v>11600</v>
@@ -33762,10 +33762,10 @@
         <v>1</v>
       </c>
       <c r="N777" t="n">
-        <v>42312.716</v>
+        <v>26445.452</v>
       </c>
       <c r="O777" t="n">
-        <v>42312.716</v>
+        <v>26445.452</v>
       </c>
       <c r="P777" t="n">
         <v>44900</v>
@@ -33854,10 +33854,10 @@
         <v>62</v>
       </c>
       <c r="N779" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O779" t="n">
-        <v>855293.426315796</v>
+        <v>848594</v>
       </c>
       <c r="P779" t="n">
         <v>21900</v>
@@ -34823,10 +34823,10 @@
         <v>1</v>
       </c>
       <c r="N800" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="O800" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="P800" t="n">
         <v>55900</v>
@@ -35329,10 +35329,10 @@
         <v>19</v>
       </c>
       <c r="N811" t="n">
-        <v>3412.5148218527</v>
+        <v>3396.38</v>
       </c>
       <c r="O811" t="n">
-        <v>64837.7816152013</v>
+        <v>64531.22</v>
       </c>
       <c r="P811" t="n">
         <v>6500</v>
@@ -35513,10 +35513,10 @@
         <v>13</v>
       </c>
       <c r="N815" t="n">
-        <v>23932.94</v>
+        <v>23376.36</v>
       </c>
       <c r="O815" t="n">
-        <v>311128.22</v>
+        <v>303892.68</v>
       </c>
       <c r="P815" t="n">
         <v>40900</v>
@@ -35559,10 +35559,10 @@
         <v>111</v>
       </c>
       <c r="N816" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O816" t="n">
-        <v>1468891.531690194</v>
+        <v>1466310</v>
       </c>
       <c r="P816" t="n">
         <v>23900</v>
@@ -35738,10 +35738,10 @@
         <v>3</v>
       </c>
       <c r="N820" t="n">
-        <v>36516.685818182</v>
+        <v>35864.602181818</v>
       </c>
       <c r="O820" t="n">
-        <v>109550.057454546</v>
+        <v>107593.806545454</v>
       </c>
       <c r="P820" t="n">
         <v>62900</v>
@@ -36014,10 +36014,10 @@
         <v>10</v>
       </c>
       <c r="N826" t="n">
-        <v>12498.870967742</v>
+        <v>11922</v>
       </c>
       <c r="O826" t="n">
-        <v>124988.70967742</v>
+        <v>119220</v>
       </c>
       <c r="P826" t="n">
         <v>19900</v>
@@ -36106,10 +36106,10 @@
         <v>252</v>
       </c>
       <c r="N828" t="n">
-        <v>2657.2435094002</v>
+        <v>2629</v>
       </c>
       <c r="O828" t="n">
-        <v>669625.3643688504</v>
+        <v>662508</v>
       </c>
       <c r="P828" t="n">
         <v>4500</v>
@@ -36198,10 +36198,10 @@
         <v>10</v>
       </c>
       <c r="N830" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O830" t="n">
-        <v>68818.46329837901</v>
+        <v>68492</v>
       </c>
       <c r="P830" t="n">
         <v>11500</v>
@@ -36336,10 +36336,10 @@
         <v>324</v>
       </c>
       <c r="N833" t="n">
-        <v>6279.1629563669</v>
+        <v>6268</v>
       </c>
       <c r="O833" t="n">
-        <v>2034448.797862876</v>
+        <v>2030832</v>
       </c>
       <c r="P833" t="n">
         <v>10900</v>
@@ -36612,10 +36612,10 @@
         <v>447</v>
       </c>
       <c r="N839" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O839" t="n">
-        <v>3414754.283916071</v>
+        <v>3412845</v>
       </c>
       <c r="P839" t="n">
         <v>13900</v>
@@ -37938,22 +37938,22 @@
         <v>0</v>
       </c>
       <c r="L868" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M868" t="n">
-        <v>1653</v>
+        <v>1642</v>
       </c>
       <c r="N868" t="n">
         <v>1326</v>
       </c>
       <c r="O868" t="n">
-        <v>2191878</v>
+        <v>2177292</v>
       </c>
       <c r="P868" t="n">
         <v>2500</v>
       </c>
       <c r="Q868" t="n">
-        <v>4132500</v>
+        <v>4105000</v>
       </c>
     </row>
     <row r="869">
@@ -38174,10 +38174,10 @@
         <v>26</v>
       </c>
       <c r="N873" t="n">
-        <v>21884.258426966</v>
+        <v>21762</v>
       </c>
       <c r="O873" t="n">
-        <v>568990.7191011161</v>
+        <v>565812</v>
       </c>
       <c r="P873" t="n">
         <v>35900</v>
@@ -38220,10 +38220,10 @@
         <v>1537</v>
       </c>
       <c r="N874" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O874" t="n">
-        <v>5876896.765229283</v>
+        <v>5872877</v>
       </c>
       <c r="P874" t="n">
         <v>5900</v>
@@ -38358,10 +38358,10 @@
         <v>107</v>
       </c>
       <c r="N877" t="n">
-        <v>7295.3326848249</v>
+        <v>7253</v>
       </c>
       <c r="O877" t="n">
-        <v>780600.5972762643</v>
+        <v>776071</v>
       </c>
       <c r="P877" t="n">
         <v>11900</v>
@@ -39545,22 +39545,22 @@
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M903" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="N903" t="n">
-        <v>2546.9807189542</v>
+        <v>2546.9805333333</v>
       </c>
       <c r="O903" t="n">
-        <v>241963.168300649</v>
+        <v>226681.2674666637</v>
       </c>
       <c r="P903" t="n">
         <v>3900</v>
       </c>
       <c r="Q903" t="n">
-        <v>370500</v>
+        <v>347100</v>
       </c>
     </row>
     <row r="904">
@@ -39959,10 +39959,10 @@
         <v>75</v>
       </c>
       <c r="N912" t="n">
-        <v>1955.7828121686</v>
+        <v>1955.2371130338</v>
       </c>
       <c r="O912" t="n">
-        <v>146683.710912645</v>
+        <v>146642.783477535</v>
       </c>
       <c r="P912" t="n">
         <v>3000</v>
@@ -40005,10 +40005,10 @@
         <v>570</v>
       </c>
       <c r="N913" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O913" t="n">
-        <v>675914.3714285759</v>
+        <v>675632.152380942</v>
       </c>
       <c r="P913" t="n">
         <v>1900</v>
@@ -40767,10 +40767,10 @@
         <v>41</v>
       </c>
       <c r="N929" t="n">
-        <v>3256.3775316456</v>
+        <v>3026.5160126582</v>
       </c>
       <c r="O929" t="n">
-        <v>133511.4787974696</v>
+        <v>124087.1565189862</v>
       </c>
       <c r="P929" t="n">
         <v>7000</v>
@@ -40862,10 +40862,10 @@
         <v>321</v>
       </c>
       <c r="N931" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O931" t="n">
-        <v>493684.600940301</v>
+        <v>491274.4237530819</v>
       </c>
       <c r="P931" t="n">
         <v>2600</v>
@@ -42474,10 +42474,10 @@
         <v>13061</v>
       </c>
       <c r="N967" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O967" t="n">
-        <v>9192263.51128103</v>
+        <v>9203771.222108344</v>
       </c>
       <c r="P967" t="n">
         <v>900</v>
@@ -45854,10 +45854,10 @@
         <v>1</v>
       </c>
       <c r="N1040" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="O1040" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="P1040" t="n">
         <v>45000</v>
@@ -46418,10 +46418,10 @@
         <v>3</v>
       </c>
       <c r="N1052" t="n">
-        <v>5272.2028268551</v>
+        <v>5216.9</v>
       </c>
       <c r="O1052" t="n">
-        <v>15816.6084805653</v>
+        <v>15650.7</v>
       </c>
       <c r="P1052" t="n">
         <v>20500</v>
@@ -46513,10 +46513,10 @@
         <v>3</v>
       </c>
       <c r="N1054" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="O1054" t="n">
-        <v>22816.3485981309</v>
+        <v>22397.7</v>
       </c>
       <c r="P1054" t="n">
         <v>11900</v>
@@ -46837,10 +46837,10 @@
         <v>24</v>
       </c>
       <c r="N1061" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="O1061" t="n">
-        <v>1071717.008098152</v>
+        <v>1058726.500122696</v>
       </c>
       <c r="P1061" t="n">
         <v>71900</v>
@@ -48690,10 +48690,10 @@
         <v>40</v>
       </c>
       <c r="N1103" t="n">
-        <v>3186.7802147239</v>
+        <v>3181.9</v>
       </c>
       <c r="O1103" t="n">
-        <v>127471.208588956</v>
+        <v>127276</v>
       </c>
       <c r="P1103" t="n">
         <v>5100</v>
@@ -49776,10 +49776,10 @@
         <v>3</v>
       </c>
       <c r="N1128" t="n">
-        <v>2098.7012987013</v>
+        <v>1600</v>
       </c>
       <c r="O1128" t="n">
-        <v>6296.103896103899</v>
+        <v>4800</v>
       </c>
       <c r="P1128" t="n">
         <v>3500</v>
@@ -49822,10 +49822,10 @@
         <v>4</v>
       </c>
       <c r="N1129" t="n">
-        <v>707.69883076923</v>
+        <v>705.5279692307701</v>
       </c>
       <c r="O1129" t="n">
-        <v>2830.79532307692</v>
+        <v>2822.11187692308</v>
       </c>
       <c r="P1129" t="n">
         <v>1500</v>
@@ -50224,10 +50224,10 @@
         <v>12</v>
       </c>
       <c r="N1138" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="O1138" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="P1138" t="n">
         <v>3000</v>
@@ -50460,10 +50460,10 @@
         <v>251</v>
       </c>
       <c r="N1143" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O1143" t="n">
-        <v>666534.2608026776</v>
+        <v>663869.9</v>
       </c>
       <c r="P1143" t="n">
         <v>3900</v>
@@ -51196,22 +51196,22 @@
         <v>0</v>
       </c>
       <c r="L1159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1159" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N1159" t="n">
         <v>7920</v>
       </c>
       <c r="O1159" t="n">
-        <v>419760</v>
+        <v>396000</v>
       </c>
       <c r="P1159" t="n">
         <v>10500</v>
       </c>
       <c r="Q1159" t="n">
-        <v>556500</v>
+        <v>525000</v>
       </c>
     </row>
     <row r="1160">
@@ -51245,22 +51245,22 @@
         <v>0</v>
       </c>
       <c r="L1160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1160" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N1160" t="n">
         <v>7920</v>
       </c>
       <c r="O1160" t="n">
-        <v>498960</v>
+        <v>475200</v>
       </c>
       <c r="P1160" t="n">
         <v>10500</v>
       </c>
       <c r="Q1160" t="n">
-        <v>661500</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="1161">
@@ -51294,22 +51294,22 @@
         <v>0</v>
       </c>
       <c r="L1161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1161" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N1161" t="n">
         <v>7920</v>
       </c>
       <c r="O1161" t="n">
-        <v>340560</v>
+        <v>308880</v>
       </c>
       <c r="P1161" t="n">
         <v>10500</v>
       </c>
       <c r="Q1161" t="n">
-        <v>451500</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="1162">
@@ -51343,22 +51343,22 @@
         <v>0</v>
       </c>
       <c r="L1162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1162" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N1162" t="n">
         <v>7920</v>
       </c>
       <c r="O1162" t="n">
-        <v>396000</v>
+        <v>388080</v>
       </c>
       <c r="P1162" t="n">
         <v>10500</v>
       </c>
       <c r="Q1162" t="n">
-        <v>525000</v>
+        <v>514500</v>
       </c>
     </row>
     <row r="1163">
@@ -51717,10 +51717,10 @@
         <v>13</v>
       </c>
       <c r="N1170" t="n">
-        <v>6162.2222222222</v>
+        <v>5900</v>
       </c>
       <c r="O1170" t="n">
-        <v>80108.8888888886</v>
+        <v>76700</v>
       </c>
       <c r="P1170" t="n">
         <v>7100</v>
@@ -51809,10 +51809,10 @@
         <v>14</v>
       </c>
       <c r="N1172" t="n">
-        <v>26102.941176471</v>
+        <v>25000</v>
       </c>
       <c r="O1172" t="n">
-        <v>365441.176470594</v>
+        <v>350000</v>
       </c>
       <c r="P1172" t="n">
         <v>30000</v>
@@ -51855,10 +51855,10 @@
         <v>1</v>
       </c>
       <c r="N1173" t="n">
-        <v>6750</v>
+        <v>4500</v>
       </c>
       <c r="O1173" t="n">
-        <v>6750</v>
+        <v>4500</v>
       </c>
       <c r="P1173" t="n">
         <v>5400</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -3316,10 +3316,10 @@
         <v>74</v>
       </c>
       <c r="N72" t="n">
-        <v>31566.3666</v>
+        <v>31409.32</v>
       </c>
       <c r="O72" t="n">
-        <v>2335911.1284</v>
+        <v>2324289.68</v>
       </c>
       <c r="P72" t="n">
         <v>45500</v>
@@ -11104,10 +11104,10 @@
         <v>297</v>
       </c>
       <c r="N255" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O255" t="n">
-        <v>4042136.415875877</v>
+        <v>4037224.95</v>
       </c>
       <c r="P255" t="n">
         <v>25500</v>
@@ -11670,10 +11670,10 @@
         <v>587</v>
       </c>
       <c r="N268" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O268" t="n">
-        <v>1516546.529461525</v>
+        <v>1515783.677614484</v>
       </c>
       <c r="P268" t="n">
         <v>4500</v>
@@ -12100,10 +12100,10 @@
         <v>2787</v>
       </c>
       <c r="N278" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O278" t="n">
-        <v>8809000.340296987</v>
+        <v>8803745.158789644</v>
       </c>
       <c r="P278" t="n">
         <v>5600</v>
@@ -12325,10 +12325,10 @@
         <v>2</v>
       </c>
       <c r="N283" t="n">
-        <v>8252.563380281699</v>
+        <v>8214</v>
       </c>
       <c r="O283" t="n">
-        <v>16505.1267605634</v>
+        <v>16428</v>
       </c>
       <c r="P283" t="n">
         <v>7900</v>
@@ -12374,10 +12374,10 @@
         <v>55</v>
       </c>
       <c r="N284" t="n">
-        <v>3283.163260274</v>
+        <v>3230.0662191781</v>
       </c>
       <c r="O284" t="n">
-        <v>180573.97931507</v>
+        <v>177653.6420547955</v>
       </c>
       <c r="P284" t="n">
         <v>6200</v>
@@ -12825,10 +12825,10 @@
         <v>323</v>
       </c>
       <c r="N294" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="O294" t="n">
-        <v>2848860</v>
+        <v>2841108</v>
       </c>
       <c r="P294" t="n">
         <v>14900</v>
@@ -15626,10 +15626,10 @@
         <v>8119</v>
       </c>
       <c r="N358" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O358" t="n">
-        <v>35496799.5301413</v>
+        <v>35489539.48324803</v>
       </c>
       <c r="P358" t="n">
         <v>8900</v>
@@ -15967,10 +15967,10 @@
         <v>125</v>
       </c>
       <c r="N366" t="n">
-        <v>5371.5779551122</v>
+        <v>5331.69</v>
       </c>
       <c r="O366" t="n">
-        <v>671447.2443890249</v>
+        <v>666461.25</v>
       </c>
       <c r="P366" t="n">
         <v>7900</v>
@@ -16529,10 +16529,10 @@
         <v>2524</v>
       </c>
       <c r="N379" t="n">
-        <v>1534.4227525419</v>
+        <v>1532.6290227489</v>
       </c>
       <c r="O379" t="n">
-        <v>3872883.027415756</v>
+        <v>3868355.653418224</v>
       </c>
       <c r="P379" t="n">
         <v>1200</v>
@@ -17281,10 +17281,10 @@
         <v>1</v>
       </c>
       <c r="N396" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O396" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="P396" t="n">
         <v>6900</v>
@@ -18554,10 +18554,10 @@
         <v>37</v>
       </c>
       <c r="N425" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="O425" t="n">
-        <v>707240.611111107</v>
+        <v>688126</v>
       </c>
       <c r="P425" t="n">
         <v>21900</v>
@@ -21963,10 +21963,10 @@
         <v>6</v>
       </c>
       <c r="N504" t="n">
-        <v>7719.830483871</v>
+        <v>7537.4723387097</v>
       </c>
       <c r="O504" t="n">
-        <v>46318.982903226</v>
+        <v>45224.8340322582</v>
       </c>
       <c r="P504" t="n">
         <v>8900</v>
@@ -22209,10 +22209,10 @@
         <v>162</v>
       </c>
       <c r="N510" t="n">
-        <v>1974.990872211</v>
+        <v>1969</v>
       </c>
       <c r="O510" t="n">
-        <v>319948.521298182</v>
+        <v>318978</v>
       </c>
       <c r="P510" t="n">
         <v>1500</v>
@@ -22294,10 +22294,10 @@
         <v>251</v>
       </c>
       <c r="N512" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O512" t="n">
-        <v>2208665.84875283</v>
+        <v>2207414.48</v>
       </c>
       <c r="P512" t="n">
         <v>14500</v>
@@ -24508,10 +24508,10 @@
         <v>11</v>
       </c>
       <c r="N565" t="n">
-        <v>57801.91954023</v>
+        <v>56503</v>
       </c>
       <c r="O565" t="n">
-        <v>635821.1149425301</v>
+        <v>621533</v>
       </c>
       <c r="P565" t="n">
         <v>90500</v>
@@ -27308,10 +27308,10 @@
         <v>46</v>
       </c>
       <c r="N631" t="n">
-        <v>22761.155411606</v>
+        <v>22730.48</v>
       </c>
       <c r="O631" t="n">
-        <v>1047013.148933876</v>
+        <v>1045602.08</v>
       </c>
       <c r="P631" t="n">
         <v>36900</v>
@@ -28199,10 +28199,10 @@
         <v>37</v>
       </c>
       <c r="N652" t="n">
-        <v>5455.0456387665</v>
+        <v>5431.12</v>
       </c>
       <c r="O652" t="n">
-        <v>201836.6886343605</v>
+        <v>200951.44</v>
       </c>
       <c r="P652" t="n">
         <v>8900</v>
@@ -32288,10 +32288,10 @@
         <v>56</v>
       </c>
       <c r="N745" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O745" t="n">
-        <v>1009299.5584</v>
+        <v>1008896</v>
       </c>
       <c r="P745" t="n">
         <v>29900</v>
@@ -37257,10 +37257,10 @@
         <v>40</v>
       </c>
       <c r="N853" t="n">
-        <v>60093.865363735</v>
+        <v>59834</v>
       </c>
       <c r="O853" t="n">
-        <v>2403754.6145494</v>
+        <v>2393360</v>
       </c>
       <c r="P853" t="n">
         <v>7900</v>
@@ -37720,10 +37720,10 @@
         <v>18</v>
       </c>
       <c r="N863" t="n">
-        <v>40318.846625767</v>
+        <v>40073</v>
       </c>
       <c r="O863" t="n">
-        <v>725739.239263806</v>
+        <v>721314</v>
       </c>
       <c r="P863" t="n">
         <v>64900</v>
@@ -37904,10 +37904,10 @@
         <v>13</v>
       </c>
       <c r="N867" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="O867" t="n">
-        <v>47484.641036586</v>
+        <v>47311.55</v>
       </c>
       <c r="P867" t="n">
         <v>7500</v>
@@ -38641,10 +38641,10 @@
         <v>246</v>
       </c>
       <c r="N883" t="n">
-        <v>2463.8091310592</v>
+        <v>2458.5124991023</v>
       </c>
       <c r="O883" t="n">
-        <v>606097.0462405632</v>
+        <v>604794.0747791658</v>
       </c>
       <c r="P883" t="n">
         <v>3500</v>
@@ -39511,10 +39511,10 @@
         <v>164</v>
       </c>
       <c r="N902" t="n">
-        <v>1692.9473786408</v>
+        <v>1668.6473786408</v>
       </c>
       <c r="O902" t="n">
-        <v>277643.3700970912</v>
+        <v>273658.1700970912</v>
       </c>
       <c r="P902" t="n">
         <v>2500</v>
@@ -41555,10 +41555,10 @@
         <v>4299</v>
       </c>
       <c r="N946" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O946" t="n">
-        <v>1485881.812092449</v>
+        <v>1485555.501316155</v>
       </c>
       <c r="P946" t="n">
         <v>600</v>
@@ -41599,10 +41599,10 @@
         <v>1557</v>
       </c>
       <c r="N947" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O947" t="n">
-        <v>1108395.009048314</v>
+        <v>1107551.156568319</v>
       </c>
       <c r="P947" t="n">
         <v>900</v>
@@ -42299,10 +42299,10 @@
         <v>1</v>
       </c>
       <c r="N963" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="O963" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="P963" t="n">
         <v>3600</v>
@@ -44263,10 +44263,10 @@
         <v>43</v>
       </c>
       <c r="N1006" t="n">
-        <v>5480.6844036697</v>
+        <v>5430.86</v>
       </c>
       <c r="O1006" t="n">
-        <v>235669.4293577971</v>
+        <v>233526.98</v>
       </c>
       <c r="P1006" t="n">
         <v>13900</v>
@@ -46612,10 +46612,10 @@
         <v>38</v>
       </c>
       <c r="N1056" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O1056" t="n">
-        <v>268131.2588102966</v>
+        <v>267783.7134241836</v>
       </c>
       <c r="P1056" t="n">
         <v>9900</v>
@@ -47221,22 +47221,22 @@
         <v>0</v>
       </c>
       <c r="L1069" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1069" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N1069" t="n">
         <v>3155</v>
       </c>
       <c r="O1069" t="n">
-        <v>1107405</v>
+        <v>1104250</v>
       </c>
       <c r="P1069" t="n">
         <v>5900</v>
       </c>
       <c r="Q1069" t="n">
-        <v>2070900</v>
+        <v>2065000</v>
       </c>
     </row>
     <row r="1070">
@@ -48265,10 +48265,10 @@
         <v>332</v>
       </c>
       <c r="N1093" t="n">
-        <v>2490.4710359188</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O1093" t="n">
-        <v>826836.3839250416</v>
+        <v>826406.1872774548</v>
       </c>
       <c r="P1093" t="n">
         <v>3000</v>
@@ -48822,10 +48822,10 @@
         <v>1198</v>
       </c>
       <c r="N1106" t="n">
-        <v>1796.1048285838</v>
+        <v>1794.2879574714</v>
       </c>
       <c r="O1106" t="n">
-        <v>2151733.584643392</v>
+        <v>2149556.973050737</v>
       </c>
       <c r="P1106" t="n">
         <v>1600</v>
@@ -50926,10 +50926,10 @@
         <v>4</v>
       </c>
       <c r="N1153" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="O1153" t="n">
-        <v>29985.9030837004</v>
+        <v>29920</v>
       </c>
       <c r="P1153" t="n">
         <v>9500</v>
@@ -50972,10 +50972,10 @@
         <v>9</v>
       </c>
       <c r="N1154" t="n">
-        <v>5320.824742268</v>
+        <v>5280</v>
       </c>
       <c r="O1154" t="n">
-        <v>47887.422680412</v>
+        <v>47520</v>
       </c>
       <c r="P1154" t="n">
         <v>6900</v>
@@ -53058,10 +53058,10 @@
         <v>227</v>
       </c>
       <c r="N1199" t="n">
-        <v>2547.0191593353</v>
+        <v>2539.5717399804</v>
       </c>
       <c r="O1199" t="n">
-        <v>578173.3491691131</v>
+        <v>576482.7849755507</v>
       </c>
       <c r="P1199" t="n">
         <v>2900</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -895,10 +895,10 @@
         <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>1811.3093916756</v>
+        <v>1830.8488673139</v>
       </c>
       <c r="O12" t="n">
-        <v>76074.9944503752</v>
+        <v>76895.6524271838</v>
       </c>
       <c r="P12" t="n">
         <v>2600</v>
@@ -2475,22 +2475,22 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N51" t="n">
         <v>18777.5</v>
       </c>
       <c r="O51" t="n">
-        <v>488215</v>
+        <v>469437.5</v>
       </c>
       <c r="P51" t="n">
         <v>27300</v>
       </c>
       <c r="Q51" t="n">
-        <v>709800</v>
+        <v>682500</v>
       </c>
     </row>
     <row r="52">
@@ -2592,22 +2592,22 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>6272.8551705566</v>
+        <v>6272.8551798561</v>
       </c>
       <c r="O54" t="n">
-        <v>43909.9861938962</v>
+        <v>37637.1310791366</v>
       </c>
       <c r="P54" t="n">
         <v>7900</v>
       </c>
       <c r="Q54" t="n">
-        <v>55300</v>
+        <v>47400</v>
       </c>
     </row>
     <row r="55">
@@ -4982,10 +4982,10 @@
         <v>1</v>
       </c>
       <c r="N110" t="n">
-        <v>9392.0756666667</v>
+        <v>9392.075964912299</v>
       </c>
       <c r="O110" t="n">
-        <v>9392.0756666667</v>
+        <v>9392.075964912299</v>
       </c>
       <c r="P110" t="n">
         <v>18500</v>
@@ -9791,22 +9791,22 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N224" t="n">
         <v>14233.54</v>
       </c>
       <c r="O224" t="n">
-        <v>626275.76</v>
+        <v>612042.2200000001</v>
       </c>
       <c r="P224" t="n">
         <v>10000</v>
       </c>
       <c r="Q224" t="n">
-        <v>440000</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="225">
@@ -9882,10 +9882,10 @@
         <v>796</v>
       </c>
       <c r="N226" t="n">
-        <v>1098.0684371373</v>
+        <v>1098.0685808709</v>
       </c>
       <c r="O226" t="n">
-        <v>874062.4759612908</v>
+        <v>874062.5903732363</v>
       </c>
       <c r="P226" t="n">
         <v>1500</v>
@@ -11664,22 +11664,22 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="N268" t="n">
-        <v>2582.2549620637</v>
+        <v>2582.2549607893</v>
       </c>
       <c r="O268" t="n">
-        <v>1466720.818452182</v>
+        <v>1464138.562767533</v>
       </c>
       <c r="P268" t="n">
         <v>4500</v>
       </c>
       <c r="Q268" t="n">
-        <v>2556000</v>
+        <v>2551500</v>
       </c>
     </row>
     <row r="269">
@@ -11710,22 +11710,22 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M269" t="n">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="N269" t="n">
-        <v>5216.8958877086</v>
+        <v>5216.8958858357</v>
       </c>
       <c r="O269" t="n">
-        <v>7126279.782609947</v>
+        <v>7110629.09239406</v>
       </c>
       <c r="P269" t="n">
         <v>8500</v>
       </c>
       <c r="Q269" t="n">
-        <v>11611000</v>
+        <v>11585500</v>
       </c>
     </row>
     <row r="270">
@@ -12100,10 +12100,10 @@
         <v>2787</v>
       </c>
       <c r="N278" t="n">
-        <v>3158.8608391782</v>
+        <v>3158.86083922</v>
       </c>
       <c r="O278" t="n">
-        <v>8803745.158789644</v>
+        <v>8803745.158906139</v>
       </c>
       <c r="P278" t="n">
         <v>5600</v>
@@ -12770,22 +12770,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M293" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N293" t="n">
         <v>9664</v>
       </c>
       <c r="O293" t="n">
-        <v>251264</v>
+        <v>231936</v>
       </c>
       <c r="P293" t="n">
         <v>15900</v>
       </c>
       <c r="Q293" t="n">
-        <v>413400</v>
+        <v>381600</v>
       </c>
     </row>
     <row r="294">
@@ -13045,10 +13045,10 @@
         <v>468</v>
       </c>
       <c r="N299" t="n">
-        <v>3795.7100076176</v>
+        <v>3795.7100076234</v>
       </c>
       <c r="O299" t="n">
-        <v>1776392.283565037</v>
+        <v>1776392.283567751</v>
       </c>
       <c r="P299" t="n">
         <v>6200</v>
@@ -13434,10 +13434,10 @@
         <v>297</v>
       </c>
       <c r="N308" t="n">
-        <v>4890.9300534045</v>
+        <v>4890.9300534402</v>
       </c>
       <c r="O308" t="n">
-        <v>1452606.225861136</v>
+        <v>1452606.225871739</v>
       </c>
       <c r="P308" t="n">
         <v>8200</v>
@@ -14233,10 +14233,10 @@
         <v>353</v>
       </c>
       <c r="N326" t="n">
-        <v>3594.2530181818</v>
+        <v>3594.2529978118</v>
       </c>
       <c r="O326" t="n">
-        <v>1268771.315418175</v>
+        <v>1268771.308227565</v>
       </c>
       <c r="P326" t="n">
         <v>6500</v>
@@ -15225,10 +15225,10 @@
         <v>2514</v>
       </c>
       <c r="N349" t="n">
-        <v>3472.2762167406</v>
+        <v>3472.276224504</v>
       </c>
       <c r="O349" t="n">
-        <v>8729302.408885868</v>
+        <v>8729302.428403055</v>
       </c>
       <c r="P349" t="n">
         <v>5900</v>
@@ -15533,22 +15533,22 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M356" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N356" t="n">
-        <v>3041.6600141844</v>
+        <v>3041.6600141945</v>
       </c>
       <c r="O356" t="n">
-        <v>188582.9208794328</v>
+        <v>185541.2608658645</v>
       </c>
       <c r="P356" t="n">
         <v>5500</v>
       </c>
       <c r="Q356" t="n">
-        <v>341000</v>
+        <v>335500</v>
       </c>
     </row>
     <row r="357">
@@ -15574,22 +15574,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M357" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N357" t="n">
         <v>3981.47</v>
       </c>
       <c r="O357" t="n">
-        <v>370276.71</v>
+        <v>366295.24</v>
       </c>
       <c r="P357" t="n">
         <v>7000</v>
       </c>
       <c r="Q357" t="n">
-        <v>651000</v>
+        <v>644000</v>
       </c>
     </row>
     <row r="358">
@@ -15626,10 +15626,10 @@
         <v>8119</v>
       </c>
       <c r="N358" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O358" t="n">
-        <v>35489539.48394708</v>
+        <v>35494380.50692941</v>
       </c>
       <c r="P358" t="n">
         <v>8900</v>
@@ -15926,10 +15926,10 @@
         <v>93</v>
       </c>
       <c r="N365" t="n">
-        <v>3655.96</v>
+        <v>3668.2806919793</v>
       </c>
       <c r="O365" t="n">
-        <v>340004.28</v>
+        <v>341150.1043540749</v>
       </c>
       <c r="P365" t="n">
         <v>5500</v>
@@ -16403,10 +16403,10 @@
         <v>211</v>
       </c>
       <c r="N376" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O376" t="n">
-        <v>980854.6000000001</v>
+        <v>981026.1680601746</v>
       </c>
       <c r="P376" t="n">
         <v>8900</v>
@@ -18116,10 +18116,10 @@
         <v>97</v>
       </c>
       <c r="N415" t="n">
-        <v>1630.9246047904</v>
+        <v>1630.9246075494</v>
       </c>
       <c r="O415" t="n">
-        <v>158199.6866646688</v>
+        <v>158199.6869322918</v>
       </c>
       <c r="P415" t="n">
         <v>2500</v>
@@ -18208,10 +18208,10 @@
         <v>263</v>
       </c>
       <c r="N417" t="n">
-        <v>1550.1946673374</v>
+        <v>1551.3666948085</v>
       </c>
       <c r="O417" t="n">
-        <v>407701.1975097362</v>
+        <v>408009.4407346355</v>
       </c>
       <c r="P417" t="n">
         <v>2500</v>
@@ -18300,10 +18300,10 @@
         <v>194</v>
       </c>
       <c r="N419" t="n">
-        <v>2403.5202775057</v>
+        <v>2407.4618268285</v>
       </c>
       <c r="O419" t="n">
-        <v>466282.9338361058</v>
+        <v>467047.594404729</v>
       </c>
       <c r="P419" t="n">
         <v>3500</v>
@@ -20386,22 +20386,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N467" t="n">
         <v>9043.690000000001</v>
       </c>
       <c r="O467" t="n">
-        <v>18087.38</v>
+        <v>9043.690000000001</v>
       </c>
       <c r="P467" t="n">
         <v>13500</v>
       </c>
       <c r="Q467" t="n">
-        <v>27000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="468">
@@ -22004,10 +22004,10 @@
         <v>11</v>
       </c>
       <c r="N505" t="n">
-        <v>2661.82</v>
+        <v>2668.524836272</v>
       </c>
       <c r="O505" t="n">
-        <v>29280.02</v>
+        <v>29353.773198992</v>
       </c>
       <c r="P505" t="n">
         <v>3200</v>
@@ -22127,10 +22127,10 @@
         <v>1</v>
       </c>
       <c r="N508" t="n">
-        <v>2081</v>
+        <v>2086.0024038462</v>
       </c>
       <c r="O508" t="n">
-        <v>2081</v>
+        <v>2086.0024038462</v>
       </c>
       <c r="P508" t="n">
         <v>3200</v>
@@ -22671,10 +22671,10 @@
         <v>15</v>
       </c>
       <c r="N521" t="n">
-        <v>2517.22</v>
+        <v>2545.636406397</v>
       </c>
       <c r="O521" t="n">
-        <v>37758.3</v>
+        <v>38184.546095955</v>
       </c>
       <c r="P521" t="n">
         <v>4200</v>
@@ -22706,22 +22706,22 @@
         <v>0</v>
       </c>
       <c r="L522" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M522" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N522" t="n">
         <v>2397</v>
       </c>
       <c r="O522" t="n">
-        <v>69513</v>
+        <v>64719</v>
       </c>
       <c r="P522" t="n">
         <v>2500</v>
       </c>
       <c r="Q522" t="n">
-        <v>72500</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="523">
@@ -23335,10 +23335,10 @@
         <v>36</v>
       </c>
       <c r="N537" t="n">
-        <v>24538.02</v>
+        <v>25442.647465438</v>
       </c>
       <c r="O537" t="n">
-        <v>883368.72</v>
+        <v>915935.308755768</v>
       </c>
       <c r="P537" t="n">
         <v>52900</v>
@@ -24886,22 +24886,22 @@
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M574" t="n">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="N574" t="n">
         <v>3877.89</v>
       </c>
       <c r="O574" t="n">
-        <v>1570545.45</v>
+        <v>1543400.22</v>
       </c>
       <c r="P574" t="n">
         <v>6500</v>
       </c>
       <c r="Q574" t="n">
-        <v>2632500</v>
+        <v>2587000</v>
       </c>
     </row>
     <row r="575">
@@ -24976,22 +24976,22 @@
         <v>0</v>
       </c>
       <c r="L576" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M576" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="N576" t="n">
-        <v>4285.1963420724</v>
+        <v>4285.1963819095</v>
       </c>
       <c r="O576" t="n">
-        <v>608497.8805742807</v>
+        <v>587071.9043216015</v>
       </c>
       <c r="P576" t="n">
         <v>6900</v>
       </c>
       <c r="Q576" t="n">
-        <v>979800</v>
+        <v>945300</v>
       </c>
     </row>
     <row r="577">
@@ -27128,22 +27128,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M627" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N627" t="n">
         <v>15137.62</v>
       </c>
       <c r="O627" t="n">
-        <v>136238.58</v>
+        <v>121100.96</v>
       </c>
       <c r="P627" t="n">
         <v>31500</v>
       </c>
       <c r="Q627" t="n">
-        <v>283500</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="628">
@@ -27948,10 +27948,10 @@
         <v>78</v>
       </c>
       <c r="N646" t="n">
-        <v>8332.779612403099</v>
+        <v>8332.7796073298</v>
       </c>
       <c r="O646" t="n">
-        <v>649956.8097674417</v>
+        <v>649956.8093717244</v>
       </c>
       <c r="P646" t="n">
         <v>14900</v>
@@ -28239,22 +28239,22 @@
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M653" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N653" t="n">
-        <v>1561.0051173709</v>
+        <v>1600.4118322476</v>
       </c>
       <c r="O653" t="n">
-        <v>167027.5475586863</v>
+        <v>169643.6542182456</v>
       </c>
       <c r="P653" t="n">
         <v>2900</v>
       </c>
       <c r="Q653" t="n">
-        <v>310300</v>
+        <v>307400</v>
       </c>
     </row>
     <row r="654">
@@ -28962,10 +28962,10 @@
         <v>165</v>
       </c>
       <c r="N670" t="n">
-        <v>7969.9501704105</v>
+        <v>7969.9501706749</v>
       </c>
       <c r="O670" t="n">
-        <v>1315041.778117732</v>
+        <v>1315041.778161359</v>
       </c>
       <c r="P670" t="n">
         <v>12900</v>
@@ -32006,22 +32006,22 @@
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M739" t="n">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="N739" t="n">
         <v>3486</v>
       </c>
       <c r="O739" t="n">
-        <v>2231040</v>
+        <v>2217096</v>
       </c>
       <c r="P739" t="n">
         <v>6900</v>
       </c>
       <c r="Q739" t="n">
-        <v>4416000</v>
+        <v>4388400</v>
       </c>
     </row>
     <row r="740">
@@ -32058,10 +32058,10 @@
         <v>1160</v>
       </c>
       <c r="N740" t="n">
-        <v>1778.4728413344</v>
+        <v>1778.4728487518</v>
       </c>
       <c r="O740" t="n">
-        <v>2063028.495947904</v>
+        <v>2063028.504552088</v>
       </c>
       <c r="P740" t="n">
         <v>4900</v>
@@ -32098,22 +32098,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M741" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="N741" t="n">
         <v>2325</v>
       </c>
       <c r="O741" t="n">
-        <v>702150</v>
+        <v>688200</v>
       </c>
       <c r="P741" t="n">
         <v>4900</v>
       </c>
       <c r="Q741" t="n">
-        <v>1479800</v>
+        <v>1450400</v>
       </c>
     </row>
     <row r="742">
@@ -34458,10 +34458,10 @@
         <v>93</v>
       </c>
       <c r="N792" t="n">
-        <v>2252.298328125</v>
+        <v>2252.2983673469</v>
       </c>
       <c r="O792" t="n">
-        <v>209463.744515625</v>
+        <v>209463.7481632617</v>
       </c>
       <c r="P792" t="n">
         <v>3900</v>
@@ -34915,22 +34915,22 @@
         <v>0</v>
       </c>
       <c r="L802" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M802" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N802" t="n">
         <v>3519</v>
       </c>
       <c r="O802" t="n">
-        <v>207621</v>
+        <v>204102</v>
       </c>
       <c r="P802" t="n">
         <v>5900</v>
       </c>
       <c r="Q802" t="n">
-        <v>348100</v>
+        <v>342200</v>
       </c>
     </row>
     <row r="803">
@@ -35473,10 +35473,10 @@
         <v>130</v>
       </c>
       <c r="N814" t="n">
-        <v>6414</v>
+        <v>6426.9445005045</v>
       </c>
       <c r="O814" t="n">
-        <v>833820</v>
+        <v>835502.785065585</v>
       </c>
       <c r="P814" t="n">
         <v>10900</v>
@@ -35703,10 +35703,10 @@
         <v>5</v>
       </c>
       <c r="N819" t="n">
-        <v>3903.7394479074</v>
+        <v>3903.7394652406</v>
       </c>
       <c r="O819" t="n">
-        <v>19518.697239537</v>
+        <v>19518.697326203</v>
       </c>
       <c r="P819" t="n">
         <v>7500</v>
@@ -36612,22 +36612,22 @@
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M839" t="n">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="N839" t="n">
         <v>7635</v>
       </c>
       <c r="O839" t="n">
-        <v>3412845</v>
+        <v>3389940</v>
       </c>
       <c r="P839" t="n">
         <v>13900</v>
       </c>
       <c r="Q839" t="n">
-        <v>6213300</v>
+        <v>6171600</v>
       </c>
     </row>
     <row r="840">
@@ -38641,10 +38641,10 @@
         <v>245</v>
       </c>
       <c r="N883" t="n">
-        <v>2458.5124311594</v>
+        <v>2458.5124201742</v>
       </c>
       <c r="O883" t="n">
-        <v>602335.5456340529</v>
+        <v>602335.542942679</v>
       </c>
       <c r="P883" t="n">
         <v>3500</v>
@@ -38687,10 +38687,10 @@
         <v>74</v>
       </c>
       <c r="N884" t="n">
-        <v>1771.0893441415</v>
+        <v>1771.0893205318</v>
       </c>
       <c r="O884" t="n">
-        <v>131060.611466471</v>
+        <v>131060.6097193532</v>
       </c>
       <c r="P884" t="n">
         <v>2500</v>
@@ -38779,10 +38779,10 @@
         <v>171</v>
       </c>
       <c r="N886" t="n">
-        <v>1803.0169781803</v>
+        <v>1803.0169868096</v>
       </c>
       <c r="O886" t="n">
-        <v>308315.9032688313</v>
+        <v>308315.9047444416</v>
       </c>
       <c r="P886" t="n">
         <v>2500</v>
@@ -39236,22 +39236,22 @@
         <v>0</v>
       </c>
       <c r="L896" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M896" t="n">
-        <v>344</v>
+        <v>307</v>
       </c>
       <c r="N896" t="n">
-        <v>1592.2838740157</v>
+        <v>1592.2847324415</v>
       </c>
       <c r="O896" t="n">
-        <v>547745.6526614007</v>
+        <v>488831.4128595405</v>
       </c>
       <c r="P896" t="n">
         <v>2500</v>
       </c>
       <c r="Q896" t="n">
-        <v>860000</v>
+        <v>767500</v>
       </c>
     </row>
     <row r="897">
@@ -39603,10 +39603,10 @@
         <v>1015</v>
       </c>
       <c r="N904" t="n">
-        <v>1259.2749291992</v>
+        <v>1262.9750514202</v>
       </c>
       <c r="O904" t="n">
-        <v>1278164.053137188</v>
+        <v>1281919.677191503</v>
       </c>
       <c r="P904" t="n">
         <v>1900</v>
@@ -40868,10 +40868,10 @@
         <v>321</v>
       </c>
       <c r="N931" t="n">
-        <v>1530.4499180664</v>
+        <v>1538.0108069164</v>
       </c>
       <c r="O931" t="n">
-        <v>491274.4236993144</v>
+        <v>493701.4690201644</v>
       </c>
       <c r="P931" t="n">
         <v>2600</v>
@@ -42157,22 +42157,22 @@
         <v>0</v>
       </c>
       <c r="L960" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M960" t="n">
-        <v>677</v>
+        <v>629</v>
       </c>
       <c r="N960" t="n">
-        <v>517.2950312417501</v>
+        <v>517.29511103247</v>
       </c>
       <c r="O960" t="n">
-        <v>350208.7361506648</v>
+        <v>325378.6248394236</v>
       </c>
       <c r="P960" t="n">
         <v>900</v>
       </c>
       <c r="Q960" t="n">
-        <v>609300</v>
+        <v>566100</v>
       </c>
     </row>
     <row r="961">
@@ -42348,10 +42348,10 @@
         <v>848</v>
       </c>
       <c r="N964" t="n">
-        <v>3110.8368831169</v>
+        <v>3110.8366754617</v>
       </c>
       <c r="O964" t="n">
-        <v>2637989.676883131</v>
+        <v>2637989.500791522</v>
       </c>
       <c r="P964" t="n">
         <v>4500</v>
@@ -42474,22 +42474,22 @@
         <v>0</v>
       </c>
       <c r="L967" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M967" t="n">
-        <v>12958</v>
+        <v>12910</v>
       </c>
       <c r="N967" t="n">
-        <v>703.7947376286299</v>
+        <v>703.79473431536</v>
       </c>
       <c r="O967" t="n">
-        <v>9119772.210191786</v>
+        <v>9085990.020011296</v>
       </c>
       <c r="P967" t="n">
         <v>900</v>
       </c>
       <c r="Q967" t="n">
-        <v>11662200</v>
+        <v>11619000</v>
       </c>
     </row>
     <row r="968">
@@ -47172,22 +47172,22 @@
         <v>0</v>
       </c>
       <c r="L1068" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1068" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N1068" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1068" t="n">
-        <v>1072150.56</v>
+        <v>1058405.04</v>
       </c>
       <c r="P1068" t="n">
         <v>7900</v>
       </c>
       <c r="Q1068" t="n">
-        <v>1848600</v>
+        <v>1824900</v>
       </c>
     </row>
     <row r="1069">
@@ -47221,22 +47221,22 @@
         <v>0</v>
       </c>
       <c r="L1069" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1069" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N1069" t="n">
         <v>3155</v>
       </c>
       <c r="O1069" t="n">
-        <v>1091630</v>
+        <v>1085320</v>
       </c>
       <c r="P1069" t="n">
         <v>5900</v>
       </c>
       <c r="Q1069" t="n">
-        <v>2041400</v>
+        <v>2029600</v>
       </c>
     </row>
     <row r="1070">
@@ -47276,10 +47276,10 @@
         <v>72</v>
       </c>
       <c r="N1070" t="n">
-        <v>430.60997530864</v>
+        <v>430.60997520149</v>
       </c>
       <c r="O1070" t="n">
-        <v>31003.91822222208</v>
+        <v>31003.91821450728</v>
       </c>
       <c r="P1070" t="n">
         <v>2200</v>
@@ -51064,10 +51064,10 @@
         <v>190</v>
       </c>
       <c r="N1156" t="n">
-        <v>6160</v>
+        <v>6202.5414364641</v>
       </c>
       <c r="O1156" t="n">
-        <v>1170400</v>
+        <v>1178482.872928179</v>
       </c>
       <c r="P1156" t="n">
         <v>7500</v>
@@ -53052,22 +53052,22 @@
         <v>0</v>
       </c>
       <c r="L1199" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1199" t="n">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="N1199" t="n">
-        <v>4687.974964965</v>
+        <v>4687.9750151668</v>
       </c>
       <c r="O1199" t="n">
-        <v>1959573.53535537</v>
+        <v>1912693.806188055</v>
       </c>
       <c r="P1199" t="n">
         <v>5500</v>
       </c>
       <c r="Q1199" t="n">
-        <v>2299000</v>
+        <v>2244000</v>
       </c>
     </row>
     <row r="1200">
@@ -53144,22 +53144,22 @@
         <v>0</v>
       </c>
       <c r="L1201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1201" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N1201" t="n">
         <v>7695.8</v>
       </c>
       <c r="O1201" t="n">
-        <v>623359.8</v>
+        <v>600272.4</v>
       </c>
       <c r="P1201" t="n">
         <v>11900</v>
       </c>
       <c r="Q1201" t="n">
-        <v>963900</v>
+        <v>928200</v>
       </c>
     </row>
     <row r="1202">
@@ -60790,10 +60790,10 @@
         <v>3</v>
       </c>
       <c r="N1386" t="n">
-        <v>1059.1847727273</v>
+        <v>1059.1855263158</v>
       </c>
       <c r="O1386" t="n">
-        <v>3177.5543181819</v>
+        <v>3177.5565789474</v>
       </c>
       <c r="P1386" t="n">
         <v>9500</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -2400,10 +2400,10 @@
         <v>7</v>
       </c>
       <c r="N49" t="n">
-        <v>1854.241047619</v>
+        <v>1854.2411004785</v>
       </c>
       <c r="O49" t="n">
-        <v>12979.687333333</v>
+        <v>12979.6877033495</v>
       </c>
       <c r="P49" t="n">
         <v>3200</v>
@@ -14952,22 +14952,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N343" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O343" t="n">
-        <v>4720535.924641539</v>
+        <v>4708113.46216973</v>
       </c>
       <c r="P343" t="n">
         <v>19900</v>
       </c>
       <c r="Q343" t="n">
-        <v>7562000</v>
+        <v>7542100</v>
       </c>
     </row>
     <row r="344">
@@ -16780,22 +16780,22 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M385" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N385" t="n">
         <v>13304.13</v>
       </c>
       <c r="O385" t="n">
-        <v>1782753.42</v>
+        <v>1756145.16</v>
       </c>
       <c r="P385" t="n">
         <v>20900</v>
       </c>
       <c r="Q385" t="n">
-        <v>2800600</v>
+        <v>2758800</v>
       </c>
     </row>
     <row r="386">
@@ -18158,22 +18158,22 @@
         <v>0</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M416" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N416" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="O416" t="n">
-        <v>447054.8533889328</v>
+        <v>444651.335230301</v>
       </c>
       <c r="P416" t="n">
         <v>3500</v>
       </c>
       <c r="Q416" t="n">
-        <v>651000</v>
+        <v>647500</v>
       </c>
     </row>
     <row r="417">
@@ -27719,22 +27719,22 @@
         <v>0</v>
       </c>
       <c r="L641" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M641" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N641" t="n">
         <v>16974.69</v>
       </c>
       <c r="O641" t="n">
-        <v>1137304.23</v>
+        <v>1103354.85</v>
       </c>
       <c r="P641" t="n">
         <v>26900</v>
       </c>
       <c r="Q641" t="n">
-        <v>1802300</v>
+        <v>1748500</v>
       </c>
     </row>
     <row r="642">
@@ -28011,22 +28011,22 @@
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M648" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N648" t="n">
         <v>19863.45</v>
       </c>
       <c r="O648" t="n">
-        <v>774674.55</v>
+        <v>754811.1</v>
       </c>
       <c r="P648" t="n">
         <v>37100</v>
       </c>
       <c r="Q648" t="n">
-        <v>1446900</v>
+        <v>1409800</v>
       </c>
     </row>
     <row r="649">
@@ -31134,22 +31134,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M720" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N720" t="n">
         <v>10161</v>
       </c>
       <c r="O720" t="n">
-        <v>487728</v>
+        <v>447084</v>
       </c>
       <c r="P720" t="n">
         <v>16900</v>
       </c>
       <c r="Q720" t="n">
-        <v>811200</v>
+        <v>743600</v>
       </c>
     </row>
     <row r="721">
@@ -39106,10 +39106,10 @@
         <v>273</v>
       </c>
       <c r="N893" t="n">
-        <v>1592.2857321429</v>
+        <v>1592.2857602862</v>
       </c>
       <c r="O893" t="n">
-        <v>434694.0048750117</v>
+        <v>434694.0125581326</v>
       </c>
       <c r="P893" t="n">
         <v>2500</v>
@@ -40016,22 +40016,22 @@
         <v>0</v>
       </c>
       <c r="L913" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M913" t="n">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="N913" t="n">
         <v>9736</v>
       </c>
       <c r="O913" t="n">
-        <v>6990448</v>
+        <v>6961240</v>
       </c>
       <c r="P913" t="n">
         <v>15900</v>
       </c>
       <c r="Q913" t="n">
-        <v>11416200</v>
+        <v>11368500</v>
       </c>
     </row>
     <row r="914">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -2592,22 +2592,22 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>6272.855198556</v>
+        <v>6272.8552079566</v>
       </c>
       <c r="O54" t="n">
-        <v>25091.420794224</v>
+        <v>18818.5656238698</v>
       </c>
       <c r="P54" t="n">
         <v>7900</v>
       </c>
       <c r="Q54" t="n">
-        <v>31600</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="55">
@@ -2636,22 +2636,22 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N55" t="n">
         <v>2445.67</v>
       </c>
       <c r="O55" t="n">
-        <v>39130.72</v>
+        <v>36685.05</v>
       </c>
       <c r="P55" t="n">
         <v>4600</v>
       </c>
       <c r="Q55" t="n">
-        <v>73600</v>
+        <v>69000</v>
       </c>
     </row>
     <row r="56">
@@ -3154,22 +3154,22 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N68" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O68" t="n">
-        <v>196965.5004262289</v>
+        <v>193249.1702463036</v>
       </c>
       <c r="P68" t="n">
         <v>9500</v>
       </c>
       <c r="Q68" t="n">
-        <v>503500</v>
+        <v>494000</v>
       </c>
     </row>
     <row r="69">
@@ -9189,22 +9189,22 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>9036</v>
+        <v>9035</v>
       </c>
       <c r="N210" t="n">
         <v>1726.32</v>
       </c>
       <c r="O210" t="n">
-        <v>15599027.52</v>
+        <v>15597301.2</v>
       </c>
       <c r="P210" t="n">
         <v>1500</v>
       </c>
       <c r="Q210" t="n">
-        <v>13554000</v>
+        <v>13552500</v>
       </c>
     </row>
     <row r="211">
@@ -14091,22 +14091,22 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M323" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="N323" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O323" t="n">
-        <v>1265177.031634771</v>
+        <v>1261582.776875456</v>
       </c>
       <c r="P323" t="n">
         <v>6500</v>
       </c>
       <c r="Q323" t="n">
-        <v>2288000</v>
+        <v>2281500</v>
       </c>
     </row>
     <row r="324">
@@ -14958,10 +14958,10 @@
         <v>379</v>
       </c>
       <c r="N343" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O343" t="n">
-        <v>4708113.472013118</v>
+        <v>4708113.473504483</v>
       </c>
       <c r="P343" t="n">
         <v>19900</v>
@@ -15397,22 +15397,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M353" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N353" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O353" t="n">
-        <v>155124.6607561158</v>
+        <v>149041.3407275422</v>
       </c>
       <c r="P353" t="n">
         <v>5500</v>
       </c>
       <c r="Q353" t="n">
-        <v>280500</v>
+        <v>269500</v>
       </c>
     </row>
     <row r="354">
@@ -15438,22 +15438,22 @@
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M354" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N354" t="n">
         <v>3981.47</v>
       </c>
       <c r="O354" t="n">
-        <v>342406.42</v>
+        <v>338424.95</v>
       </c>
       <c r="P354" t="n">
         <v>7000</v>
       </c>
       <c r="Q354" t="n">
-        <v>602000</v>
+        <v>595000</v>
       </c>
     </row>
     <row r="355">
@@ -17980,10 +17980,10 @@
         <v>94</v>
       </c>
       <c r="N412" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O412" t="n">
-        <v>153306.9199634844</v>
+        <v>153306.9215760544</v>
       </c>
       <c r="P412" t="n">
         <v>2500</v>
@@ -24840,22 +24840,22 @@
         <v>0</v>
       </c>
       <c r="L573" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M573" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N573" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O573" t="n">
-        <v>569931.1230808062</v>
+        <v>561360.7323797408</v>
       </c>
       <c r="P573" t="n">
         <v>6900</v>
       </c>
       <c r="Q573" t="n">
-        <v>917700</v>
+        <v>903900</v>
       </c>
     </row>
     <row r="574">
@@ -38369,10 +38369,10 @@
         <v>1242</v>
       </c>
       <c r="N877" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O877" t="n">
-        <v>1882920.109640537</v>
+        <v>1882920.103812328</v>
       </c>
       <c r="P877" t="n">
         <v>2300</v>
@@ -47137,22 +47137,22 @@
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1067" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N1067" t="n">
-        <v>465.87102642276</v>
+        <v>465.87102746694</v>
       </c>
       <c r="O1067" t="n">
-        <v>43791.87648373944</v>
+        <v>43326.00555442542</v>
       </c>
       <c r="P1067" t="n">
         <v>2500</v>
       </c>
       <c r="Q1067" t="n">
-        <v>235000</v>
+        <v>232500</v>
       </c>
     </row>
     <row r="1068">
@@ -52824,22 +52824,22 @@
         <v>0</v>
       </c>
       <c r="L1194" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1194" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N1194" t="n">
-        <v>2539.571774676</v>
+        <v>2539.5717817818</v>
       </c>
       <c r="O1194" t="n">
-        <v>546007.9315553401</v>
+        <v>535849.6459559598</v>
       </c>
       <c r="P1194" t="n">
         <v>2900</v>
       </c>
       <c r="Q1194" t="n">
-        <v>623500</v>
+        <v>611900</v>
       </c>
     </row>
     <row r="1195">
@@ -52916,22 +52916,22 @@
         <v>0</v>
       </c>
       <c r="L1196" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1196" t="n">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="N1196" t="n">
-        <v>4171.6684503311</v>
+        <v>4171.6684420772</v>
       </c>
       <c r="O1196" t="n">
-        <v>2169267.594172172</v>
+        <v>2152580.916111835</v>
       </c>
       <c r="P1196" t="n">
         <v>5000</v>
       </c>
       <c r="Q1196" t="n">
-        <v>2600000</v>
+        <v>2580000</v>
       </c>
     </row>
     <row r="1197">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -2642,10 +2642,10 @@
         <v>19</v>
       </c>
       <c r="N55" t="n">
-        <v>12357.960428571</v>
+        <v>12357.960431655</v>
       </c>
       <c r="O55" t="n">
-        <v>234801.248142849</v>
+        <v>234801.248201445</v>
       </c>
       <c r="P55" t="n">
         <v>15900</v>
@@ -3160,10 +3160,10 @@
         <v>138</v>
       </c>
       <c r="N68" t="n">
-        <v>2785.6243902439</v>
+        <v>2681</v>
       </c>
       <c r="O68" t="n">
-        <v>384416.1658536582</v>
+        <v>369978</v>
       </c>
       <c r="P68" t="n">
         <v>3500</v>
@@ -4896,10 +4896,10 @@
         <v>7</v>
       </c>
       <c r="N108" t="n">
-        <v>15711.963831169</v>
+        <v>15711.96379085</v>
       </c>
       <c r="O108" t="n">
-        <v>109983.746818183</v>
+        <v>109983.74653595</v>
       </c>
       <c r="P108" t="n">
         <v>28500</v>
@@ -7136,10 +7136,10 @@
         <v>199</v>
       </c>
       <c r="N162" t="n">
-        <v>2584.1380683507</v>
+        <v>2572.67</v>
       </c>
       <c r="O162" t="n">
-        <v>514243.4756017893</v>
+        <v>511961.33</v>
       </c>
       <c r="P162" t="n">
         <v>4700</v>
@@ -9026,22 +9026,22 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M206" t="n">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="N206" t="n">
         <v>2833</v>
       </c>
       <c r="O206" t="n">
-        <v>1662971</v>
+        <v>1654472</v>
       </c>
       <c r="P206" t="n">
         <v>3500</v>
       </c>
       <c r="Q206" t="n">
-        <v>2054500</v>
+        <v>2044000</v>
       </c>
     </row>
     <row r="207">
@@ -9195,22 +9195,22 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M210" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="N210" t="n">
-        <v>4937.3101733649</v>
+        <v>4937.3101737757</v>
       </c>
       <c r="O210" t="n">
-        <v>898590.4515524118</v>
+        <v>883778.5211058502</v>
       </c>
       <c r="P210" t="n">
         <v>7500</v>
       </c>
       <c r="Q210" t="n">
-        <v>1365000</v>
+        <v>1342500</v>
       </c>
     </row>
     <row r="211">
@@ -9659,22 +9659,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M221" t="n">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="N221" t="n">
-        <v>1108.8838530981</v>
+        <v>1098.0703134021</v>
       </c>
       <c r="O221" t="n">
-        <v>787307.535699651</v>
+        <v>766453.0787546658</v>
       </c>
       <c r="P221" t="n">
         <v>1500</v>
       </c>
       <c r="Q221" t="n">
-        <v>1065000</v>
+        <v>1047000</v>
       </c>
     </row>
     <row r="222">
@@ -10672,10 +10672,10 @@
         <v>4</v>
       </c>
       <c r="N245" t="n">
-        <v>13261.303571429</v>
+        <v>12587</v>
       </c>
       <c r="O245" t="n">
-        <v>53045.214285716</v>
+        <v>50348</v>
       </c>
       <c r="P245" t="n">
         <v>18900</v>
@@ -11447,22 +11447,22 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M263" t="n">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="N263" t="n">
-        <v>2582.2548633316</v>
+        <v>2582.2548540429</v>
       </c>
       <c r="O263" t="n">
-        <v>1427986.939422375</v>
+        <v>1417657.914869552</v>
       </c>
       <c r="P263" t="n">
         <v>4500</v>
       </c>
       <c r="Q263" t="n">
-        <v>2488500</v>
+        <v>2470500</v>
       </c>
     </row>
     <row r="264">
@@ -12285,10 +12285,10 @@
         <v>279</v>
       </c>
       <c r="N282" t="n">
-        <v>1482.2572445348</v>
+        <v>1480</v>
       </c>
       <c r="O282" t="n">
-        <v>413549.7712252092</v>
+        <v>412920</v>
       </c>
       <c r="P282" t="n">
         <v>2600</v>
@@ -12504,22 +12504,22 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N287" t="n">
         <v>7507.39</v>
       </c>
       <c r="O287" t="n">
-        <v>2064532.25</v>
+        <v>2057024.86</v>
       </c>
       <c r="P287" t="n">
         <v>13500</v>
       </c>
       <c r="Q287" t="n">
-        <v>3712500</v>
+        <v>3699000</v>
       </c>
     </row>
     <row r="288">
@@ -12553,22 +12553,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M288" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N288" t="n">
         <v>9664</v>
       </c>
       <c r="O288" t="n">
-        <v>202944</v>
+        <v>193280</v>
       </c>
       <c r="P288" t="n">
         <v>15900</v>
       </c>
       <c r="Q288" t="n">
-        <v>333900</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="289">
@@ -13211,22 +13211,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N303" t="n">
-        <v>4890.9300540176</v>
+        <v>4890.9300540541</v>
       </c>
       <c r="O303" t="n">
-        <v>1423260.645719122</v>
+        <v>1418369.715675689</v>
       </c>
       <c r="P303" t="n">
         <v>8200</v>
       </c>
       <c r="Q303" t="n">
-        <v>2386200</v>
+        <v>2378000</v>
       </c>
     </row>
     <row r="304">
@@ -13306,22 +13306,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M305" t="n">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="N305" t="n">
         <v>1203.38</v>
       </c>
       <c r="O305" t="n">
-        <v>302048.38</v>
+        <v>280387.54</v>
       </c>
       <c r="P305" t="n">
         <v>1900</v>
       </c>
       <c r="Q305" t="n">
-        <v>476900</v>
+        <v>442700</v>
       </c>
     </row>
     <row r="306">
@@ -13659,22 +13659,22 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M313" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N313" t="n">
-        <v>7063.376059322</v>
+        <v>7041</v>
       </c>
       <c r="O313" t="n">
-        <v>268408.290254236</v>
+        <v>260517</v>
       </c>
       <c r="P313" t="n">
         <v>11500</v>
       </c>
       <c r="Q313" t="n">
-        <v>437000</v>
+        <v>425500</v>
       </c>
     </row>
     <row r="314">
@@ -14016,10 +14016,10 @@
         <v>351</v>
       </c>
       <c r="N321" t="n">
-        <v>3594.2528730512</v>
+        <v>3594.2528624535</v>
       </c>
       <c r="O321" t="n">
-        <v>1261582.758440971</v>
+        <v>1261582.754721178</v>
       </c>
       <c r="P321" t="n">
         <v>6500</v>
@@ -14188,10 +14188,10 @@
         <v>1</v>
       </c>
       <c r="N325" t="n">
-        <v>3354.2325655977</v>
+        <v>3240.850058309</v>
       </c>
       <c r="O325" t="n">
-        <v>3354.2325655977</v>
+        <v>3240.850058309</v>
       </c>
       <c r="P325" t="n">
         <v>5200</v>
@@ -14455,10 +14455,10 @@
         <v>6254</v>
       </c>
       <c r="N331" t="n">
-        <v>2093.3158067369</v>
+        <v>2090.85</v>
       </c>
       <c r="O331" t="n">
-        <v>13091597.05533257</v>
+        <v>13076175.9</v>
       </c>
       <c r="P331" t="n">
         <v>2900</v>
@@ -15008,10 +15008,10 @@
         <v>2490</v>
       </c>
       <c r="N344" t="n">
-        <v>3472.276319645</v>
+        <v>3472.276322317</v>
       </c>
       <c r="O344" t="n">
-        <v>8645968.035916051</v>
+        <v>8645968.04256933</v>
       </c>
       <c r="P344" t="n">
         <v>5900</v>
@@ -15575,22 +15575,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M357" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.5646884576</v>
+        <v>1592.5646666667</v>
       </c>
       <c r="O357" t="n">
-        <v>441140.4187027552</v>
+        <v>437955.2833333425</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
       </c>
       <c r="Q357" t="n">
-        <v>1080300</v>
+        <v>1072500</v>
       </c>
     </row>
     <row r="358">
@@ -15663,10 +15663,10 @@
         <v>2</v>
       </c>
       <c r="N359" t="n">
-        <v>2231.2604819277</v>
+        <v>2224.56</v>
       </c>
       <c r="O359" t="n">
-        <v>4462.5209638554</v>
+        <v>4449.12</v>
       </c>
       <c r="P359" t="n">
         <v>3900</v>
@@ -16180,22 +16180,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M371" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N371" t="n">
         <v>4648.6</v>
       </c>
       <c r="O371" t="n">
-        <v>962260.2000000001</v>
+        <v>943665.8</v>
       </c>
       <c r="P371" t="n">
         <v>8900</v>
       </c>
       <c r="Q371" t="n">
-        <v>1842300</v>
+        <v>1806700</v>
       </c>
     </row>
     <row r="372">
@@ -16485,10 +16485,10 @@
         <v>1</v>
       </c>
       <c r="N378" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O378" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="P378" t="n">
         <v>16900</v>
@@ -16523,22 +16523,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M379" t="n">
-        <v>2043</v>
+        <v>2035</v>
       </c>
       <c r="N379" t="n">
         <v>1387.55</v>
       </c>
       <c r="O379" t="n">
-        <v>2834764.65</v>
+        <v>2823664.25</v>
       </c>
       <c r="P379" t="n">
         <v>2300</v>
       </c>
       <c r="Q379" t="n">
-        <v>4698900</v>
+        <v>4680500</v>
       </c>
     </row>
     <row r="380">
@@ -17893,22 +17893,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M410" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N410" t="n">
-        <v>1630.9247235872</v>
+        <v>1630.9247279434</v>
       </c>
       <c r="O410" t="n">
-        <v>145152.3003992608</v>
+        <v>140259.5266031324</v>
       </c>
       <c r="P410" t="n">
         <v>2500</v>
       </c>
       <c r="Q410" t="n">
-        <v>222500</v>
+        <v>215000</v>
       </c>
     </row>
     <row r="411">
@@ -18077,22 +18077,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M414" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="N414" t="n">
-        <v>2403.5218851304</v>
+        <v>2403.5220092133</v>
       </c>
       <c r="O414" t="n">
-        <v>322071.9326074736</v>
+        <v>286019.1190963827</v>
       </c>
       <c r="P414" t="n">
         <v>3500</v>
       </c>
       <c r="Q414" t="n">
-        <v>469000</v>
+        <v>416500</v>
       </c>
     </row>
     <row r="415">
@@ -21986,22 +21986,22 @@
         <v>0</v>
       </c>
       <c r="L505" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M505" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N505" t="n">
         <v>1969</v>
       </c>
       <c r="O505" t="n">
-        <v>291412</v>
+        <v>287474</v>
       </c>
       <c r="P505" t="n">
         <v>1500</v>
       </c>
       <c r="Q505" t="n">
-        <v>222000</v>
+        <v>219000</v>
       </c>
     </row>
     <row r="506">
@@ -24418,22 +24418,22 @@
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M563" t="n">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="N563" t="n">
-        <v>6207.988218663</v>
+        <v>6207.9882181666</v>
       </c>
       <c r="O563" t="n">
-        <v>7449585.8623956</v>
+        <v>7437169.885363586</v>
       </c>
       <c r="P563" t="n">
         <v>9900</v>
       </c>
       <c r="Q563" t="n">
-        <v>11880000</v>
+        <v>11860200</v>
       </c>
     </row>
     <row r="564">
@@ -25264,22 +25264,22 @@
         <v>0</v>
       </c>
       <c r="L583" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M583" t="n">
-        <v>14105</v>
+        <v>14102</v>
       </c>
       <c r="N583" t="n">
-        <v>4814.2679247144</v>
+        <v>4814.2679243911</v>
       </c>
       <c r="O583" t="n">
-        <v>67905249.07809661</v>
+        <v>67890806.26976329</v>
       </c>
       <c r="P583" t="n">
         <v>9900</v>
       </c>
       <c r="Q583" t="n">
-        <v>139639500</v>
+        <v>139609800</v>
       </c>
     </row>
     <row r="584">
@@ -26870,22 +26870,22 @@
         <v>0</v>
       </c>
       <c r="L621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M621" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N621" t="n">
         <v>4793.53</v>
       </c>
       <c r="O621" t="n">
-        <v>1596245.49</v>
+        <v>1591451.96</v>
       </c>
       <c r="P621" t="n">
         <v>7900</v>
       </c>
       <c r="Q621" t="n">
-        <v>2630700</v>
+        <v>2622800</v>
       </c>
     </row>
     <row r="622">
@@ -27224,10 +27224,10 @@
         <v>1</v>
       </c>
       <c r="N629" t="n">
-        <v>14744.236363636</v>
+        <v>13515.55</v>
       </c>
       <c r="O629" t="n">
-        <v>14744.236363636</v>
+        <v>13515.55</v>
       </c>
       <c r="P629" t="n">
         <v>30900</v>
@@ -28022,22 +28022,22 @@
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M648" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N648" t="n">
-        <v>1561.0061538462</v>
+        <v>1561.0062900506</v>
       </c>
       <c r="O648" t="n">
-        <v>109270.430769234</v>
+        <v>93660.37740303599</v>
       </c>
       <c r="P648" t="n">
         <v>2900</v>
       </c>
       <c r="Q648" t="n">
-        <v>203000</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="649">
@@ -31289,10 +31289,10 @@
         <v>2</v>
       </c>
       <c r="N723" t="n">
-        <v>18873.018181818</v>
+        <v>18536</v>
       </c>
       <c r="O723" t="n">
-        <v>37746.036363636</v>
+        <v>37072</v>
       </c>
       <c r="P723" t="n">
         <v>30900</v>
@@ -32258,10 +32258,10 @@
         <v>71</v>
       </c>
       <c r="N744" t="n">
-        <v>5188.8571428571</v>
+        <v>5148</v>
       </c>
       <c r="O744" t="n">
-        <v>368408.8571428541</v>
+        <v>365508</v>
       </c>
       <c r="P744" t="n">
         <v>8600</v>
@@ -34514,22 +34514,22 @@
         <v>0</v>
       </c>
       <c r="L793" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M793" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N793" t="n">
         <v>21676</v>
       </c>
       <c r="O793" t="n">
-        <v>1842460</v>
+        <v>1820784</v>
       </c>
       <c r="P793" t="n">
         <v>34900</v>
       </c>
       <c r="Q793" t="n">
-        <v>2966500</v>
+        <v>2931600</v>
       </c>
     </row>
     <row r="794">
@@ -35521,22 +35521,22 @@
         <v>0</v>
       </c>
       <c r="L815" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M815" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N815" t="n">
         <v>20731</v>
       </c>
       <c r="O815" t="n">
-        <v>539006</v>
+        <v>518275</v>
       </c>
       <c r="P815" t="n">
         <v>33900</v>
       </c>
       <c r="Q815" t="n">
-        <v>881400</v>
+        <v>847500</v>
       </c>
     </row>
     <row r="816">
@@ -35849,10 +35849,10 @@
         <v>252</v>
       </c>
       <c r="N822" t="n">
-        <v>2636.2357798165</v>
+        <v>2629</v>
       </c>
       <c r="O822" t="n">
-        <v>664331.416513758</v>
+        <v>662508</v>
       </c>
       <c r="P822" t="n">
         <v>4500</v>
@@ -37086,10 +37086,10 @@
         <v>65</v>
       </c>
       <c r="N849" t="n">
-        <v>18170.288401254</v>
+        <v>18001</v>
       </c>
       <c r="O849" t="n">
-        <v>1181068.74608151</v>
+        <v>1170065</v>
       </c>
       <c r="P849" t="n">
         <v>28900</v>
@@ -37733,10 +37733,10 @@
         <v>16</v>
       </c>
       <c r="N863" t="n">
-        <v>10795.831156812</v>
+        <v>10713.21</v>
       </c>
       <c r="O863" t="n">
-        <v>172733.298508992</v>
+        <v>171411.36</v>
       </c>
       <c r="P863" t="n">
         <v>20900</v>
@@ -38282,22 +38282,22 @@
         <v>0</v>
       </c>
       <c r="L875" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M875" t="n">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="N875" t="n">
-        <v>1516.0387131507</v>
+        <v>1516.0387126124</v>
       </c>
       <c r="O875" t="n">
-        <v>1878371.965593717</v>
+        <v>1872307.810076314</v>
       </c>
       <c r="P875" t="n">
         <v>2300</v>
       </c>
       <c r="Q875" t="n">
-        <v>2849700</v>
+        <v>2840500</v>
       </c>
     </row>
     <row r="876">
@@ -38973,22 +38973,22 @@
         <v>0</v>
       </c>
       <c r="L890" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M890" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="N890" t="n">
-        <v>1592.2864981273</v>
+        <v>1592.2866856061</v>
       </c>
       <c r="O890" t="n">
-        <v>413994.489513098</v>
+        <v>404440.8181439494</v>
       </c>
       <c r="P890" t="n">
         <v>2500</v>
       </c>
       <c r="Q890" t="n">
-        <v>650000</v>
+        <v>635000</v>
       </c>
     </row>
     <row r="891">
@@ -39242,22 +39242,22 @@
         <v>0</v>
       </c>
       <c r="L896" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M896" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N896" t="n">
-        <v>1693.5530348259</v>
+        <v>1668.6492929293</v>
       </c>
       <c r="O896" t="n">
-        <v>277742.6977114476</v>
+        <v>268652.5361616173</v>
       </c>
       <c r="P896" t="n">
         <v>2500</v>
       </c>
       <c r="Q896" t="n">
-        <v>410000</v>
+        <v>402500</v>
       </c>
     </row>
     <row r="897">
@@ -39557,22 +39557,22 @@
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M903" t="n">
-        <v>2410</v>
+        <v>2398</v>
       </c>
       <c r="N903" t="n">
-        <v>692.15249234096</v>
+        <v>692.15249774246</v>
       </c>
       <c r="O903" t="n">
-        <v>1668087.506541713</v>
+        <v>1659781.689586419</v>
       </c>
       <c r="P903" t="n">
         <v>1200</v>
       </c>
       <c r="Q903" t="n">
-        <v>2892000</v>
+        <v>2877600</v>
       </c>
     </row>
     <row r="904">
@@ -39612,10 +39612,10 @@
         <v>3</v>
       </c>
       <c r="N904" t="n">
-        <v>19051.333333333</v>
+        <v>18491</v>
       </c>
       <c r="O904" t="n">
-        <v>57153.999999999</v>
+        <v>55473</v>
       </c>
       <c r="P904" t="n">
         <v>13500</v>
@@ -39987,22 +39987,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M912" t="n">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="N912" t="n">
         <v>5215</v>
       </c>
       <c r="O912" t="n">
-        <v>6138055</v>
+        <v>6117195</v>
       </c>
       <c r="P912" t="n">
         <v>8900</v>
       </c>
       <c r="Q912" t="n">
-        <v>10475300</v>
+        <v>10439700</v>
       </c>
     </row>
     <row r="913">
@@ -40135,10 +40135,10 @@
         <v>1</v>
       </c>
       <c r="N915" t="n">
-        <v>5510.92</v>
+        <v>6178.9103030303</v>
       </c>
       <c r="O915" t="n">
-        <v>5510.92</v>
+        <v>6178.9103030303</v>
       </c>
       <c r="P915" t="n">
         <v>4900</v>
@@ -41593,10 +41593,10 @@
         <v>10</v>
       </c>
       <c r="N947" t="n">
-        <v>1333.9879518072</v>
+        <v>1326</v>
       </c>
       <c r="O947" t="n">
-        <v>13339.879518072</v>
+        <v>13260</v>
       </c>
       <c r="P947" t="n">
         <v>2900</v>
@@ -41894,22 +41894,22 @@
         <v>0</v>
       </c>
       <c r="L954" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M954" t="n">
-        <v>601</v>
+        <v>556</v>
       </c>
       <c r="N954" t="n">
-        <v>517.29622957051</v>
+        <v>517.29632575033</v>
       </c>
       <c r="O954" t="n">
-        <v>310895.0339718765</v>
+        <v>287616.7571171835</v>
       </c>
       <c r="P954" t="n">
         <v>900</v>
       </c>
       <c r="Q954" t="n">
-        <v>540900</v>
+        <v>500400</v>
       </c>
     </row>
     <row r="955">
@@ -42211,22 +42211,22 @@
         <v>0</v>
       </c>
       <c r="L961" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M961" t="n">
-        <v>12785</v>
+        <v>12770</v>
       </c>
       <c r="N961" t="n">
-        <v>703.79465893216</v>
+        <v>703.79465786602</v>
       </c>
       <c r="O961" t="n">
-        <v>8998014.714447666</v>
+        <v>8987457.780949075</v>
       </c>
       <c r="P961" t="n">
         <v>900</v>
       </c>
       <c r="Q961" t="n">
-        <v>11506500</v>
+        <v>11493000</v>
       </c>
     </row>
     <row r="962">
@@ -42697,22 +42697,22 @@
         <v>0</v>
       </c>
       <c r="L972" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M972" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N972" t="n">
-        <v>2077.4948837209</v>
+        <v>2077.4948989114</v>
       </c>
       <c r="O972" t="n">
-        <v>853850.3972092898</v>
+        <v>849695.4136547626</v>
       </c>
       <c r="P972" t="n">
         <v>2900</v>
       </c>
       <c r="Q972" t="n">
-        <v>1191900</v>
+        <v>1186100</v>
       </c>
     </row>
     <row r="973">
@@ -42960,10 +42960,10 @@
         <v>81</v>
       </c>
       <c r="N978" t="n">
-        <v>1595.4982940252</v>
+        <v>1595.4982440945</v>
       </c>
       <c r="O978" t="n">
-        <v>129235.3618160412</v>
+        <v>129235.3577716545</v>
       </c>
       <c r="P978" t="n">
         <v>2500</v>
@@ -48339,22 +48339,22 @@
         <v>0</v>
       </c>
       <c r="L1095" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M1095" t="n">
-        <v>1311</v>
+        <v>1297</v>
       </c>
       <c r="N1095" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1095" t="n">
-        <v>1542483.27</v>
+        <v>1526011.29</v>
       </c>
       <c r="P1095" t="n">
         <v>1900</v>
       </c>
       <c r="Q1095" t="n">
-        <v>2490900</v>
+        <v>2464300</v>
       </c>
     </row>
     <row r="1096">
@@ -49163,22 +49163,22 @@
         <v>0</v>
       </c>
       <c r="L1114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1114" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N1114" t="n">
         <v>9261</v>
       </c>
       <c r="O1114" t="n">
-        <v>537138</v>
+        <v>509355</v>
       </c>
       <c r="P1114" t="n">
         <v>4900</v>
       </c>
       <c r="Q1114" t="n">
-        <v>284200</v>
+        <v>269500</v>
       </c>
     </row>
     <row r="1115">
@@ -49566,22 +49566,22 @@
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1123" t="n">
-        <v>1757.3206341463</v>
+        <v>1757.3206356968</v>
       </c>
       <c r="O1123" t="n">
-        <v>1757.3206341463</v>
+        <v>0</v>
       </c>
       <c r="P1123" t="n">
         <v>2000</v>
       </c>
       <c r="Q1123" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1124">
@@ -50659,22 +50659,22 @@
         <v>0</v>
       </c>
       <c r="L1147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N1147" t="n">
         <v>5280</v>
       </c>
       <c r="O1147" t="n">
-        <v>15840</v>
+        <v>0</v>
       </c>
       <c r="P1147" t="n">
         <v>6900</v>
       </c>
       <c r="Q1147" t="n">
-        <v>20700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1148">
@@ -50751,22 +50751,22 @@
         <v>0</v>
       </c>
       <c r="L1149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1149" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N1149" t="n">
         <v>6160</v>
       </c>
       <c r="O1149" t="n">
-        <v>942480</v>
+        <v>924000</v>
       </c>
       <c r="P1149" t="n">
         <v>7500</v>
       </c>
       <c r="Q1149" t="n">
-        <v>1147500</v>
+        <v>1125000</v>
       </c>
     </row>
     <row r="1150">
@@ -50800,22 +50800,22 @@
         <v>0</v>
       </c>
       <c r="L1150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1150" t="n">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="N1150" t="n">
         <v>1056</v>
       </c>
       <c r="O1150" t="n">
-        <v>1176384</v>
+        <v>1173216</v>
       </c>
       <c r="P1150" t="n">
         <v>1400</v>
       </c>
       <c r="Q1150" t="n">
-        <v>1559600</v>
+        <v>1555400</v>
       </c>
     </row>
     <row r="1151">
@@ -51079,22 +51079,22 @@
         <v>0</v>
       </c>
       <c r="L1156" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1156" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N1156" t="n">
         <v>4576</v>
       </c>
       <c r="O1156" t="n">
-        <v>420992</v>
+        <v>366080</v>
       </c>
       <c r="P1156" t="n">
         <v>5900</v>
       </c>
       <c r="Q1156" t="n">
-        <v>542800</v>
+        <v>472000</v>
       </c>
     </row>
     <row r="1157">
@@ -51125,22 +51125,22 @@
         <v>0</v>
       </c>
       <c r="L1157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1157" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N1157" t="n">
         <v>5280</v>
       </c>
       <c r="O1157" t="n">
-        <v>211200</v>
+        <v>200640</v>
       </c>
       <c r="P1157" t="n">
         <v>6900</v>
       </c>
       <c r="Q1157" t="n">
-        <v>276000</v>
+        <v>262200</v>
       </c>
     </row>
     <row r="1158">
@@ -52794,22 +52794,22 @@
         <v>0</v>
       </c>
       <c r="L1193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1193" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N1193" t="n">
-        <v>4687.9753161844</v>
+        <v>4687.9753276047</v>
       </c>
       <c r="O1193" t="n">
-        <v>1650167.311296909</v>
+        <v>1640791.364661645</v>
       </c>
       <c r="P1193" t="n">
         <v>5500</v>
       </c>
       <c r="Q1193" t="n">
-        <v>1936000</v>
+        <v>1925000</v>
       </c>
     </row>
     <row r="1194">
@@ -60578,10 +60578,10 @@
         <v>7</v>
       </c>
       <c r="N1381" t="n">
-        <v>345.26651452282</v>
+        <v>341.02145228216</v>
       </c>
       <c r="O1381" t="n">
-        <v>2416.86560165974</v>
+        <v>2387.15016597512</v>
       </c>
       <c r="P1381" t="n">
         <v>14500</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -10533,22 +10533,22 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M242" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N242" t="n">
         <v>3395</v>
       </c>
       <c r="O242" t="n">
-        <v>420980</v>
+        <v>414190</v>
       </c>
       <c r="P242" t="n">
         <v>5500</v>
       </c>
       <c r="Q242" t="n">
-        <v>682000</v>
+        <v>671000</v>
       </c>
     </row>
     <row r="243">
@@ -21319,22 +21319,22 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M489" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N489" t="n">
         <v>9338</v>
       </c>
       <c r="O489" t="n">
-        <v>242788</v>
+        <v>233450</v>
       </c>
       <c r="P489" t="n">
         <v>15500</v>
       </c>
       <c r="Q489" t="n">
-        <v>403000</v>
+        <v>387500</v>
       </c>
     </row>
     <row r="490">
@@ -30091,22 +30091,22 @@
         <v>0</v>
       </c>
       <c r="L697" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M697" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N697" t="n">
         <v>5164.33</v>
       </c>
       <c r="O697" t="n">
-        <v>418310.73</v>
+        <v>407982.07</v>
       </c>
       <c r="P697" t="n">
         <v>10200</v>
       </c>
       <c r="Q697" t="n">
-        <v>826200</v>
+        <v>805800</v>
       </c>
     </row>
     <row r="698">
@@ -37175,22 +37175,22 @@
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M851" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N851" t="n">
-        <v>10755</v>
+        <v>10795.738636364</v>
       </c>
       <c r="O851" t="n">
-        <v>1817595</v>
+        <v>1781296.87500006</v>
       </c>
       <c r="P851" t="n">
         <v>17900</v>
       </c>
       <c r="Q851" t="n">
-        <v>3025100</v>
+        <v>2953500</v>
       </c>
     </row>
     <row r="852">
@@ -42171,10 +42171,10 @@
         <v>12731</v>
       </c>
       <c r="N960" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O960" t="n">
-        <v>8960009.527635749</v>
+        <v>8960009.505740212</v>
       </c>
       <c r="P960" t="n">
         <v>900</v>
@@ -49518,22 +49518,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M1122" t="n">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="N1122" t="n">
         <v>1760</v>
       </c>
       <c r="O1122" t="n">
-        <v>517440</v>
+        <v>482240</v>
       </c>
       <c r="P1122" t="n">
         <v>2300</v>
       </c>
       <c r="Q1122" t="n">
-        <v>676200</v>
+        <v>630200</v>
       </c>
     </row>
     <row r="1123">
@@ -52697,22 +52697,22 @@
         <v>0</v>
       </c>
       <c r="L1191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1191" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N1191" t="n">
-        <v>4171.6683165468</v>
+        <v>4171.668314121</v>
       </c>
       <c r="O1191" t="n">
-        <v>1994057.455309371</v>
+        <v>1989885.785835717</v>
       </c>
       <c r="P1191" t="n">
         <v>5000</v>
       </c>
       <c r="Q1191" t="n">
-        <v>2390000</v>
+        <v>2385000</v>
       </c>
     </row>
     <row r="1192">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -2404,22 +2404,22 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N49" t="n">
         <v>4604.2</v>
       </c>
       <c r="O49" t="n">
-        <v>1326009.6</v>
+        <v>1312197</v>
       </c>
       <c r="P49" t="n">
         <v>7500</v>
       </c>
       <c r="Q49" t="n">
-        <v>2160000</v>
+        <v>2137500</v>
       </c>
     </row>
     <row r="50">
@@ -2600,22 +2600,22 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="N54" t="n">
         <v>3585</v>
       </c>
       <c r="O54" t="n">
-        <v>351330</v>
+        <v>340575</v>
       </c>
       <c r="P54" t="n">
         <v>4500</v>
       </c>
       <c r="Q54" t="n">
-        <v>441000</v>
+        <v>427500</v>
       </c>
     </row>
     <row r="55">
@@ -2722,22 +2722,22 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M57" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N57" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O57" t="n">
-        <v>70683.0672803346</v>
+        <v>58902.555997905</v>
       </c>
       <c r="P57" t="n">
         <v>4800</v>
       </c>
       <c r="Q57" t="n">
-        <v>86400</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="58">
@@ -3045,22 +3045,22 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N65" t="n">
         <v>3526.1</v>
       </c>
       <c r="O65" t="n">
-        <v>169252.8</v>
+        <v>162200.6</v>
       </c>
       <c r="P65" t="n">
         <v>6300</v>
       </c>
       <c r="Q65" t="n">
-        <v>302400</v>
+        <v>289800</v>
       </c>
     </row>
     <row r="66">
@@ -3162,22 +3162,22 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N68" t="n">
-        <v>3716.3301970443</v>
+        <v>3716.3301973684</v>
       </c>
       <c r="O68" t="n">
-        <v>193249.1702463036</v>
+        <v>189532.8400657884</v>
       </c>
       <c r="P68" t="n">
         <v>9500</v>
       </c>
       <c r="Q68" t="n">
-        <v>494000</v>
+        <v>484500</v>
       </c>
     </row>
     <row r="69">
@@ -6958,22 +6958,22 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M158" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="N158" t="n">
         <v>3865.67</v>
       </c>
       <c r="O158" t="n">
-        <v>1105581.62</v>
+        <v>1093984.61</v>
       </c>
       <c r="P158" t="n">
         <v>5500</v>
       </c>
       <c r="Q158" t="n">
-        <v>1573000</v>
+        <v>1556500</v>
       </c>
     </row>
     <row r="159">
@@ -7530,22 +7530,22 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M171" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N171" t="n">
         <v>3114.49</v>
       </c>
       <c r="O171" t="n">
-        <v>146381.03</v>
+        <v>137037.56</v>
       </c>
       <c r="P171" t="n">
         <v>5500</v>
       </c>
       <c r="Q171" t="n">
-        <v>258500</v>
+        <v>242000</v>
       </c>
     </row>
     <row r="172">
@@ -9031,22 +9031,22 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M206" t="n">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="N206" t="n">
         <v>2833</v>
       </c>
       <c r="O206" t="n">
-        <v>1654472</v>
+        <v>1637474</v>
       </c>
       <c r="P206" t="n">
         <v>3500</v>
       </c>
       <c r="Q206" t="n">
-        <v>2044000</v>
+        <v>2023000</v>
       </c>
     </row>
     <row r="207">
@@ -9078,10 +9078,10 @@
         <v>12</v>
       </c>
       <c r="N207" t="n">
-        <v>33815</v>
+        <v>41061.071428571</v>
       </c>
       <c r="O207" t="n">
-        <v>405780</v>
+        <v>492732.857142852</v>
       </c>
       <c r="P207" t="n">
         <v>47900</v>
@@ -9670,10 +9670,10 @@
         <v>585</v>
       </c>
       <c r="N221" t="n">
-        <v>1098.072297891</v>
+        <v>1098.0725121628</v>
       </c>
       <c r="O221" t="n">
-        <v>642372.2942662351</v>
+        <v>642372.419615238</v>
       </c>
       <c r="P221" t="n">
         <v>1500</v>
@@ -11452,22 +11452,22 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M263" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="N263" t="n">
-        <v>2582.2548125</v>
+        <v>2582.2547989556</v>
       </c>
       <c r="O263" t="n">
-        <v>1409911.127625</v>
+        <v>1389253.081838113</v>
       </c>
       <c r="P263" t="n">
         <v>4500</v>
       </c>
       <c r="Q263" t="n">
-        <v>2457000</v>
+        <v>2421000</v>
       </c>
     </row>
     <row r="264">
@@ -12162,10 +12162,10 @@
         <v>52</v>
       </c>
       <c r="N279" t="n">
-        <v>3230.0657538462</v>
+        <v>3230.0657009346</v>
       </c>
       <c r="O279" t="n">
-        <v>167963.4192000024</v>
+        <v>167963.4164485992</v>
       </c>
       <c r="P279" t="n">
         <v>6200</v>
@@ -13216,22 +13216,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M303" t="n">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="N303" t="n">
-        <v>4890.9300552868</v>
+        <v>4890.930055517</v>
       </c>
       <c r="O303" t="n">
-        <v>1418369.716033172</v>
+        <v>1389024.135766828</v>
       </c>
       <c r="P303" t="n">
         <v>8200</v>
       </c>
       <c r="Q303" t="n">
-        <v>2378000</v>
+        <v>2328800</v>
       </c>
     </row>
     <row r="304">
@@ -13311,22 +13311,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M305" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="N305" t="n">
         <v>1203.38</v>
       </c>
       <c r="O305" t="n">
-        <v>244286.14</v>
+        <v>229845.58</v>
       </c>
       <c r="P305" t="n">
         <v>1900</v>
       </c>
       <c r="Q305" t="n">
-        <v>385700</v>
+        <v>362900</v>
       </c>
     </row>
     <row r="306">
@@ -13664,22 +13664,22 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M313" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N313" t="n">
         <v>7041</v>
       </c>
       <c r="O313" t="n">
-        <v>260517</v>
+        <v>253476</v>
       </c>
       <c r="P313" t="n">
         <v>11500</v>
       </c>
       <c r="Q313" t="n">
-        <v>425500</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="314">
@@ -13802,22 +13802,22 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M316" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N316" t="n">
         <v>8662</v>
       </c>
       <c r="O316" t="n">
-        <v>138592</v>
+        <v>121268</v>
       </c>
       <c r="P316" t="n">
         <v>14200</v>
       </c>
       <c r="Q316" t="n">
-        <v>227200</v>
+        <v>198800</v>
       </c>
     </row>
     <row r="317">
@@ -14331,10 +14331,10 @@
         <v>282</v>
       </c>
       <c r="N328" t="n">
-        <v>14822.378817006</v>
+        <v>14822.378814083</v>
       </c>
       <c r="O328" t="n">
-        <v>4179910.826395692</v>
+        <v>4179910.825571406</v>
       </c>
       <c r="P328" t="n">
         <v>24900</v>
@@ -14882,10 +14882,10 @@
         <v>378</v>
       </c>
       <c r="N341" t="n">
-        <v>12422.463007951</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O341" t="n">
-        <v>4695691.017005478</v>
+        <v>4695691.019017573</v>
       </c>
       <c r="P341" t="n">
         <v>19900</v>
@@ -15013,10 +15013,10 @@
         <v>2490</v>
       </c>
       <c r="N344" t="n">
-        <v>3472.2763500602</v>
+        <v>3472.2763717066</v>
       </c>
       <c r="O344" t="n">
-        <v>8645968.111649899</v>
+        <v>8645968.165549435</v>
       </c>
       <c r="P344" t="n">
         <v>5900</v>
@@ -15321,22 +15321,22 @@
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M351" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N351" t="n">
-        <v>3041.6600149925</v>
+        <v>3041.660015015</v>
       </c>
       <c r="O351" t="n">
-        <v>109499.76053973</v>
+        <v>103416.44051051</v>
       </c>
       <c r="P351" t="n">
         <v>5500</v>
       </c>
       <c r="Q351" t="n">
-        <v>198000</v>
+        <v>187000</v>
       </c>
     </row>
     <row r="352">
@@ -15362,22 +15362,22 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M352" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N352" t="n">
         <v>3981.47</v>
       </c>
       <c r="O352" t="n">
-        <v>294628.78</v>
+        <v>286665.84</v>
       </c>
       <c r="P352" t="n">
         <v>7000</v>
       </c>
       <c r="Q352" t="n">
-        <v>518000</v>
+        <v>504000</v>
       </c>
     </row>
     <row r="353">
@@ -15408,22 +15408,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M353" t="n">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="N353" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O353" t="n">
-        <v>1888346.722564929</v>
+        <v>1875233.204271055</v>
       </c>
       <c r="P353" t="n">
         <v>8900</v>
       </c>
       <c r="Q353" t="n">
-        <v>3844800</v>
+        <v>3818100</v>
       </c>
     </row>
     <row r="354">
@@ -15586,10 +15586,10 @@
         <v>275</v>
       </c>
       <c r="N357" t="n">
-        <v>1592.5645263158</v>
+        <v>1592.5644086022</v>
       </c>
       <c r="O357" t="n">
-        <v>437955.244736845</v>
+        <v>437955.212365605</v>
       </c>
       <c r="P357" t="n">
         <v>3900</v>
@@ -16185,22 +16185,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M371" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N371" t="n">
         <v>4648.6</v>
       </c>
       <c r="O371" t="n">
-        <v>939017.2000000001</v>
+        <v>911125.6000000001</v>
       </c>
       <c r="P371" t="n">
         <v>8900</v>
       </c>
       <c r="Q371" t="n">
-        <v>1797800</v>
+        <v>1744400</v>
       </c>
     </row>
     <row r="372">
@@ -16704,22 +16704,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M383" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N383" t="n">
         <v>13304.13</v>
       </c>
       <c r="O383" t="n">
-        <v>1729536.9</v>
+        <v>1716232.77</v>
       </c>
       <c r="P383" t="n">
         <v>20900</v>
       </c>
       <c r="Q383" t="n">
-        <v>2717000</v>
+        <v>2696100</v>
       </c>
     </row>
     <row r="384">
@@ -17672,22 +17672,22 @@
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M405" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N405" t="n">
         <v>3751</v>
       </c>
       <c r="O405" t="n">
-        <v>127534</v>
+        <v>112530</v>
       </c>
       <c r="P405" t="n">
         <v>6400</v>
       </c>
       <c r="Q405" t="n">
-        <v>217600</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="406">
@@ -17898,22 +17898,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M410" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="N410" t="n">
-        <v>1630.9249342316</v>
+        <v>1630.925009772</v>
       </c>
       <c r="O410" t="n">
-        <v>70129.7721719588</v>
+        <v>50558.675302932</v>
       </c>
       <c r="P410" t="n">
         <v>2500</v>
       </c>
       <c r="Q410" t="n">
-        <v>107500</v>
+        <v>77500</v>
       </c>
     </row>
     <row r="411">
@@ -17996,10 +17996,10 @@
         <v>239</v>
       </c>
       <c r="N412" t="n">
-        <v>1550.1949322169</v>
+        <v>1550.1949414115</v>
       </c>
       <c r="O412" t="n">
-        <v>370496.5887998391</v>
+        <v>370496.5909973485</v>
       </c>
       <c r="P412" t="n">
         <v>2500</v>
@@ -18082,22 +18082,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M414" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="N414" t="n">
-        <v>2403.5224548084</v>
+        <v>2403.5228513613</v>
       </c>
       <c r="O414" t="n">
-        <v>221124.0658423728</v>
+        <v>124983.1882707876</v>
       </c>
       <c r="P414" t="n">
         <v>3500</v>
       </c>
       <c r="Q414" t="n">
-        <v>322000</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="415">
@@ -18421,22 +18421,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M422" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="N422" t="n">
-        <v>1830.7551149425</v>
+        <v>1830.7548795181</v>
       </c>
       <c r="O422" t="n">
-        <v>294751.5735057425</v>
+        <v>280105.4965662693</v>
       </c>
       <c r="P422" t="n">
         <v>3150</v>
       </c>
       <c r="Q422" t="n">
-        <v>507150</v>
+        <v>481950</v>
       </c>
     </row>
     <row r="423">
@@ -19542,10 +19542,10 @@
         <v>84</v>
       </c>
       <c r="N447" t="n">
-        <v>17328</v>
+        <v>17991.272727273</v>
       </c>
       <c r="O447" t="n">
-        <v>1455552</v>
+        <v>1511266.909090932</v>
       </c>
       <c r="P447" t="n">
         <v>32900</v>
@@ -19797,22 +19797,22 @@
         <v>0</v>
       </c>
       <c r="L453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N453" t="n">
-        <v>10132</v>
+        <v>0</v>
       </c>
       <c r="O453" t="n">
-        <v>10132</v>
+        <v>0</v>
       </c>
       <c r="P453" t="n">
         <v>9900</v>
       </c>
       <c r="Q453" t="n">
-        <v>9900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -21324,22 +21324,22 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M489" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N489" t="n">
         <v>9338</v>
       </c>
       <c r="O489" t="n">
-        <v>233450</v>
+        <v>177422</v>
       </c>
       <c r="P489" t="n">
         <v>15500</v>
       </c>
       <c r="Q489" t="n">
-        <v>387500</v>
+        <v>294500</v>
       </c>
     </row>
     <row r="490">
@@ -21991,22 +21991,22 @@
         <v>0</v>
       </c>
       <c r="L505" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M505" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N505" t="n">
         <v>1969</v>
       </c>
       <c r="O505" t="n">
-        <v>287474</v>
+        <v>275660</v>
       </c>
       <c r="P505" t="n">
         <v>1500</v>
       </c>
       <c r="Q505" t="n">
-        <v>219000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="506">
@@ -22286,22 +22286,22 @@
         <v>0</v>
       </c>
       <c r="L512" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M512" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N512" t="n">
         <v>13152</v>
       </c>
       <c r="O512" t="n">
-        <v>1354656</v>
+        <v>1315200</v>
       </c>
       <c r="P512" t="n">
         <v>16900</v>
       </c>
       <c r="Q512" t="n">
-        <v>1740700</v>
+        <v>1690000</v>
       </c>
     </row>
     <row r="513">
@@ -22541,10 +22541,10 @@
         <v>189</v>
       </c>
       <c r="N518" t="n">
-        <v>2029.8742253521</v>
+        <v>2029.8742541123</v>
       </c>
       <c r="O518" t="n">
-        <v>383646.2285915469</v>
+        <v>383646.2340272247</v>
       </c>
       <c r="P518" t="n">
         <v>3600</v>
@@ -23287,10 +23287,10 @@
         <v>179</v>
       </c>
       <c r="N536" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O536" t="n">
-        <v>479852.4050782713</v>
+        <v>479852.4050438675</v>
       </c>
       <c r="P536" t="n">
         <v>4900</v>
@@ -23620,10 +23620,10 @@
         <v>7</v>
       </c>
       <c r="N544" t="n">
-        <v>11431.604625</v>
+        <v>11724.722692308</v>
       </c>
       <c r="O544" t="n">
-        <v>80021.23237499999</v>
+        <v>82073.058846156</v>
       </c>
       <c r="P544" t="n">
         <v>48900</v>
@@ -23742,22 +23742,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M547" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N547" t="n">
         <v>5894.64</v>
       </c>
       <c r="O547" t="n">
-        <v>613042.5600000001</v>
+        <v>595358.64</v>
       </c>
       <c r="P547" t="n">
         <v>11000</v>
       </c>
       <c r="Q547" t="n">
-        <v>1144000</v>
+        <v>1111000</v>
       </c>
     </row>
     <row r="548">
@@ -24250,10 +24250,10 @@
         <v>87</v>
       </c>
       <c r="N559" t="n">
-        <v>30611</v>
+        <v>30745.062773723</v>
       </c>
       <c r="O559" t="n">
-        <v>2663157</v>
+        <v>2674820.461313901</v>
       </c>
       <c r="P559" t="n">
         <v>38900</v>
@@ -24429,10 +24429,10 @@
         <v>1198</v>
       </c>
       <c r="N563" t="n">
-        <v>6207.9882021366</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O563" t="n">
-        <v>7437169.866159647</v>
+        <v>7437169.865250964</v>
       </c>
       <c r="P563" t="n">
         <v>9900</v>
@@ -24674,22 +24674,22 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M569" t="n">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="N569" t="n">
         <v>3877.89</v>
       </c>
       <c r="O569" t="n">
-        <v>1477476.09</v>
+        <v>1442575.08</v>
       </c>
       <c r="P569" t="n">
         <v>6500</v>
       </c>
       <c r="Q569" t="n">
-        <v>2476500</v>
+        <v>2418000</v>
       </c>
     </row>
     <row r="570">
@@ -24764,22 +24764,22 @@
         <v>0</v>
       </c>
       <c r="L571" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M571" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N571" t="n">
-        <v>4285.1965633075</v>
+        <v>4285.1966145833</v>
       </c>
       <c r="O571" t="n">
-        <v>501367.9979069775</v>
+        <v>484227.217447913</v>
       </c>
       <c r="P571" t="n">
         <v>6900</v>
       </c>
       <c r="Q571" t="n">
-        <v>807300</v>
+        <v>779700</v>
       </c>
     </row>
     <row r="572">
@@ -25106,10 +25106,10 @@
         <v>260</v>
       </c>
       <c r="N579" t="n">
-        <v>1106</v>
+        <v>1111.1642023346</v>
       </c>
       <c r="O579" t="n">
-        <v>287560</v>
+        <v>288902.692606996</v>
       </c>
       <c r="P579" t="n">
         <v>2100</v>
@@ -25310,22 +25310,22 @@
         <v>0</v>
       </c>
       <c r="L584" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M584" t="n">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="N584" t="n">
-        <v>4814.2633769677</v>
+        <v>4814.2633736737</v>
       </c>
       <c r="O584" t="n">
-        <v>4342465.566024866</v>
+        <v>4328022.772932656</v>
       </c>
       <c r="P584" t="n">
         <v>9900</v>
       </c>
       <c r="Q584" t="n">
-        <v>8929800</v>
+        <v>8900100</v>
       </c>
     </row>
     <row r="585">
@@ -25484,22 +25484,22 @@
         <v>0</v>
       </c>
       <c r="L588" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M588" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N588" t="n">
-        <v>11562.038395415</v>
+        <v>11562.038381503</v>
       </c>
       <c r="O588" t="n">
-        <v>994335.3020056901</v>
+        <v>971211.224046252</v>
       </c>
       <c r="P588" t="n">
         <v>18500</v>
       </c>
       <c r="Q588" t="n">
-        <v>1591000</v>
+        <v>1554000</v>
       </c>
     </row>
     <row r="589">
@@ -25536,10 +25536,10 @@
         <v>2</v>
       </c>
       <c r="N589" t="n">
-        <v>13513.643534483</v>
+        <v>13513.643727273</v>
       </c>
       <c r="O589" t="n">
-        <v>27027.287068966</v>
+        <v>27027.287454546</v>
       </c>
       <c r="P589" t="n">
         <v>21900</v>
@@ -25582,10 +25582,10 @@
         <v>75</v>
       </c>
       <c r="N590" t="n">
-        <v>12005.159823009</v>
+        <v>12005.159821429</v>
       </c>
       <c r="O590" t="n">
-        <v>900386.9867256751</v>
+        <v>900386.9866071751</v>
       </c>
       <c r="P590" t="n">
         <v>19500</v>
@@ -26916,22 +26916,22 @@
         <v>0</v>
       </c>
       <c r="L622" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M622" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="N622" t="n">
         <v>4793.53</v>
       </c>
       <c r="O622" t="n">
-        <v>1572277.84</v>
+        <v>1543516.66</v>
       </c>
       <c r="P622" t="n">
         <v>7900</v>
       </c>
       <c r="Q622" t="n">
-        <v>2591200</v>
+        <v>2543800</v>
       </c>
     </row>
     <row r="623">
@@ -27398,10 +27398,10 @@
         <v>135</v>
       </c>
       <c r="N633" t="n">
-        <v>27123.764688797</v>
+        <v>27123.764610526</v>
       </c>
       <c r="O633" t="n">
-        <v>3661708.232987595</v>
+        <v>3661708.22242101</v>
       </c>
       <c r="P633" t="n">
         <v>44500</v>
@@ -27777,10 +27777,10 @@
         <v>78</v>
       </c>
       <c r="N642" t="n">
-        <v>8332.7796042216</v>
+        <v>8332.7795967742</v>
       </c>
       <c r="O642" t="n">
-        <v>649956.8091292848</v>
+        <v>649956.8085483876</v>
       </c>
       <c r="P642" t="n">
         <v>14900</v>
@@ -28068,22 +28068,22 @@
         <v>0</v>
       </c>
       <c r="L649" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M649" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N649" t="n">
-        <v>1561.0066122098</v>
+        <v>1561.0072654155</v>
       </c>
       <c r="O649" t="n">
-        <v>93660.39673258801</v>
+        <v>74928.34873994399</v>
       </c>
       <c r="P649" t="n">
         <v>2900</v>
       </c>
       <c r="Q649" t="n">
-        <v>174000</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="650">
@@ -28289,10 +28289,10 @@
         <v>19</v>
       </c>
       <c r="N654" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O654" t="n">
-        <v>510226</v>
+        <v>514537.769014092</v>
       </c>
       <c r="P654" t="n">
         <v>43900</v>
@@ -28493,22 +28493,22 @@
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M659" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N659" t="n">
         <v>29700</v>
       </c>
       <c r="O659" t="n">
-        <v>564300</v>
+        <v>504900</v>
       </c>
       <c r="P659" t="n">
         <v>50500</v>
       </c>
       <c r="Q659" t="n">
-        <v>959500</v>
+        <v>858500</v>
       </c>
     </row>
     <row r="660">
@@ -28575,22 +28575,22 @@
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M661" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N661" t="n">
-        <v>2568.8354081633</v>
+        <v>2568.8353767123</v>
       </c>
       <c r="O661" t="n">
-        <v>400738.3236734748</v>
+        <v>395600.6480136942</v>
       </c>
       <c r="P661" t="n">
         <v>4500</v>
       </c>
       <c r="Q661" t="n">
-        <v>702000</v>
+        <v>693000</v>
       </c>
     </row>
     <row r="662">
@@ -28949,22 +28949,22 @@
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M670" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N670" t="n">
         <v>17044.07</v>
       </c>
       <c r="O670" t="n">
-        <v>357925.47</v>
+        <v>323837.33</v>
       </c>
       <c r="P670" t="n">
         <v>34700</v>
       </c>
       <c r="Q670" t="n">
-        <v>728700</v>
+        <v>659300</v>
       </c>
     </row>
     <row r="671">
@@ -30230,10 +30230,10 @@
         <v>1</v>
       </c>
       <c r="N700" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="O700" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="P700" t="n">
         <v>13900</v>
@@ -31697,22 +31697,22 @@
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M732" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N732" t="n">
         <v>3646</v>
       </c>
       <c r="O732" t="n">
-        <v>904208</v>
+        <v>889624</v>
       </c>
       <c r="P732" t="n">
         <v>6900</v>
       </c>
       <c r="Q732" t="n">
-        <v>1711200</v>
+        <v>1683600</v>
       </c>
     </row>
     <row r="733">
@@ -31749,10 +31749,10 @@
         <v>17</v>
       </c>
       <c r="N733" t="n">
-        <v>23521.622708333</v>
+        <v>23521.621666667</v>
       </c>
       <c r="O733" t="n">
-        <v>399867.586041661</v>
+        <v>399867.568333339</v>
       </c>
       <c r="P733" t="n">
         <v>39000</v>
@@ -31835,22 +31835,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M735" t="n">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="N735" t="n">
         <v>3486</v>
       </c>
       <c r="O735" t="n">
-        <v>2217096</v>
+        <v>2175264</v>
       </c>
       <c r="P735" t="n">
         <v>6900</v>
       </c>
       <c r="Q735" t="n">
-        <v>4388400</v>
+        <v>4305600</v>
       </c>
     </row>
     <row r="736">
@@ -31881,22 +31881,22 @@
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M736" t="n">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="N736" t="n">
-        <v>1778.4728840436</v>
+        <v>1778.4728878597</v>
       </c>
       <c r="O736" t="n">
-        <v>2063028.545490576</v>
+        <v>2048800.766814374</v>
       </c>
       <c r="P736" t="n">
         <v>4900</v>
       </c>
       <c r="Q736" t="n">
-        <v>5684000</v>
+        <v>5644800</v>
       </c>
     </row>
     <row r="737">
@@ -32071,10 +32071,10 @@
         <v>40</v>
       </c>
       <c r="N740" t="n">
-        <v>22739</v>
+        <v>22935.194995686</v>
       </c>
       <c r="O740" t="n">
-        <v>909560</v>
+        <v>917407.7998274401</v>
       </c>
       <c r="P740" t="n">
         <v>36900</v>
@@ -32163,10 +32163,10 @@
         <v>175</v>
       </c>
       <c r="N742" t="n">
-        <v>16058</v>
+        <v>16177.301634473</v>
       </c>
       <c r="O742" t="n">
-        <v>2810150</v>
+        <v>2831027.786032775</v>
       </c>
       <c r="P742" t="n">
         <v>25900</v>
@@ -32298,22 +32298,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M745" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N745" t="n">
         <v>5148</v>
       </c>
       <c r="O745" t="n">
-        <v>365508</v>
+        <v>334620</v>
       </c>
       <c r="P745" t="n">
         <v>8600</v>
       </c>
       <c r="Q745" t="n">
-        <v>610600</v>
+        <v>559000</v>
       </c>
     </row>
     <row r="746">
@@ -32482,22 +32482,22 @@
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M749" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N749" t="n">
         <v>4620</v>
       </c>
       <c r="O749" t="n">
-        <v>559020</v>
+        <v>545160</v>
       </c>
       <c r="P749" t="n">
         <v>7500</v>
       </c>
       <c r="Q749" t="n">
-        <v>907500</v>
+        <v>885000</v>
       </c>
     </row>
     <row r="750">
@@ -32712,22 +32712,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M754" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N754" t="n">
         <v>5200</v>
       </c>
       <c r="O754" t="n">
-        <v>265200</v>
+        <v>249600</v>
       </c>
       <c r="P754" t="n">
         <v>8500</v>
       </c>
       <c r="Q754" t="n">
-        <v>433500</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="755">
@@ -32804,22 +32804,22 @@
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M756" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="N756" t="n">
         <v>6000</v>
       </c>
       <c r="O756" t="n">
-        <v>378000</v>
+        <v>348000</v>
       </c>
       <c r="P756" t="n">
         <v>10000</v>
       </c>
       <c r="Q756" t="n">
-        <v>630000</v>
+        <v>580000</v>
       </c>
     </row>
     <row r="757">
@@ -32896,22 +32896,22 @@
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M758" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="N758" t="n">
         <v>1230</v>
       </c>
       <c r="O758" t="n">
-        <v>116850</v>
+        <v>111930</v>
       </c>
       <c r="P758" t="n">
         <v>2000</v>
       </c>
       <c r="Q758" t="n">
-        <v>190000</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="759">
@@ -32948,10 +32948,10 @@
         <v>21</v>
       </c>
       <c r="N759" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O759" t="n">
-        <v>68443.41560000071</v>
+        <v>68443.4156756763</v>
       </c>
       <c r="P759" t="n">
         <v>5300</v>
@@ -33085,22 +33085,22 @@
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M762" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="N762" t="n">
         <v>1870</v>
       </c>
       <c r="O762" t="n">
-        <v>35530</v>
+        <v>16830</v>
       </c>
       <c r="P762" t="n">
         <v>3000</v>
       </c>
       <c r="Q762" t="n">
-        <v>57000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="763">
@@ -33269,22 +33269,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M766" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N766" t="n">
         <v>2720</v>
       </c>
       <c r="O766" t="n">
-        <v>5440</v>
+        <v>2720</v>
       </c>
       <c r="P766" t="n">
         <v>4500</v>
       </c>
       <c r="Q766" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="767">
@@ -33315,22 +33315,22 @@
         <v>0</v>
       </c>
       <c r="L767" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M767" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N767" t="n">
         <v>1840</v>
       </c>
       <c r="O767" t="n">
-        <v>86480</v>
+        <v>80960</v>
       </c>
       <c r="P767" t="n">
         <v>3000</v>
       </c>
       <c r="Q767" t="n">
-        <v>141000</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="768">
@@ -33361,22 +33361,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M768" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N768" t="n">
         <v>2670</v>
       </c>
       <c r="O768" t="n">
-        <v>194910</v>
+        <v>186900</v>
       </c>
       <c r="P768" t="n">
         <v>4500</v>
       </c>
       <c r="Q768" t="n">
-        <v>328500</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="769">
@@ -33827,10 +33827,10 @@
         <v>1</v>
       </c>
       <c r="N778" t="n">
-        <v>12709</v>
+        <v>29654.333333333</v>
       </c>
       <c r="O778" t="n">
-        <v>12709</v>
+        <v>29654.333333333</v>
       </c>
       <c r="P778" t="n">
         <v>20500</v>
@@ -33873,10 +33873,10 @@
         <v>23</v>
       </c>
       <c r="N779" t="n">
-        <v>28116</v>
+        <v>28661.941747573</v>
       </c>
       <c r="O779" t="n">
-        <v>646668</v>
+        <v>659224.660194179</v>
       </c>
       <c r="P779" t="n">
         <v>45900</v>
@@ -34287,10 +34287,10 @@
         <v>93</v>
       </c>
       <c r="N788" t="n">
-        <v>2252.3008997955</v>
+        <v>2252.3011740042</v>
       </c>
       <c r="O788" t="n">
-        <v>209463.9836809815</v>
+        <v>209464.0091823906</v>
       </c>
       <c r="P788" t="n">
         <v>3900</v>
@@ -34750,10 +34750,10 @@
         <v>54</v>
       </c>
       <c r="N798" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="O798" t="n">
-        <v>190026</v>
+        <v>223016.625</v>
       </c>
       <c r="P798" t="n">
         <v>5900</v>
@@ -35072,10 +35072,10 @@
         <v>43</v>
       </c>
       <c r="N805" t="n">
-        <v>16285.911125</v>
+        <v>16703.498589744</v>
       </c>
       <c r="O805" t="n">
-        <v>700294.178375</v>
+        <v>718250.4393589919</v>
       </c>
       <c r="P805" t="n">
         <v>29900</v>
@@ -35118,10 +35118,10 @@
         <v>42</v>
       </c>
       <c r="N806" t="n">
-        <v>17981</v>
+        <v>18487.507042254</v>
       </c>
       <c r="O806" t="n">
-        <v>755202</v>
+        <v>776475.295774668</v>
       </c>
       <c r="P806" t="n">
         <v>29900</v>
@@ -35256,10 +35256,10 @@
         <v>15</v>
       </c>
       <c r="N809" t="n">
-        <v>4907.8227973568</v>
+        <v>4907.8228159645</v>
       </c>
       <c r="O809" t="n">
-        <v>73617.341960352</v>
+        <v>73617.3422394675</v>
       </c>
       <c r="P809" t="n">
         <v>8200</v>
@@ -35573,10 +35573,10 @@
         <v>25</v>
       </c>
       <c r="N816" t="n">
-        <v>20731</v>
+        <v>21767.55</v>
       </c>
       <c r="O816" t="n">
-        <v>518275</v>
+        <v>544188.75</v>
       </c>
       <c r="P816" t="n">
         <v>33900</v>
@@ -36355,10 +36355,10 @@
         <v>184</v>
       </c>
       <c r="N833" t="n">
-        <v>13565</v>
+        <v>13585.998452012</v>
       </c>
       <c r="O833" t="n">
-        <v>2495960</v>
+        <v>2499823.715170208</v>
       </c>
       <c r="P833" t="n">
         <v>22500</v>
@@ -36493,10 +36493,10 @@
         <v>12</v>
       </c>
       <c r="N836" t="n">
-        <v>16086</v>
+        <v>16443.466666667</v>
       </c>
       <c r="O836" t="n">
-        <v>193032</v>
+        <v>197321.600000004</v>
       </c>
       <c r="P836" t="n">
         <v>25900</v>
@@ -36533,22 +36533,22 @@
         <v>0</v>
       </c>
       <c r="L837" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M837" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N837" t="n">
         <v>8806</v>
       </c>
       <c r="O837" t="n">
-        <v>651644</v>
+        <v>598808</v>
       </c>
       <c r="P837" t="n">
         <v>14900</v>
       </c>
       <c r="Q837" t="n">
-        <v>1102600</v>
+        <v>1013200</v>
       </c>
     </row>
     <row r="838">
@@ -36585,10 +36585,10 @@
         <v>21</v>
       </c>
       <c r="N838" t="n">
-        <v>23439</v>
+        <v>24040</v>
       </c>
       <c r="O838" t="n">
-        <v>492219</v>
+        <v>504840</v>
       </c>
       <c r="P838" t="n">
         <v>37900</v>
@@ -36631,10 +36631,10 @@
         <v>105</v>
       </c>
       <c r="N839" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O839" t="n">
-        <v>1995840</v>
+        <v>2001212.382234135</v>
       </c>
       <c r="P839" t="n">
         <v>30900</v>
@@ -36723,10 +36723,10 @@
         <v>111</v>
       </c>
       <c r="N841" t="n">
-        <v>17992</v>
+        <v>18038.854166667</v>
       </c>
       <c r="O841" t="n">
-        <v>1997112</v>
+        <v>2002312.812500037</v>
       </c>
       <c r="P841" t="n">
         <v>28900</v>
@@ -37727,22 +37727,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M863" t="n">
-        <v>1630</v>
+        <v>1618</v>
       </c>
       <c r="N863" t="n">
         <v>1326</v>
       </c>
       <c r="O863" t="n">
-        <v>2161380</v>
+        <v>2145468</v>
       </c>
       <c r="P863" t="n">
         <v>2500</v>
       </c>
       <c r="Q863" t="n">
-        <v>4075000</v>
+        <v>4045000</v>
       </c>
     </row>
     <row r="864">
@@ -37825,10 +37825,10 @@
         <v>1</v>
       </c>
       <c r="N865" t="n">
-        <v>10817</v>
+        <v>10997.283333333</v>
       </c>
       <c r="O865" t="n">
-        <v>10817</v>
+        <v>10997.283333333</v>
       </c>
       <c r="P865" t="n">
         <v>17900</v>
@@ -37871,10 +37871,10 @@
         <v>45</v>
       </c>
       <c r="N866" t="n">
-        <v>12489</v>
+        <v>12769.651685393</v>
       </c>
       <c r="O866" t="n">
-        <v>562005</v>
+        <v>574634.3258426851</v>
       </c>
       <c r="P866" t="n">
         <v>20900</v>
@@ -38003,22 +38003,22 @@
         <v>0</v>
       </c>
       <c r="L869" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M869" t="n">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="N869" t="n">
         <v>3821</v>
       </c>
       <c r="O869" t="n">
-        <v>5872877</v>
+        <v>5853772</v>
       </c>
       <c r="P869" t="n">
         <v>5900</v>
       </c>
       <c r="Q869" t="n">
-        <v>9068300</v>
+        <v>9038800</v>
       </c>
     </row>
     <row r="870">
@@ -38055,10 +38055,10 @@
         <v>4</v>
       </c>
       <c r="N870" t="n">
-        <v>15472</v>
+        <v>15602.016806723</v>
       </c>
       <c r="O870" t="n">
-        <v>61888</v>
+        <v>62408.067226892</v>
       </c>
       <c r="P870" t="n">
         <v>25900</v>
@@ -38562,10 +38562,10 @@
         <v>83</v>
       </c>
       <c r="N881" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942583732</v>
       </c>
       <c r="O881" t="n">
-        <v>274447.3242038197</v>
+        <v>274447.3234449756</v>
       </c>
       <c r="P881" t="n">
         <v>4900</v>
@@ -38648,22 +38648,22 @@
         <v>0</v>
       </c>
       <c r="L883" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M883" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="N883" t="n">
-        <v>2056.0812616427</v>
+        <v>2056.081010453</v>
       </c>
       <c r="O883" t="n">
-        <v>176822.9885012722</v>
+        <v>41121.62020906</v>
       </c>
       <c r="P883" t="n">
         <v>2900</v>
       </c>
       <c r="Q883" t="n">
-        <v>249400</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="884">
@@ -38746,10 +38746,10 @@
         <v>66</v>
       </c>
       <c r="N885" t="n">
-        <v>1655.9287880016</v>
+        <v>1655.9287789047</v>
       </c>
       <c r="O885" t="n">
-        <v>109291.3000081056</v>
+        <v>109291.2994077102</v>
       </c>
       <c r="P885" t="n">
         <v>2500</v>
@@ -38881,22 +38881,22 @@
         <v>0</v>
       </c>
       <c r="L888" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M888" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="N888" t="n">
         <v>1662</v>
       </c>
       <c r="O888" t="n">
-        <v>304146</v>
+        <v>264258</v>
       </c>
       <c r="P888" t="n">
         <v>2900</v>
       </c>
       <c r="Q888" t="n">
-        <v>530700</v>
+        <v>461100</v>
       </c>
     </row>
     <row r="889">
@@ -38973,22 +38973,22 @@
         <v>0</v>
       </c>
       <c r="L890" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M890" t="n">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="N890" t="n">
-        <v>1592.2874455446</v>
+        <v>1592.2885084034</v>
       </c>
       <c r="O890" t="n">
-        <v>372595.2622574364</v>
+        <v>342342.029306731</v>
       </c>
       <c r="P890" t="n">
         <v>2500</v>
       </c>
       <c r="Q890" t="n">
-        <v>585000</v>
+        <v>537500</v>
       </c>
     </row>
     <row r="891">
@@ -39519,10 +39519,10 @@
         <v>63</v>
       </c>
       <c r="N902" t="n">
-        <v>2556.7485294118</v>
+        <v>2556.7486567164</v>
       </c>
       <c r="O902" t="n">
-        <v>161075.1573529434</v>
+        <v>161075.1653731332</v>
       </c>
       <c r="P902" t="n">
         <v>3900</v>
@@ -39557,22 +39557,22 @@
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M903" t="n">
-        <v>2374</v>
+        <v>2338</v>
       </c>
       <c r="N903" t="n">
-        <v>692.15251958462</v>
+        <v>692.1525362185999</v>
       </c>
       <c r="O903" t="n">
-        <v>1643170.081493888</v>
+        <v>1618252.629679087</v>
       </c>
       <c r="P903" t="n">
         <v>1200</v>
       </c>
       <c r="Q903" t="n">
-        <v>2848800</v>
+        <v>2805600</v>
       </c>
     </row>
     <row r="904">
@@ -41894,22 +41894,22 @@
         <v>0</v>
       </c>
       <c r="L954" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M954" t="n">
-        <v>556</v>
+        <v>470</v>
       </c>
       <c r="N954" t="n">
-        <v>517.29656001551</v>
+        <v>517.29673853391</v>
       </c>
       <c r="O954" t="n">
-        <v>287616.8873686235</v>
+        <v>243129.4671109377</v>
       </c>
       <c r="P954" t="n">
         <v>900</v>
       </c>
       <c r="Q954" t="n">
-        <v>500400</v>
+        <v>423000</v>
       </c>
     </row>
     <row r="955">
@@ -42036,10 +42036,10 @@
         <v>1</v>
       </c>
       <c r="N957" t="n">
-        <v>3259.1346835443</v>
+        <v>3259.1347844828</v>
       </c>
       <c r="O957" t="n">
-        <v>3259.1346835443</v>
+        <v>3259.1347844828</v>
       </c>
       <c r="P957" t="n">
         <v>3600</v>
@@ -42085,10 +42085,10 @@
         <v>834</v>
       </c>
       <c r="N958" t="n">
-        <v>3110.8352523988</v>
+        <v>3110.8351781971</v>
       </c>
       <c r="O958" t="n">
-        <v>2594436.600500599</v>
+        <v>2594436.538616382</v>
       </c>
       <c r="P958" t="n">
         <v>4500</v>
@@ -42211,22 +42211,22 @@
         <v>0</v>
       </c>
       <c r="L961" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M961" t="n">
-        <v>12629</v>
+        <v>12619</v>
       </c>
       <c r="N961" t="n">
-        <v>703.79459507493</v>
+        <v>703.79459259958</v>
       </c>
       <c r="O961" t="n">
-        <v>8888221.941201292</v>
+        <v>8881183.9640141</v>
       </c>
       <c r="P961" t="n">
         <v>900</v>
       </c>
       <c r="Q961" t="n">
-        <v>11366100</v>
+        <v>11357100</v>
       </c>
     </row>
     <row r="962">
@@ -46112,10 +46112,10 @@
         <v>3</v>
       </c>
       <c r="N1045" t="n">
-        <v>5216.9</v>
+        <v>5254.1635714286</v>
       </c>
       <c r="O1045" t="n">
-        <v>15650.7</v>
+        <v>15762.4907142858</v>
       </c>
       <c r="P1045" t="n">
         <v>20500</v>
@@ -46346,10 +46346,10 @@
         <v>1</v>
       </c>
       <c r="N1050" t="n">
-        <v>24338.47</v>
+        <v>24856.309787234</v>
       </c>
       <c r="O1050" t="n">
-        <v>24338.47</v>
+        <v>24856.309787234</v>
       </c>
       <c r="P1050" t="n">
         <v>27900</v>
@@ -46860,22 +46860,22 @@
         <v>0</v>
       </c>
       <c r="L1061" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1061" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N1061" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1061" t="n">
-        <v>985095.6</v>
+        <v>966768.24</v>
       </c>
       <c r="P1061" t="n">
         <v>7900</v>
       </c>
       <c r="Q1061" t="n">
-        <v>1698500</v>
+        <v>1666900</v>
       </c>
     </row>
     <row r="1062">
@@ -46909,22 +46909,22 @@
         <v>0</v>
       </c>
       <c r="L1062" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1062" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="N1062" t="n">
         <v>3155</v>
       </c>
       <c r="O1062" t="n">
-        <v>1012755</v>
+        <v>1003290</v>
       </c>
       <c r="P1062" t="n">
         <v>5900</v>
       </c>
       <c r="Q1062" t="n">
-        <v>1893900</v>
+        <v>1876200</v>
       </c>
     </row>
     <row r="1063">
@@ -46958,22 +46958,22 @@
         <v>0</v>
       </c>
       <c r="L1063" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1063" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N1063" t="n">
-        <v>430.60997520149</v>
+        <v>430.6099751861</v>
       </c>
       <c r="O1063" t="n">
-        <v>31003.91821450728</v>
+        <v>30573.3082382131</v>
       </c>
       <c r="P1063" t="n">
         <v>2200</v>
       </c>
       <c r="Q1063" t="n">
-        <v>158400</v>
+        <v>156200</v>
       </c>
     </row>
     <row r="1064">
@@ -49289,22 +49289,22 @@
         <v>0</v>
       </c>
       <c r="L1117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1117" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N1117" t="n">
-        <v>22951.704647137</v>
+        <v>22951.704432133</v>
       </c>
       <c r="O1117" t="n">
-        <v>8606889.242676375</v>
+        <v>8560985.753185609</v>
       </c>
       <c r="P1117" t="n">
         <v>37900</v>
       </c>
       <c r="Q1117" t="n">
-        <v>14212500</v>
+        <v>14136700</v>
       </c>
     </row>
     <row r="1118">
@@ -50654,22 +50654,22 @@
         <v>0</v>
       </c>
       <c r="L1147" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M1147" t="n">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="N1147" t="n">
         <v>1056</v>
       </c>
       <c r="O1147" t="n">
-        <v>1173216</v>
+        <v>1139424</v>
       </c>
       <c r="P1147" t="n">
         <v>1400</v>
       </c>
       <c r="Q1147" t="n">
-        <v>1555400</v>
+        <v>1510600</v>
       </c>
     </row>
     <row r="1148">
@@ -50847,10 +50847,10 @@
         <v>3</v>
       </c>
       <c r="N1151" t="n">
-        <v>9240</v>
+        <v>9401.162790697699</v>
       </c>
       <c r="O1151" t="n">
-        <v>27720</v>
+        <v>28203.4883720931</v>
       </c>
       <c r="P1151" t="n">
         <v>11500</v>
@@ -50933,22 +50933,22 @@
         <v>0</v>
       </c>
       <c r="L1153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1153" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N1153" t="n">
         <v>4576</v>
       </c>
       <c r="O1153" t="n">
-        <v>311168</v>
+        <v>283712</v>
       </c>
       <c r="P1153" t="n">
         <v>5900</v>
       </c>
       <c r="Q1153" t="n">
-        <v>401200</v>
+        <v>365800</v>
       </c>
     </row>
     <row r="1154">
@@ -52608,10 +52608,10 @@
         <v>167</v>
       </c>
       <c r="N1189" t="n">
-        <v>2539.5719057816</v>
+        <v>2539.5719098712</v>
       </c>
       <c r="O1189" t="n">
-        <v>424108.5082655272</v>
+        <v>424108.5089484904</v>
       </c>
       <c r="P1189" t="n">
         <v>2900</v>
@@ -52694,22 +52694,22 @@
         <v>0</v>
       </c>
       <c r="L1191" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1191" t="n">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="N1191" t="n">
-        <v>4171.6683018868</v>
+        <v>4171.6682869693</v>
       </c>
       <c r="O1191" t="n">
-        <v>1969027.43849057</v>
+        <v>1943997.421727694</v>
       </c>
       <c r="P1191" t="n">
         <v>5000</v>
       </c>
       <c r="Q1191" t="n">
-        <v>2360000</v>
+        <v>2330000</v>
       </c>
     </row>
     <row r="1192">
@@ -54544,22 +54544,22 @@
         <v>0</v>
       </c>
       <c r="L1236" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M1236" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="N1236" t="n">
         <v>1550</v>
       </c>
       <c r="O1236" t="n">
-        <v>34100</v>
+        <v>7750</v>
       </c>
       <c r="P1236" t="n">
         <v>2500</v>
       </c>
       <c r="Q1236" t="n">
-        <v>55000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="1237">
@@ -56922,22 +56922,22 @@
         <v>0</v>
       </c>
       <c r="L1294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1294" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N1294" t="n">
         <v>7800</v>
       </c>
       <c r="O1294" t="n">
-        <v>23400</v>
+        <v>7800</v>
       </c>
       <c r="P1294" t="n">
         <v>10500</v>
       </c>
       <c r="Q1294" t="n">
-        <v>31500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1295">
@@ -57004,22 +57004,22 @@
         <v>0</v>
       </c>
       <c r="L1296" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1296" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N1296" t="n">
         <v>6500</v>
       </c>
       <c r="O1296" t="n">
-        <v>45500</v>
+        <v>26000</v>
       </c>
       <c r="P1296" t="n">
         <v>8900</v>
       </c>
       <c r="Q1296" t="n">
-        <v>62300</v>
+        <v>35600</v>
       </c>
     </row>
     <row r="1297">
@@ -60334,22 +60334,22 @@
         <v>0</v>
       </c>
       <c r="L1376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1376" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N1376" t="n">
         <v>4550</v>
       </c>
       <c r="O1376" t="n">
-        <v>386750</v>
+        <v>377650</v>
       </c>
       <c r="P1376" t="n">
         <v>5500</v>
       </c>
       <c r="Q1376" t="n">
-        <v>467500</v>
+        <v>456500</v>
       </c>
     </row>
     <row r="1377">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -895,10 +895,10 @@
         <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>1811.3112820513</v>
+        <v>1811.3108641975</v>
       </c>
       <c r="O12" t="n">
-        <v>76075.0738461546</v>
+        <v>76075.05629629501</v>
       </c>
       <c r="P12" t="n">
         <v>2600</v>
@@ -8253,22 +8253,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M188" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N188" t="n">
-        <v>4276.1781707317</v>
+        <v>4438.5646835443</v>
       </c>
       <c r="O188" t="n">
-        <v>42761.781707317</v>
+        <v>31069.9527848101</v>
       </c>
       <c r="P188" t="n">
         <v>7800</v>
       </c>
       <c r="Q188" t="n">
-        <v>78000</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="189">
@@ -9078,10 +9078,10 @@
         <v>12</v>
       </c>
       <c r="N207" t="n">
-        <v>41061.071428571</v>
+        <v>33815</v>
       </c>
       <c r="O207" t="n">
-        <v>492732.857142852</v>
+        <v>405780</v>
       </c>
       <c r="P207" t="n">
         <v>47900</v>
@@ -9664,22 +9664,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M221" t="n">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="N221" t="n">
-        <v>1098.0729937163</v>
+        <v>1098.0730382022</v>
       </c>
       <c r="O221" t="n">
-        <v>635784.2633617377</v>
+        <v>629195.8508898607</v>
       </c>
       <c r="P221" t="n">
         <v>1500</v>
       </c>
       <c r="Q221" t="n">
-        <v>868500</v>
+        <v>859500</v>
       </c>
     </row>
     <row r="222">
@@ -10630,22 +10630,22 @@
         <v>0</v>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M244" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N244" t="n">
         <v>7569</v>
       </c>
       <c r="O244" t="n">
-        <v>280053</v>
+        <v>264915</v>
       </c>
       <c r="P244" t="n">
         <v>12900</v>
       </c>
       <c r="Q244" t="n">
-        <v>477300</v>
+        <v>451500</v>
       </c>
     </row>
     <row r="245">
@@ -11452,22 +11452,22 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M263" t="n">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="N263" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O263" t="n">
-        <v>1389253.06197214</v>
+        <v>1344908.929196508</v>
       </c>
       <c r="P263" t="n">
         <v>4500</v>
       </c>
       <c r="Q263" t="n">
-        <v>2421000</v>
+        <v>2340000</v>
       </c>
     </row>
     <row r="264">
@@ -12156,22 +12156,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M279" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N279" t="n">
-        <v>3230.0657009346</v>
+        <v>3230.0656603774</v>
       </c>
       <c r="O279" t="n">
-        <v>167963.4164485992</v>
+        <v>158273.2173584926</v>
       </c>
       <c r="P279" t="n">
         <v>6200</v>
       </c>
       <c r="Q279" t="n">
-        <v>322400</v>
+        <v>303800</v>
       </c>
     </row>
     <row r="280">
@@ -13311,22 +13311,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M305" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="N305" t="n">
         <v>1203.38</v>
       </c>
       <c r="O305" t="n">
-        <v>229845.58</v>
+        <v>220218.54</v>
       </c>
       <c r="P305" t="n">
         <v>1900</v>
       </c>
       <c r="Q305" t="n">
-        <v>362900</v>
+        <v>347700</v>
       </c>
     </row>
     <row r="306">
@@ -14967,10 +14967,10 @@
         <v>2490</v>
       </c>
       <c r="N343" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O343" t="n">
-        <v>8645968.172312522</v>
+        <v>8645968.18585638</v>
       </c>
       <c r="P343" t="n">
         <v>5900</v>
@@ -17852,22 +17852,22 @@
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M409" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="N409" t="n">
         <v>1630.9251181364</v>
       </c>
       <c r="O409" t="n">
-        <v>48927.753544092</v>
+        <v>34249.4274808644</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
       </c>
       <c r="Q409" t="n">
-        <v>75000</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="410">
@@ -17904,10 +17904,10 @@
         <v>14</v>
       </c>
       <c r="N410" t="n">
-        <v>1467.2914141414</v>
+        <v>1467.3004273504</v>
       </c>
       <c r="O410" t="n">
-        <v>20542.0797979796</v>
+        <v>20542.2059829056</v>
       </c>
       <c r="P410" t="n">
         <v>2500</v>
@@ -17950,10 +17950,10 @@
         <v>239</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.1950026961</v>
+        <v>1550.1949625568</v>
       </c>
       <c r="O411" t="n">
-        <v>370496.6056443679</v>
+        <v>370496.5960510752</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
@@ -18042,10 +18042,10 @@
         <v>52</v>
       </c>
       <c r="N413" t="n">
-        <v>2403.522961183</v>
+        <v>2403.5229357459</v>
       </c>
       <c r="O413" t="n">
-        <v>124983.193981516</v>
+        <v>124983.1926587868</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
@@ -19496,10 +19496,10 @@
         <v>84</v>
       </c>
       <c r="N446" t="n">
-        <v>17991.272727273</v>
+        <v>17328</v>
       </c>
       <c r="O446" t="n">
-        <v>1511266.909090932</v>
+        <v>1455552</v>
       </c>
       <c r="P446" t="n">
         <v>32900</v>
@@ -22443,22 +22443,22 @@
         <v>0</v>
       </c>
       <c r="L516" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M516" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="N516" t="n">
-        <v>2029.8742541123</v>
+        <v>2029.8742613636</v>
       </c>
       <c r="O516" t="n">
-        <v>383646.2340272247</v>
+        <v>377556.6126136296</v>
       </c>
       <c r="P516" t="n">
         <v>3600</v>
       </c>
       <c r="Q516" t="n">
-        <v>680400</v>
+        <v>669600</v>
       </c>
     </row>
     <row r="517">
@@ -23528,10 +23528,10 @@
         <v>7</v>
       </c>
       <c r="N542" t="n">
-        <v>11724.722692308</v>
+        <v>11431.604487179</v>
       </c>
       <c r="O542" t="n">
-        <v>82073.058846156</v>
+        <v>80021.23141025301</v>
       </c>
       <c r="P542" t="n">
         <v>48900</v>
@@ -24158,10 +24158,10 @@
         <v>87</v>
       </c>
       <c r="N557" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O557" t="n">
-        <v>2674820.461313901</v>
+        <v>2663157</v>
       </c>
       <c r="P557" t="n">
         <v>38900</v>
@@ -24337,10 +24337,10 @@
         <v>1198</v>
       </c>
       <c r="N561" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O561" t="n">
-        <v>7437169.864038229</v>
+        <v>7437169.865250964</v>
       </c>
       <c r="P561" t="n">
         <v>9900</v>
@@ -25224,10 +25224,10 @@
         <v>879</v>
       </c>
       <c r="N582" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O582" t="n">
-        <v>4231737.482192052</v>
+        <v>4231737.486082858</v>
       </c>
       <c r="P582" t="n">
         <v>9900</v>
@@ -27306,10 +27306,10 @@
         <v>135</v>
       </c>
       <c r="N631" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O631" t="n">
-        <v>3661708.22242101</v>
+        <v>3661708.21934463</v>
       </c>
       <c r="P631" t="n">
         <v>44500</v>
@@ -27976,22 +27976,22 @@
         <v>0</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M647" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N647" t="n">
         <v>1561.0074054054</v>
       </c>
       <c r="O647" t="n">
-        <v>70245.333243243</v>
+        <v>68684.3258378376</v>
       </c>
       <c r="P647" t="n">
         <v>2900</v>
       </c>
       <c r="Q647" t="n">
-        <v>130500</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="648">
@@ -28197,10 +28197,10 @@
         <v>19</v>
       </c>
       <c r="N652" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O652" t="n">
-        <v>514537.769014092</v>
+        <v>510226</v>
       </c>
       <c r="P652" t="n">
         <v>43900</v>
@@ -28524,22 +28524,22 @@
         <v>0</v>
       </c>
       <c r="L660" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M660" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N660" t="n">
         <v>22269</v>
       </c>
       <c r="O660" t="n">
-        <v>534456</v>
+        <v>512187</v>
       </c>
       <c r="P660" t="n">
         <v>37900</v>
       </c>
       <c r="Q660" t="n">
-        <v>909600</v>
+        <v>871700</v>
       </c>
     </row>
     <row r="661">
@@ -30961,22 +30961,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M716" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N716" t="n">
-        <v>10174</v>
+        <v>11021.833333333</v>
       </c>
       <c r="O716" t="n">
-        <v>518874</v>
+        <v>518026.166666651</v>
       </c>
       <c r="P716" t="n">
         <v>16900</v>
       </c>
       <c r="Q716" t="n">
-        <v>861900</v>
+        <v>794300</v>
       </c>
     </row>
     <row r="717">
@@ -31237,22 +31237,22 @@
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M722" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N722" t="n">
         <v>18536</v>
       </c>
       <c r="O722" t="n">
-        <v>18536</v>
+        <v>0</v>
       </c>
       <c r="P722" t="n">
         <v>30900</v>
       </c>
       <c r="Q722" t="n">
-        <v>30900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="723">
@@ -31657,10 +31657,10 @@
         <v>17</v>
       </c>
       <c r="N731" t="n">
-        <v>23521.621025641</v>
+        <v>23521.620277778</v>
       </c>
       <c r="O731" t="n">
-        <v>399867.557435897</v>
+        <v>399867.544722226</v>
       </c>
       <c r="P731" t="n">
         <v>39000</v>
@@ -31979,10 +31979,10 @@
         <v>40</v>
       </c>
       <c r="N738" t="n">
-        <v>22935.194995686</v>
+        <v>22739</v>
       </c>
       <c r="O738" t="n">
-        <v>917407.7998274401</v>
+        <v>909560</v>
       </c>
       <c r="P738" t="n">
         <v>36900</v>
@@ -33735,10 +33735,10 @@
         <v>1</v>
       </c>
       <c r="N776" t="n">
-        <v>29654.333333333</v>
+        <v>12709</v>
       </c>
       <c r="O776" t="n">
-        <v>29654.333333333</v>
+        <v>12709</v>
       </c>
       <c r="P776" t="n">
         <v>20500</v>
@@ -33781,10 +33781,10 @@
         <v>23</v>
       </c>
       <c r="N777" t="n">
-        <v>28661.941747573</v>
+        <v>28116</v>
       </c>
       <c r="O777" t="n">
-        <v>659224.660194179</v>
+        <v>646668</v>
       </c>
       <c r="P777" t="n">
         <v>45900</v>
@@ -34980,10 +34980,10 @@
         <v>43</v>
       </c>
       <c r="N803" t="n">
-        <v>16703.498589744</v>
+        <v>16285.911153846</v>
       </c>
       <c r="O803" t="n">
-        <v>718250.4393589919</v>
+        <v>700294.179615378</v>
       </c>
       <c r="P803" t="n">
         <v>29900</v>
@@ -35026,10 +35026,10 @@
         <v>42</v>
       </c>
       <c r="N804" t="n">
-        <v>18487.507042254</v>
+        <v>17981</v>
       </c>
       <c r="O804" t="n">
-        <v>776475.295774668</v>
+        <v>755202</v>
       </c>
       <c r="P804" t="n">
         <v>29900</v>
@@ -35481,10 +35481,10 @@
         <v>25</v>
       </c>
       <c r="N814" t="n">
-        <v>21767.55</v>
+        <v>20731</v>
       </c>
       <c r="O814" t="n">
-        <v>544188.75</v>
+        <v>518275</v>
       </c>
       <c r="P814" t="n">
         <v>33900</v>
@@ -35527,10 +35527,10 @@
         <v>34</v>
       </c>
       <c r="N815" t="n">
-        <v>33000</v>
+        <v>35444.444444444</v>
       </c>
       <c r="O815" t="n">
-        <v>1122000</v>
+        <v>1205111.111111096</v>
       </c>
       <c r="P815" t="n">
         <v>52900</v>
@@ -36263,10 +36263,10 @@
         <v>184</v>
       </c>
       <c r="N831" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O831" t="n">
-        <v>2499823.715170208</v>
+        <v>2495960</v>
       </c>
       <c r="P831" t="n">
         <v>22500</v>
@@ -36401,10 +36401,10 @@
         <v>12</v>
       </c>
       <c r="N834" t="n">
-        <v>16443.466666667</v>
+        <v>16086</v>
       </c>
       <c r="O834" t="n">
-        <v>197321.600000004</v>
+        <v>193032</v>
       </c>
       <c r="P834" t="n">
         <v>25900</v>
@@ -36539,10 +36539,10 @@
         <v>105</v>
       </c>
       <c r="N837" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O837" t="n">
-        <v>2001212.382234135</v>
+        <v>1995840</v>
       </c>
       <c r="P837" t="n">
         <v>30900</v>
@@ -36631,10 +36631,10 @@
         <v>111</v>
       </c>
       <c r="N839" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O839" t="n">
-        <v>2002312.812500037</v>
+        <v>1997112</v>
       </c>
       <c r="P839" t="n">
         <v>28900</v>
@@ -37779,10 +37779,10 @@
         <v>45</v>
       </c>
       <c r="N864" t="n">
-        <v>12769.651685393</v>
+        <v>12489</v>
       </c>
       <c r="O864" t="n">
-        <v>574634.3258426851</v>
+        <v>562005</v>
       </c>
       <c r="P864" t="n">
         <v>20900</v>
@@ -37963,10 +37963,10 @@
         <v>4</v>
       </c>
       <c r="N868" t="n">
-        <v>15602.016806723</v>
+        <v>15472</v>
       </c>
       <c r="O868" t="n">
-        <v>62408.067226892</v>
+        <v>61888</v>
       </c>
       <c r="P868" t="n">
         <v>25900</v>
@@ -38242,10 +38242,10 @@
         <v>1233</v>
       </c>
       <c r="N874" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O874" t="n">
-        <v>1869275.713838099</v>
+        <v>1869275.715875138</v>
       </c>
       <c r="P874" t="n">
         <v>2300</v>
@@ -38418,22 +38418,22 @@
         <v>0</v>
       </c>
       <c r="L878" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M878" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="N878" t="n">
-        <v>1803.0176111361</v>
+        <v>1803.0176523702</v>
       </c>
       <c r="O878" t="n">
-        <v>198331.937224971</v>
+        <v>176695.7299322796</v>
       </c>
       <c r="P878" t="n">
         <v>2500</v>
       </c>
       <c r="Q878" t="n">
-        <v>275000</v>
+        <v>245000</v>
       </c>
     </row>
     <row r="879">
@@ -38608,10 +38608,10 @@
         <v>125</v>
       </c>
       <c r="N882" t="n">
-        <v>3224.5700336323</v>
+        <v>3224.5700392597</v>
       </c>
       <c r="O882" t="n">
-        <v>403071.2542040375</v>
+        <v>403071.2549074625</v>
       </c>
       <c r="P882" t="n">
         <v>4500</v>
@@ -38648,22 +38648,22 @@
         <v>0</v>
       </c>
       <c r="L883" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M883" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="N883" t="n">
-        <v>1655.9287789047</v>
+        <v>1655.9286125978</v>
       </c>
       <c r="O883" t="n">
-        <v>109291.2994077102</v>
+        <v>89420.1450802812</v>
       </c>
       <c r="P883" t="n">
         <v>2500</v>
       </c>
       <c r="Q883" t="n">
-        <v>165000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="884">
@@ -38789,22 +38789,22 @@
         <v>0</v>
       </c>
       <c r="L886" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M886" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N886" t="n">
         <v>1662</v>
       </c>
       <c r="O886" t="n">
-        <v>264258</v>
+        <v>259272</v>
       </c>
       <c r="P886" t="n">
         <v>2900</v>
       </c>
       <c r="Q886" t="n">
-        <v>461100</v>
+        <v>452400</v>
       </c>
     </row>
     <row r="887">
@@ -38881,22 +38881,22 @@
         <v>0</v>
       </c>
       <c r="L888" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M888" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N888" t="n">
-        <v>1592.2886257928</v>
+        <v>1592.2887446809</v>
       </c>
       <c r="O888" t="n">
-        <v>342342.054545452</v>
+        <v>337565.2138723508</v>
       </c>
       <c r="P888" t="n">
         <v>2500</v>
       </c>
       <c r="Q888" t="n">
-        <v>537500</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="889">
@@ -39012,22 +39012,22 @@
         <v>0</v>
       </c>
       <c r="L891" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M891" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="N891" t="n">
-        <v>2311.6938235294</v>
+        <v>11228.227142857</v>
       </c>
       <c r="O891" t="n">
-        <v>78597.5899999996</v>
+        <v>78597.58999999901</v>
       </c>
       <c r="P891" t="n">
         <v>3500</v>
       </c>
       <c r="Q891" t="n">
-        <v>119000</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="892">
@@ -39058,22 +39058,22 @@
         <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M892" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N892" t="n">
-        <v>1906.1654098361</v>
+        <v>2153.2609259259</v>
       </c>
       <c r="O892" t="n">
-        <v>76246.616393444</v>
+        <v>71057.61055555471</v>
       </c>
       <c r="P892" t="n">
         <v>2900</v>
       </c>
       <c r="Q892" t="n">
-        <v>116000</v>
+        <v>95700</v>
       </c>
     </row>
     <row r="893">
@@ -39150,22 +39150,22 @@
         <v>0</v>
       </c>
       <c r="L894" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M894" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N894" t="n">
-        <v>1668.656744186</v>
+        <v>1668.6580952381</v>
       </c>
       <c r="O894" t="n">
-        <v>225268.66046511</v>
+        <v>218594.2104761911</v>
       </c>
       <c r="P894" t="n">
         <v>2500</v>
       </c>
       <c r="Q894" t="n">
-        <v>337500</v>
+        <v>327500</v>
       </c>
     </row>
     <row r="895">
@@ -39248,10 +39248,10 @@
         <v>971</v>
       </c>
       <c r="N896" t="n">
-        <v>1259.2752009274</v>
+        <v>1259.2751769231</v>
       </c>
       <c r="O896" t="n">
-        <v>1222756.220100505</v>
+        <v>1222756.19679233</v>
       </c>
       <c r="P896" t="n">
         <v>1900</v>
@@ -39465,22 +39465,22 @@
         <v>0</v>
       </c>
       <c r="L901" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M901" t="n">
-        <v>2326</v>
+        <v>2314</v>
       </c>
       <c r="N901" t="n">
-        <v>692.1525418121701</v>
+        <v>692.15254743047</v>
       </c>
       <c r="O901" t="n">
-        <v>1609946.812255108</v>
+        <v>1601640.994754108</v>
       </c>
       <c r="P901" t="n">
         <v>1200</v>
       </c>
       <c r="Q901" t="n">
-        <v>2791200</v>
+        <v>2776800</v>
       </c>
     </row>
     <row r="902">
@@ -40366,22 +40366,22 @@
         <v>0</v>
       </c>
       <c r="L920" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M920" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="N920" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O920" t="n">
-        <v>3005647.68</v>
+        <v>2980154.355119455</v>
       </c>
       <c r="P920" t="n">
         <v>14900</v>
       </c>
       <c r="Q920" t="n">
-        <v>5006400</v>
+        <v>4961700</v>
       </c>
     </row>
     <row r="921">
@@ -41288,10 +41288,10 @@
         <v>351</v>
       </c>
       <c r="N940" t="n">
-        <v>2286.1643873518</v>
+        <v>2286.164453125</v>
       </c>
       <c r="O940" t="n">
-        <v>802443.6999604818</v>
+        <v>802443.723046875</v>
       </c>
       <c r="P940" t="n">
         <v>3000</v>
@@ -41808,10 +41808,10 @@
         <v>464</v>
       </c>
       <c r="N952" t="n">
-        <v>517.29691759113</v>
+        <v>517.29686746988</v>
       </c>
       <c r="O952" t="n">
-        <v>240025.7697622843</v>
+        <v>240025.7465060243</v>
       </c>
       <c r="P952" t="n">
         <v>900</v>
@@ -42125,10 +42125,10 @@
         <v>12619</v>
       </c>
       <c r="N959" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O959" t="n">
-        <v>8881183.914344454</v>
+        <v>8881183.936428713</v>
       </c>
       <c r="P959" t="n">
         <v>900</v>
@@ -46020,10 +46020,10 @@
         <v>3</v>
       </c>
       <c r="N1043" t="n">
-        <v>5254.1635714286</v>
+        <v>5216.9</v>
       </c>
       <c r="O1043" t="n">
-        <v>15762.4907142858</v>
+        <v>15650.7</v>
       </c>
       <c r="P1043" t="n">
         <v>20500</v>
@@ -46817,22 +46817,22 @@
         <v>0</v>
       </c>
       <c r="L1060" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1060" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N1060" t="n">
         <v>3155</v>
       </c>
       <c r="O1060" t="n">
-        <v>1003290</v>
+        <v>1000135</v>
       </c>
       <c r="P1060" t="n">
         <v>5900</v>
       </c>
       <c r="Q1060" t="n">
-        <v>1876200</v>
+        <v>1870300</v>
       </c>
     </row>
     <row r="1061">
@@ -46915,22 +46915,22 @@
         <v>0</v>
       </c>
       <c r="L1062" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1062" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N1062" t="n">
-        <v>465.87103377687</v>
+        <v>465.87103696099</v>
       </c>
       <c r="O1062" t="n">
-        <v>43326.00614124891</v>
+        <v>41928.3933264891</v>
       </c>
       <c r="P1062" t="n">
         <v>2500</v>
       </c>
       <c r="Q1062" t="n">
-        <v>232500</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="1063">
@@ -48198,22 +48198,22 @@
         <v>0</v>
       </c>
       <c r="L1092" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M1092" t="n">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="N1092" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1092" t="n">
-        <v>1526011.29</v>
+        <v>1510715.88</v>
       </c>
       <c r="P1092" t="n">
         <v>1900</v>
       </c>
       <c r="Q1092" t="n">
-        <v>2464300</v>
+        <v>2439600</v>
       </c>
     </row>
     <row r="1093">
@@ -49203,10 +49203,10 @@
         <v>372</v>
       </c>
       <c r="N1115" t="n">
-        <v>22951.704393305</v>
+        <v>22951.704377622</v>
       </c>
       <c r="O1115" t="n">
-        <v>8538034.03430946</v>
+        <v>8538034.028475385</v>
       </c>
       <c r="P1115" t="n">
         <v>37900</v>
@@ -52510,22 +52510,22 @@
         <v>0</v>
       </c>
       <c r="L1187" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1187" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="N1187" t="n">
-        <v>4687.9754746137</v>
+        <v>4719.2286444444</v>
       </c>
       <c r="O1187" t="n">
-        <v>1537655.955673293</v>
+        <v>1519591.623511097</v>
       </c>
       <c r="P1187" t="n">
         <v>5500</v>
       </c>
       <c r="Q1187" t="n">
-        <v>1804000</v>
+        <v>1771000</v>
       </c>
     </row>
     <row r="1188">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1802,10 +1802,10 @@
         <v>116</v>
       </c>
       <c r="N34" t="n">
-        <v>15238.01</v>
+        <v>15304.843377193</v>
       </c>
       <c r="O34" t="n">
-        <v>1767609.16</v>
+        <v>1775361.831754388</v>
       </c>
       <c r="P34" t="n">
         <v>40400</v>
@@ -10892,10 +10892,10 @@
         <v>297</v>
       </c>
       <c r="N250" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O250" t="n">
-        <v>4037224.95</v>
+        <v>4067167.285846764</v>
       </c>
       <c r="P250" t="n">
         <v>25500</v>
@@ -11458,10 +11458,10 @@
         <v>517</v>
       </c>
       <c r="N263" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O263" t="n">
-        <v>1335025.684637426</v>
+        <v>1335025.672230512</v>
       </c>
       <c r="P263" t="n">
         <v>4500</v>
@@ -13222,10 +13222,10 @@
         <v>250</v>
       </c>
       <c r="N303" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O303" t="n">
-        <v>1222732.514134275</v>
+        <v>1222732.514255175</v>
       </c>
       <c r="P303" t="n">
         <v>8900</v>
@@ -14285,10 +14285,10 @@
         <v>282</v>
       </c>
       <c r="N327" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O327" t="n">
-        <v>4179910.825571406</v>
+        <v>4182494.20679844</v>
       </c>
       <c r="P327" t="n">
         <v>24900</v>
@@ -14836,10 +14836,10 @@
         <v>378</v>
       </c>
       <c r="N340" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O340" t="n">
-        <v>4695691.01750784</v>
+        <v>4695691.019017573</v>
       </c>
       <c r="P340" t="n">
         <v>19900</v>
@@ -14967,10 +14967,10 @@
         <v>2490</v>
       </c>
       <c r="N343" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O343" t="n">
-        <v>8645968.219817489</v>
+        <v>8645968.253924264</v>
       </c>
       <c r="P343" t="n">
         <v>5900</v>
@@ -15368,10 +15368,10 @@
         <v>429</v>
       </c>
       <c r="N352" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O352" t="n">
-        <v>1875233.205498467</v>
+        <v>1875233.205703272</v>
       </c>
       <c r="P352" t="n">
         <v>8900</v>
@@ -17858,10 +17858,10 @@
         <v>21</v>
       </c>
       <c r="N409" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O409" t="n">
-        <v>34249.4278037373</v>
+        <v>34295.2158088239</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
@@ -17950,10 +17950,10 @@
         <v>239</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O411" t="n">
-        <v>370496.5960510752</v>
+        <v>370496.5963683716</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
@@ -18042,10 +18042,10 @@
         <v>37</v>
       </c>
       <c r="N413" t="n">
-        <v>2403.523063498</v>
+        <v>2404.4159026746</v>
       </c>
       <c r="O413" t="n">
-        <v>88930.35334942599</v>
+        <v>88963.3883989602</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
@@ -20549,10 +20549,10 @@
         <v>36</v>
       </c>
       <c r="N471" t="n">
-        <v>18071.26</v>
+        <v>18238.586481481</v>
       </c>
       <c r="O471" t="n">
-        <v>650565.36</v>
+        <v>656589.1133333161</v>
       </c>
       <c r="P471" t="n">
         <v>23900</v>
@@ -25224,10 +25224,10 @@
         <v>879</v>
       </c>
       <c r="N582" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O582" t="n">
-        <v>4231737.484138071</v>
+        <v>4231737.482192052</v>
       </c>
       <c r="P582" t="n">
         <v>7900</v>
@@ -25444,10 +25444,10 @@
         <v>2</v>
       </c>
       <c r="N587" t="n">
-        <v>13513.644019608</v>
+        <v>13513.644059406</v>
       </c>
       <c r="O587" t="n">
-        <v>27027.288039216</v>
+        <v>27027.288118812</v>
       </c>
       <c r="P587" t="n">
         <v>21900</v>
@@ -27260,10 +27260,10 @@
         <v>135</v>
       </c>
       <c r="N630" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O630" t="n">
-        <v>3661708.21934463</v>
+        <v>3661708.217796585</v>
       </c>
       <c r="P630" t="n">
         <v>44500</v>
@@ -28694,10 +28694,10 @@
         <v>51</v>
       </c>
       <c r="N664" t="n">
-        <v>8968.24</v>
+        <v>9120.244067796601</v>
       </c>
       <c r="O664" t="n">
-        <v>457380.24</v>
+        <v>465132.4474576266</v>
       </c>
       <c r="P664" t="n">
         <v>18600</v>
@@ -29483,10 +29483,10 @@
         <v>3</v>
       </c>
       <c r="N683" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O683" t="n">
-        <v>38944.77</v>
+        <v>39101.805362904</v>
       </c>
       <c r="P683" t="n">
         <v>21900</v>
@@ -32025,10 +32025,10 @@
         <v>193</v>
       </c>
       <c r="N739" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O739" t="n">
-        <v>4928062</v>
+        <v>4936495.648602336</v>
       </c>
       <c r="P739" t="n">
         <v>40900</v>
@@ -32764,10 +32764,10 @@
         <v>21</v>
       </c>
       <c r="N755" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O755" t="n">
-        <v>68443.41560000071</v>
+        <v>68443.4156756763</v>
       </c>
       <c r="P755" t="n">
         <v>5300</v>
@@ -33045,10 +33045,10 @@
         <v>56</v>
       </c>
       <c r="N761" t="n">
-        <v>2260</v>
+        <v>2280.7339449541</v>
       </c>
       <c r="O761" t="n">
-        <v>126560</v>
+        <v>127721.1009174296</v>
       </c>
       <c r="P761" t="n">
         <v>3800</v>
@@ -34658,10 +34658,10 @@
         <v>76</v>
       </c>
       <c r="N796" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O796" t="n">
-        <v>684228</v>
+        <v>685379.8989899016</v>
       </c>
       <c r="P796" t="n">
         <v>14900</v>
@@ -36539,10 +36539,10 @@
         <v>111</v>
       </c>
       <c r="N837" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O837" t="n">
-        <v>1997112</v>
+        <v>1999722.603921528</v>
       </c>
       <c r="P837" t="n">
         <v>28900</v>
@@ -37871,10 +37871,10 @@
         <v>4</v>
       </c>
       <c r="N866" t="n">
-        <v>15472</v>
+        <v>15516.07977208</v>
       </c>
       <c r="O866" t="n">
-        <v>61888</v>
+        <v>62064.31908832</v>
       </c>
       <c r="P866" t="n">
         <v>25900</v>
@@ -38150,10 +38150,10 @@
         <v>1233</v>
       </c>
       <c r="N872" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O872" t="n">
-        <v>1869275.713838099</v>
+        <v>1869275.713668068</v>
       </c>
       <c r="P872" t="n">
         <v>2300</v>
@@ -38332,10 +38332,10 @@
         <v>98</v>
       </c>
       <c r="N876" t="n">
-        <v>1803.0176696833</v>
+        <v>1803.0176731553</v>
       </c>
       <c r="O876" t="n">
-        <v>176695.7316289634</v>
+        <v>176695.7319692194</v>
       </c>
       <c r="P876" t="n">
         <v>2500</v>
@@ -38378,10 +38378,10 @@
         <v>83</v>
       </c>
       <c r="N877" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942492013</v>
       </c>
       <c r="O877" t="n">
-        <v>274447.3242038197</v>
+        <v>274447.3226837079</v>
       </c>
       <c r="P877" t="n">
         <v>4900</v>
@@ -38795,10 +38795,10 @@
         <v>200</v>
       </c>
       <c r="N886" t="n">
-        <v>1592.2892358079</v>
+        <v>1595.7734573304</v>
       </c>
       <c r="O886" t="n">
-        <v>318457.84716158</v>
+        <v>319154.69146608</v>
       </c>
       <c r="P886" t="n">
         <v>2500</v>
@@ -39156,10 +39156,10 @@
         <v>971</v>
       </c>
       <c r="N894" t="n">
-        <v>1259.2751809084</v>
+        <v>1259.2751822382</v>
       </c>
       <c r="O894" t="n">
-        <v>1222756.200662056</v>
+        <v>1222756.201953292</v>
       </c>
       <c r="P894" t="n">
         <v>1900</v>
@@ -39662,10 +39662,10 @@
         <v>595</v>
       </c>
       <c r="N905" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O905" t="n">
-        <v>8043210</v>
+        <v>8045456.07930757</v>
       </c>
       <c r="P905" t="n">
         <v>21900</v>
@@ -40136,10 +40136,10 @@
         <v>1</v>
       </c>
       <c r="N915" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="O915" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="P915" t="n">
         <v>24900</v>
@@ -42033,10 +42033,10 @@
         <v>12595</v>
       </c>
       <c r="N957" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O957" t="n">
-        <v>8864292.796409186</v>
+        <v>8864292.774321586</v>
       </c>
       <c r="P957" t="n">
         <v>900</v>
@@ -43165,10 +43165,10 @@
         <v>8</v>
       </c>
       <c r="N982" t="n">
-        <v>9694.41</v>
+        <v>12723.913125</v>
       </c>
       <c r="O982" t="n">
-        <v>77555.28</v>
+        <v>101791.305</v>
       </c>
       <c r="P982" t="n">
         <v>32500</v>
@@ -44148,10 +44148,10 @@
         <v>1</v>
       </c>
       <c r="N1003" t="n">
-        <v>19632.66</v>
+        <v>19743.578983051</v>
       </c>
       <c r="O1003" t="n">
-        <v>19632.66</v>
+        <v>19743.578983051</v>
       </c>
       <c r="P1003" t="n">
         <v>2800</v>
@@ -44800,10 +44800,10 @@
         <v>1</v>
       </c>
       <c r="N1017" t="n">
-        <v>22042.26</v>
+        <v>23737.818461538</v>
       </c>
       <c r="O1017" t="n">
-        <v>22042.26</v>
+        <v>23737.818461538</v>
       </c>
       <c r="P1017" t="n">
         <v>56000</v>
@@ -49111,10 +49111,10 @@
         <v>372</v>
       </c>
       <c r="N1113" t="n">
-        <v>22951.704377622</v>
+        <v>22951.704345992</v>
       </c>
       <c r="O1113" t="n">
-        <v>8538034.028475385</v>
+        <v>8538034.016709024</v>
       </c>
       <c r="P1113" t="n">
         <v>37900</v>
@@ -50755,10 +50755,10 @@
         <v>60</v>
       </c>
       <c r="N1149" t="n">
-        <v>4576</v>
+        <v>4591.2533333333</v>
       </c>
       <c r="O1149" t="n">
-        <v>274560</v>
+        <v>275475.199999998</v>
       </c>
       <c r="P1149" t="n">
         <v>5900</v>
@@ -50801,10 +50801,10 @@
         <v>32</v>
       </c>
       <c r="N1150" t="n">
-        <v>5280</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O1150" t="n">
-        <v>168960</v>
+        <v>169125.8096172704</v>
       </c>
       <c r="P1150" t="n">
         <v>6900</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1802,10 +1802,10 @@
         <v>116</v>
       </c>
       <c r="N34" t="n">
-        <v>15304.843377193</v>
+        <v>15238.01</v>
       </c>
       <c r="O34" t="n">
-        <v>1775361.831754388</v>
+        <v>1767609.16</v>
       </c>
       <c r="P34" t="n">
         <v>40400</v>
@@ -3012,10 +3012,10 @@
         <v>281</v>
       </c>
       <c r="N64" t="n">
-        <v>2474.7033461538</v>
+        <v>2474.7028512397</v>
       </c>
       <c r="O64" t="n">
-        <v>695391.6402692178</v>
+        <v>695391.5011983557</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3168,10 +3168,10 @@
         <v>51</v>
       </c>
       <c r="N68" t="n">
-        <v>3716.3301980198</v>
+        <v>3716.3301983471</v>
       </c>
       <c r="O68" t="n">
-        <v>189532.8400990098</v>
+        <v>189532.8401157021</v>
       </c>
       <c r="P68" t="n">
         <v>9500</v>
@@ -3441,10 +3441,10 @@
         <v>39</v>
       </c>
       <c r="N75" t="n">
-        <v>15403.521104651</v>
+        <v>15403.521169591</v>
       </c>
       <c r="O75" t="n">
-        <v>600737.323081389</v>
+        <v>600737.325614049</v>
       </c>
       <c r="P75" t="n">
         <v>33500</v>
@@ -3480,10 +3480,10 @@
         <v>74</v>
       </c>
       <c r="N76" t="n">
-        <v>14857.623287671</v>
+        <v>14857.623302752</v>
       </c>
       <c r="O76" t="n">
-        <v>1099464.123287654</v>
+        <v>1099464.124403648</v>
       </c>
       <c r="P76" t="n">
         <v>34900</v>
@@ -4901,10 +4901,10 @@
         <v>7</v>
       </c>
       <c r="N108" t="n">
-        <v>15711.963708609</v>
+        <v>15711.963537415</v>
       </c>
       <c r="O108" t="n">
-        <v>109983.745960263</v>
+        <v>109983.744761905</v>
       </c>
       <c r="P108" t="n">
         <v>28500</v>
@@ -9206,10 +9206,10 @@
         <v>79</v>
       </c>
       <c r="N210" t="n">
-        <v>4937.3101888412</v>
+        <v>4937.3101890034</v>
       </c>
       <c r="O210" t="n">
-        <v>390047.5049184548</v>
+        <v>390047.5049312686</v>
       </c>
       <c r="P210" t="n">
         <v>7500</v>
@@ -10892,10 +10892,10 @@
         <v>297</v>
       </c>
       <c r="N250" t="n">
-        <v>13694.165945612</v>
+        <v>13593.35</v>
       </c>
       <c r="O250" t="n">
-        <v>4067167.285846764</v>
+        <v>4037224.95</v>
       </c>
       <c r="P250" t="n">
         <v>25500</v>
@@ -11458,10 +11458,10 @@
         <v>517</v>
       </c>
       <c r="N263" t="n">
-        <v>2582.2546851654</v>
+        <v>2582.2546595174</v>
       </c>
       <c r="O263" t="n">
-        <v>1335025.672230512</v>
+        <v>1335025.658970496</v>
       </c>
       <c r="P263" t="n">
         <v>4500</v>
@@ -11888,10 +11888,10 @@
         <v>2778</v>
       </c>
       <c r="N273" t="n">
-        <v>3158.8608437109</v>
+        <v>3158.8608442176</v>
       </c>
       <c r="O273" t="n">
-        <v>8775315.423828881</v>
+        <v>8775315.425236493</v>
       </c>
       <c r="P273" t="n">
         <v>5600</v>
@@ -12833,10 +12833,10 @@
         <v>468</v>
       </c>
       <c r="N294" t="n">
-        <v>3795.7100076628</v>
+        <v>3795.7100076717</v>
       </c>
       <c r="O294" t="n">
-        <v>1776392.28358619</v>
+        <v>1776392.283590356</v>
       </c>
       <c r="P294" t="n">
         <v>6200</v>
@@ -13222,10 +13222,10 @@
         <v>250</v>
       </c>
       <c r="N303" t="n">
-        <v>4890.9300570207</v>
+        <v>4890.9300571837</v>
       </c>
       <c r="O303" t="n">
-        <v>1222732.514255175</v>
+        <v>1222732.514295925</v>
       </c>
       <c r="P303" t="n">
         <v>8900</v>
@@ -14147,10 +14147,10 @@
         <v>1</v>
       </c>
       <c r="N324" t="n">
-        <v>3240.8500597015</v>
+        <v>3240.8500619195</v>
       </c>
       <c r="O324" t="n">
-        <v>3240.8500597015</v>
+        <v>3240.8500619195</v>
       </c>
       <c r="P324" t="n">
         <v>5200</v>
@@ -14285,10 +14285,10 @@
         <v>282</v>
       </c>
       <c r="N327" t="n">
-        <v>14831.53974042</v>
+        <v>14822.378811881</v>
       </c>
       <c r="O327" t="n">
-        <v>4182494.20679844</v>
+        <v>4179910.824950442</v>
       </c>
       <c r="P327" t="n">
         <v>24900</v>
@@ -14836,10 +14836,10 @@
         <v>378</v>
       </c>
       <c r="N340" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46301728</v>
       </c>
       <c r="O340" t="n">
-        <v>4695691.019017573</v>
+        <v>4695691.020531841</v>
       </c>
       <c r="P340" t="n">
         <v>19900</v>
@@ -14967,10 +14967,10 @@
         <v>2490</v>
       </c>
       <c r="N343" t="n">
-        <v>3472.2764071985</v>
+        <v>3472.2764292368</v>
       </c>
       <c r="O343" t="n">
-        <v>8645968.253924264</v>
+        <v>8645968.308799632</v>
       </c>
       <c r="P343" t="n">
         <v>5900</v>
@@ -15368,10 +15368,10 @@
         <v>429</v>
       </c>
       <c r="N352" t="n">
-        <v>4371.1729736673</v>
+        <v>4371.1729765349</v>
       </c>
       <c r="O352" t="n">
-        <v>1875233.205703272</v>
+        <v>1875233.206933472</v>
       </c>
       <c r="P352" t="n">
         <v>8900</v>
@@ -17111,10 +17111,10 @@
         <v>1</v>
       </c>
       <c r="N392" t="n">
-        <v>21670.98</v>
+        <v>32506.47</v>
       </c>
       <c r="O392" t="n">
-        <v>21670.98</v>
+        <v>32506.47</v>
       </c>
       <c r="P392" t="n">
         <v>32000</v>
@@ -17858,10 +17858,10 @@
         <v>21</v>
       </c>
       <c r="N409" t="n">
-        <v>1633.1055147059</v>
+        <v>1630.9252455662</v>
       </c>
       <c r="O409" t="n">
-        <v>34295.2158088239</v>
+        <v>34249.4301568902</v>
       </c>
       <c r="P409" t="n">
         <v>2500</v>
@@ -17950,10 +17950,10 @@
         <v>239</v>
       </c>
       <c r="N411" t="n">
-        <v>1550.1949638844</v>
+        <v>1550.1949858928</v>
       </c>
       <c r="O411" t="n">
-        <v>370496.5963683716</v>
+        <v>370496.6016283792</v>
       </c>
       <c r="P411" t="n">
         <v>2500</v>
@@ -18042,10 +18042,10 @@
         <v>37</v>
       </c>
       <c r="N413" t="n">
-        <v>2404.4159026746</v>
+        <v>2403.5234112326</v>
       </c>
       <c r="O413" t="n">
-        <v>88963.3883989602</v>
+        <v>88930.36621560621</v>
       </c>
       <c r="P413" t="n">
         <v>3500</v>
@@ -21659,10 +21659,10 @@
         <v>6</v>
       </c>
       <c r="N497" t="n">
-        <v>7537.4724786325</v>
+        <v>7537.4727619048</v>
       </c>
       <c r="O497" t="n">
-        <v>45224.834871795</v>
+        <v>45224.8365714288</v>
       </c>
       <c r="P497" t="n">
         <v>8900</v>
@@ -22449,10 +22449,10 @@
         <v>186</v>
       </c>
       <c r="N516" t="n">
-        <v>2029.8742613636</v>
+        <v>2029.8742906178</v>
       </c>
       <c r="O516" t="n">
-        <v>377556.6126136296</v>
+        <v>377556.6180549108</v>
       </c>
       <c r="P516" t="n">
         <v>3600</v>
@@ -24337,10 +24337,10 @@
         <v>1198</v>
       </c>
       <c r="N561" t="n">
-        <v>6207.9881978301</v>
+        <v>6207.9881950325</v>
       </c>
       <c r="O561" t="n">
-        <v>7437169.86100046</v>
+        <v>7437169.857648935</v>
       </c>
       <c r="P561" t="n">
         <v>9900</v>
@@ -25224,10 +25224,10 @@
         <v>879</v>
       </c>
       <c r="N582" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.263336112</v>
       </c>
       <c r="O582" t="n">
-        <v>4231737.482192052</v>
+        <v>4231737.472442448</v>
       </c>
       <c r="P582" t="n">
         <v>7900</v>
@@ -25398,10 +25398,10 @@
         <v>84</v>
       </c>
       <c r="N586" t="n">
-        <v>11562.038362573</v>
+        <v>11562.038338279</v>
       </c>
       <c r="O586" t="n">
-        <v>971211.2224561319</v>
+        <v>971211.2204154361</v>
       </c>
       <c r="P586" t="n">
         <v>18500</v>
@@ -25444,10 +25444,10 @@
         <v>2</v>
       </c>
       <c r="N587" t="n">
-        <v>13513.644059406</v>
+        <v>13513.644408602</v>
       </c>
       <c r="O587" t="n">
-        <v>27027.288118812</v>
+        <v>27027.288817204</v>
       </c>
       <c r="P587" t="n">
         <v>21900</v>
@@ -27639,10 +27639,10 @@
         <v>78</v>
       </c>
       <c r="N639" t="n">
-        <v>8332.7795945946</v>
+        <v>8332.7795901639</v>
       </c>
       <c r="O639" t="n">
-        <v>649956.8083783787</v>
+        <v>649956.8080327843</v>
       </c>
       <c r="P639" t="n">
         <v>14900</v>
@@ -27936,10 +27936,10 @@
         <v>44</v>
       </c>
       <c r="N646" t="n">
-        <v>1561.0125437573</v>
+        <v>1561.0077085243</v>
       </c>
       <c r="O646" t="n">
-        <v>68684.5519253212</v>
+        <v>68684.3391750692</v>
       </c>
       <c r="P646" t="n">
         <v>2900</v>
@@ -29483,10 +29483,10 @@
         <v>3</v>
       </c>
       <c r="N683" t="n">
-        <v>13033.935120968</v>
+        <v>12981.59</v>
       </c>
       <c r="O683" t="n">
-        <v>39101.805362904</v>
+        <v>38944.77</v>
       </c>
       <c r="P683" t="n">
         <v>21900</v>
@@ -31519,10 +31519,10 @@
         <v>244</v>
       </c>
       <c r="N728" t="n">
-        <v>3646</v>
+        <v>3656.7445972495</v>
       </c>
       <c r="O728" t="n">
-        <v>889624</v>
+        <v>892245.6817288781</v>
       </c>
       <c r="P728" t="n">
         <v>6900</v>
@@ -31565,10 +31565,10 @@
         <v>16</v>
       </c>
       <c r="N729" t="n">
-        <v>23521.618709677</v>
+        <v>23521.6175</v>
       </c>
       <c r="O729" t="n">
-        <v>376345.899354832</v>
+        <v>376345.88</v>
       </c>
       <c r="P729" t="n">
         <v>39000</v>
@@ -31657,10 +31657,10 @@
         <v>624</v>
       </c>
       <c r="N731" t="n">
-        <v>3486</v>
+        <v>3488.1801125704</v>
       </c>
       <c r="O731" t="n">
-        <v>2175264</v>
+        <v>2176624.39024393</v>
       </c>
       <c r="P731" t="n">
         <v>6900</v>
@@ -31703,10 +31703,10 @@
         <v>1152</v>
       </c>
       <c r="N732" t="n">
-        <v>1778.4728955224</v>
+        <v>1779.3581483325</v>
       </c>
       <c r="O732" t="n">
-        <v>2048800.775641805</v>
+        <v>2049820.58687904</v>
       </c>
       <c r="P732" t="n">
         <v>4900</v>
@@ -32025,10 +32025,10 @@
         <v>193</v>
       </c>
       <c r="N739" t="n">
-        <v>25577.697661152</v>
+        <v>25534</v>
       </c>
       <c r="O739" t="n">
-        <v>4936495.648602336</v>
+        <v>4928062</v>
       </c>
       <c r="P739" t="n">
         <v>40900</v>
@@ -32074,10 +32074,10 @@
         <v>5</v>
       </c>
       <c r="N740" t="n">
-        <v>26956</v>
+        <v>28541.647058824</v>
       </c>
       <c r="O740" t="n">
-        <v>134780</v>
+        <v>142708.23529412</v>
       </c>
       <c r="P740" t="n">
         <v>44900</v>
@@ -34103,10 +34103,10 @@
         <v>93</v>
       </c>
       <c r="N784" t="n">
-        <v>2252.3013646055</v>
+        <v>2252.3013888889</v>
       </c>
       <c r="O784" t="n">
-        <v>209464.0269083115</v>
+        <v>209464.0291666677</v>
       </c>
       <c r="P784" t="n">
         <v>3900</v>
@@ -34336,10 +34336,10 @@
         <v>422</v>
       </c>
       <c r="N789" t="n">
-        <v>2328.1186316472</v>
+        <v>2328.1186298701</v>
       </c>
       <c r="O789" t="n">
-        <v>982466.0625551183</v>
+        <v>982466.0618051823</v>
       </c>
       <c r="P789" t="n">
         <v>4500</v>
@@ -34382,10 +34382,10 @@
         <v>84</v>
       </c>
       <c r="N790" t="n">
-        <v>21676</v>
+        <v>21700.382452193</v>
       </c>
       <c r="O790" t="n">
-        <v>1820784</v>
+        <v>1822832.125984212</v>
       </c>
       <c r="P790" t="n">
         <v>34900</v>
@@ -34428,10 +34428,10 @@
         <v>90</v>
       </c>
       <c r="N791" t="n">
-        <v>9384</v>
+        <v>9474.8129032258</v>
       </c>
       <c r="O791" t="n">
-        <v>844560</v>
+        <v>852733.161290322</v>
       </c>
       <c r="P791" t="n">
         <v>15900</v>
@@ -34658,10 +34658,10 @@
         <v>76</v>
       </c>
       <c r="N796" t="n">
-        <v>9018.1565656566</v>
+        <v>9003</v>
       </c>
       <c r="O796" t="n">
-        <v>685379.8989899016</v>
+        <v>684228</v>
       </c>
       <c r="P796" t="n">
         <v>14900</v>
@@ -35072,10 +35072,10 @@
         <v>15</v>
       </c>
       <c r="N805" t="n">
-        <v>4907.8228863636</v>
+        <v>4907.8230382775</v>
       </c>
       <c r="O805" t="n">
-        <v>73617.343295454</v>
+        <v>73617.34557416249</v>
       </c>
       <c r="P805" t="n">
         <v>8200</v>
@@ -37595,10 +37595,10 @@
         <v>16</v>
       </c>
       <c r="N860" t="n">
-        <v>10713.21</v>
+        <v>10736.550326797</v>
       </c>
       <c r="O860" t="n">
-        <v>171411.36</v>
+        <v>171784.805228752</v>
       </c>
       <c r="P860" t="n">
         <v>20900</v>
@@ -37871,10 +37871,10 @@
         <v>4</v>
       </c>
       <c r="N866" t="n">
-        <v>15516.07977208</v>
+        <v>15472</v>
       </c>
       <c r="O866" t="n">
-        <v>62064.31908832</v>
+        <v>61888</v>
       </c>
       <c r="P866" t="n">
         <v>25900</v>
@@ -38150,10 +38150,10 @@
         <v>1233</v>
       </c>
       <c r="N872" t="n">
-        <v>1516.0386972166</v>
+        <v>1516.0386977679</v>
       </c>
       <c r="O872" t="n">
-        <v>1869275.713668068</v>
+        <v>1869275.714347821</v>
       </c>
       <c r="P872" t="n">
         <v>2300</v>
@@ -38240,10 +38240,10 @@
         <v>243</v>
       </c>
       <c r="N874" t="n">
-        <v>2458.5122572276</v>
+        <v>2458.5121994025</v>
       </c>
       <c r="O874" t="n">
-        <v>597418.4785063068</v>
+        <v>597418.4644548075</v>
       </c>
       <c r="P874" t="n">
         <v>3500</v>
@@ -38286,10 +38286,10 @@
         <v>164</v>
       </c>
       <c r="N875" t="n">
-        <v>2079.3831463696</v>
+        <v>2079.3831437356</v>
       </c>
       <c r="O875" t="n">
-        <v>341018.8360046144</v>
+        <v>341018.8355726384</v>
       </c>
       <c r="P875" t="n">
         <v>2900</v>
@@ -38332,10 +38332,10 @@
         <v>98</v>
       </c>
       <c r="N876" t="n">
-        <v>1803.0176731553</v>
+        <v>1803.0177185792</v>
       </c>
       <c r="O876" t="n">
-        <v>176695.7319692194</v>
+        <v>176695.7364207616</v>
       </c>
       <c r="P876" t="n">
         <v>2500</v>
@@ -38424,10 +38424,10 @@
         <v>13</v>
       </c>
       <c r="N878" t="n">
-        <v>2108.8001384083</v>
+        <v>2108.8003733956</v>
       </c>
       <c r="O878" t="n">
-        <v>27414.4017993079</v>
+        <v>27414.4048541428</v>
       </c>
       <c r="P878" t="n">
         <v>2900</v>
@@ -38516,10 +38516,10 @@
         <v>125</v>
       </c>
       <c r="N880" t="n">
-        <v>3224.5700392597</v>
+        <v>3224.5700448934</v>
       </c>
       <c r="O880" t="n">
-        <v>403071.2549074625</v>
+        <v>403071.255611675</v>
       </c>
       <c r="P880" t="n">
         <v>4500</v>
@@ -38795,10 +38795,10 @@
         <v>200</v>
       </c>
       <c r="N886" t="n">
-        <v>1595.7734573304</v>
+        <v>1592.2894481236</v>
       </c>
       <c r="O886" t="n">
-        <v>319154.69146608</v>
+        <v>318457.88962472</v>
       </c>
       <c r="P886" t="n">
         <v>2500</v>
@@ -39156,10 +39156,10 @@
         <v>971</v>
       </c>
       <c r="N894" t="n">
-        <v>1259.2751822382</v>
+        <v>1259.2752022675</v>
       </c>
       <c r="O894" t="n">
-        <v>1222756.201953292</v>
+        <v>1222756.221401742</v>
       </c>
       <c r="P894" t="n">
         <v>1900</v>
@@ -39662,10 +39662,10 @@
         <v>595</v>
       </c>
       <c r="N905" t="n">
-        <v>13521.774923206</v>
+        <v>13518</v>
       </c>
       <c r="O905" t="n">
-        <v>8045456.07930757</v>
+        <v>8043210</v>
       </c>
       <c r="P905" t="n">
         <v>21900</v>
@@ -40136,10 +40136,10 @@
         <v>1</v>
       </c>
       <c r="N915" t="n">
-        <v>15547.741935484</v>
+        <v>15423.36</v>
       </c>
       <c r="O915" t="n">
-        <v>15547.741935484</v>
+        <v>15423.36</v>
       </c>
       <c r="P915" t="n">
         <v>24900</v>
@@ -40971,10 +40971,10 @@
         <v>3529</v>
       </c>
       <c r="N933" t="n">
-        <v>481.48790068997</v>
+        <v>481.48790045249</v>
       </c>
       <c r="O933" t="n">
-        <v>1699170.801534904</v>
+        <v>1699170.800696837</v>
       </c>
       <c r="P933" t="n">
         <v>650</v>
@@ -41582,10 +41582,10 @@
         <v>28</v>
       </c>
       <c r="N947" t="n">
-        <v>4032.3967801047</v>
+        <v>4032.3967716535</v>
       </c>
       <c r="O947" t="n">
-        <v>112907.1098429316</v>
+        <v>112907.109606298</v>
       </c>
       <c r="P947" t="n">
         <v>4200</v>
@@ -41716,10 +41716,10 @@
         <v>464</v>
       </c>
       <c r="N950" t="n">
-        <v>517.29686746988</v>
+        <v>517.29687747036</v>
       </c>
       <c r="O950" t="n">
-        <v>240025.7465060243</v>
+        <v>240025.751146247</v>
       </c>
       <c r="P950" t="n">
         <v>900</v>
@@ -42033,10 +42033,10 @@
         <v>12595</v>
       </c>
       <c r="N957" t="n">
-        <v>703.7945831140599</v>
+        <v>703.79457726026</v>
       </c>
       <c r="O957" t="n">
-        <v>8864292.774321586</v>
+        <v>8864292.700592974</v>
       </c>
       <c r="P957" t="n">
         <v>900</v>
@@ -43165,10 +43165,10 @@
         <v>8</v>
       </c>
       <c r="N982" t="n">
-        <v>12723.913125</v>
+        <v>9694.41</v>
       </c>
       <c r="O982" t="n">
-        <v>101791.305</v>
+        <v>77555.28</v>
       </c>
       <c r="P982" t="n">
         <v>32500</v>
@@ -43816,10 +43816,10 @@
         <v>40</v>
       </c>
       <c r="N996" t="n">
-        <v>5430.86</v>
+        <v>5546.410212766</v>
       </c>
       <c r="O996" t="n">
-        <v>217234.4</v>
+        <v>221856.40851064</v>
       </c>
       <c r="P996" t="n">
         <v>13900</v>
@@ -44936,10 +44936,10 @@
         <v>1</v>
       </c>
       <c r="N1020" t="n">
-        <v>34880.17</v>
+        <v>34880.19</v>
       </c>
       <c r="O1020" t="n">
-        <v>34880.17</v>
+        <v>34880.19</v>
       </c>
       <c r="P1020" t="n">
         <v>65900</v>
@@ -46162,10 +46162,10 @@
         <v>1</v>
       </c>
       <c r="N1046" t="n">
-        <v>24338.47</v>
+        <v>24602.063537906</v>
       </c>
       <c r="O1046" t="n">
-        <v>24338.47</v>
+        <v>24602.063537906</v>
       </c>
       <c r="P1046" t="n">
         <v>27900</v>
@@ -46211,10 +46211,10 @@
         <v>6</v>
       </c>
       <c r="N1047" t="n">
-        <v>8931.4411111111</v>
+        <v>8931.4411764706</v>
       </c>
       <c r="O1047" t="n">
-        <v>53588.6466666666</v>
+        <v>53588.6470588236</v>
       </c>
       <c r="P1047" t="n">
         <v>19900</v>
@@ -49111,10 +49111,10 @@
         <v>372</v>
       </c>
       <c r="N1113" t="n">
-        <v>22951.704345992</v>
+        <v>22951.704248927</v>
       </c>
       <c r="O1113" t="n">
-        <v>8538034.016709024</v>
+        <v>8538033.980600843</v>
       </c>
       <c r="P1113" t="n">
         <v>37900</v>
@@ -49429,10 +49429,10 @@
         <v>24</v>
       </c>
       <c r="N1120" t="n">
-        <v>2367.6159259259</v>
+        <v>2367.6158955224</v>
       </c>
       <c r="O1120" t="n">
-        <v>56822.78222222159</v>
+        <v>56822.7814925376</v>
       </c>
       <c r="P1120" t="n">
         <v>2900</v>
@@ -50755,10 +50755,10 @@
         <v>60</v>
       </c>
       <c r="N1149" t="n">
-        <v>4591.2533333333</v>
+        <v>4576</v>
       </c>
       <c r="O1149" t="n">
-        <v>275475.199999998</v>
+        <v>274560</v>
       </c>
       <c r="P1149" t="n">
         <v>5900</v>
